--- a/data_extactor/batch/951_1000.xlsx
+++ b/data_extactor/batch/951_1000.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26529"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sarbazi\code\sarbazi\data_extactor\batch\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BC642D9-EFCB-4DA7-8B5F-AC3B82E79057}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,8 +24,1612 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="533">
+  <si>
+    <t>53-2022.00</t>
+  </si>
+  <si>
+    <t>Airfield Operations Specialists</t>
+  </si>
+  <si>
+    <t>Airfield Operations Specialist | Airport Operations Agent | Airport Operations Coordinator | Airport Operations Officer | Airport Operations Specialist | Flight Follower | Operations Agent | Operations Coordinator | Operations Officer | Operations Specialist</t>
+  </si>
+  <si>
+    <t>Adobe Photoshop | Aircraft noise monitoring system software | Apache HTTP Server | Decision Support Technologies Propworks | Extensible markup language XML | FileMaker Pro | Ground transportation management system | Internet Protocol Television Systems | Intuit QuickBooks | Linux | Microsoft Access | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft SharePoint | Microsoft Windows | Microsoft Word | Operations scheduling software | Oracle Database | Parking access revenue control system | SAP software | TRMI Airport AVI</t>
+  </si>
+  <si>
+    <t>Monitoring | Active Listening | Speaking | Critical Thinking | Reading Comprehension | Writing | Active Learning | Learning Strategies</t>
+  </si>
+  <si>
+    <t>Public Safety and Security | Transportation | English Language | Customer and Personal Service | Education and Training | Telecommunications | Administration and Management | Law and Government | Administrative | Computers and Electronics | Mathematics | Communications and Media</t>
+  </si>
+  <si>
+    <t>Deductive Reasoning | Problem Sensitivity | Oral Comprehension | Written Comprehension | Oral Expression | Speech Clarity | Inductive Reasoning | Near Vision | Far Vision | Written Expression | Information Ordering | Flexibility of Closure | Perceptual Speed | Selective Attention | Speech Recognition | Category Flexibility | Auditory Attention | Time Sharing | Visualization</t>
+  </si>
+  <si>
+    <t>Contact With Others | Telephone Conversations | Face-to-Face Discussions with Individuals and Within Teams | Freedom to Make Decisions | Consequence of Error | Deal With External Customers or the Public in General | Work With or Contribute to a Work Group or Team | E-Mail | Importance of Being Exact or Accurate | Impact of Decisions on Co-workers or Company Results | Determine Tasks, Priorities and Goals | Importance of Repeating Same Tasks | In an Enclosed Vehicle or Operate Enclosed Equipment | Frequency of Decision Making | Coordinate or Lead Others in Accomplishing Work Activities | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Health and Safety of Other Workers | Outdoors, Exposed to All Weather Conditions | Time Pressure | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Exposed to Contaminants | Indoors, Environmentally Controlled | Work Outcomes and Results of Other Workers | Physical Proximity | Dealing With Unpleasant, Angry, or Discourteous People | Exposed to Very Hot or Cold Temperatures | Conflict Situations | Written Letters and Memos | Exposed to Extremely Bright or Inadequate Lighting Conditions</t>
+  </si>
+  <si>
+    <t>Air Traffic Controllers | Aircraft Cargo Handling Supervisors | Aircraft Service Attendants | Airline Pilots, Copilots, and Flight Engineers | Aviation Inspectors | Commercial Pilots | Dispatchers, Except Police, Fire, and Ambulance | Facilities Managers | First-Line Supervisors of Firefighting and Prevention Workers | First-Line Supervisors of Helpers, Laborers, and Material Movers, Hand | First-Line Supervisors of Material-Moving Machine and Vehicle Operators | First-Line Supervisors of Passenger Attendants | First-Line Supervisors of Security Workers | Flight Attendants | Locomotive Engineers | Railroad Conductors and Yardmasters | Ship Engineers | Traffic Technicians | Transportation Inspectors | Transportation, Storage, and Distribution Managers</t>
+  </si>
+  <si>
+    <t>Ensure the safe takeoff and landing of commercial and military aircraft. Duties include coordination between air-traffic control and maintenance personnel, dispatching, using airfield landing and navigational aids, implementing airfield safety procedures, monitoring and maintaining flight records, and applying knowledge of weather information.</t>
+  </si>
+  <si>
+    <t>Anticipate aircraft equipment needs for air evacuation and cargo flights. | Assist in responding to aircraft and medical emergencies. | Check military flight plans with civilian agencies. | Collaborate with others to plan flight schedules and air crew assignments. | Conduct departure and arrival briefings. | Conduct inspections of the airport property and perimeter to maintain controlled access to airfields. | Coordinate changes to flight itineraries with appropriate Air Traffic Control (ATC) agencies. | Coordinate communications between air traffic control and maintenance personnel. | Coordinate with agencies to meet aircrew requirements for billeting, messing, refueling, ground transportation, and transient aircraft maintenance. | Coordinate with agencies, such as air traffic control, civil engineers, or command posts, to ensure support of airfield management activities. | Implement airfield safety procedures to ensure a safe operating environment for personnel and aircraft operation. | Initiate or conduct airport-wide coordination of snow removal on runways and taxiways. | Inspect airfield conditions to ensure compliance with federal regulatory requirements. | Maintain air-to-ground and point-to-point radio contact with aircraft commanders. | Maintain flight and event logs, air crew flying records, and flight operations records of incoming and outgoing flights. | Manage wildlife on and around airport grounds. | Monitor the arrival, parking, refueling, loading, and departure of all aircraft. | Perform and supervise airfield management activities, including mobile airfield management functions. | Plan and coordinate airfield construction. | Post visual display boards and status boards. | Procure, produce, and provide information on the safe operation of aircraft, such as flight planning publications, operations publications, charts and maps, or weather information. | Provide aircrews with information and services needed for airfield management and flight planning. | Receive and post weather information and flight plan data, such as air routes or arrival and departure times. | Receive, transmit, and control message traffic. | Relay departure, arrival, delay, aircraft and airfield status, and other pertinent information to upline controlling agencies. | Train operations staff. | Use airfield landing and navigational aids and digital data terminal communications equipment to perform duties.</t>
+  </si>
+  <si>
+    <t>53-2031.00</t>
+  </si>
+  <si>
+    <t>Flight Attendants</t>
+  </si>
+  <si>
+    <t>Flight Attendant | In-Flight Crew Member | Inflight Services Flight Attendant | International Flight Attendant | Purser</t>
+  </si>
+  <si>
+    <t>AD OPT Altitude | Arkitektia Flight Itinerary | Bid Assistant | IBM Lotus LearningSpace | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Windows | Microsoft Word | SBS International Maestro Suite | ValtamTech Flight Crew Log</t>
+  </si>
+  <si>
+    <t>Speaking | Active Listening | Monitoring | Reading Comprehension | Critical Thinking | Active Learning | Writing</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | Public Safety and Security | English Language | Transportation | Psychology | Geography | Computers and Electronics | Personnel and Human Resources</t>
+  </si>
+  <si>
+    <t>Oral Expression | Speech Clarity | Oral Comprehension | Speech Recognition | Problem Sensitivity | Near Vision | Deductive Reasoning | Information Ordering | Auditory Attention | Far Vision | Extent Flexibility | Selective Attention | Perceptual Speed | Inductive Reasoning | Flexibility of Closure | Category Flexibility | Written Comprehension | Gross Body Equilibrium | Trunk Strength</t>
+  </si>
+  <si>
+    <t>Health and Safety of Other Workers | Public Speaking | Indoors, Environmentally Controlled | Deal With External Customers or the Public in General | Contact With Others | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Face-to-Face Discussions with Individuals and Within Teams | Physical Proximity | Dealing With Unpleasant, Angry, or Discourteous People | Frequency of Decision Making | Work With or Contribute to a Work Group or Team | Freedom to Make Decisions | Exposed to High Places | Impact of Decisions on Co-workers or Company Results | Consequence of Error | Time Pressure | E-Mail | Exposed to Contaminants | Conflict Situations | Exposed to Radiation | Work Outcomes and Results of Other Workers | Exposed to Cramped Work Space, Awkward Positions | In an Enclosed Vehicle or Operate Enclosed Equipment | Importance of Being Exact or Accurate | Spend Time Standing | Exposed to Disease or Infections | Coordinate or Lead Others in Accomplishing Work Activities | Determine Tasks, Priorities and Goals | Spend Time Walking or Running | Importance of Repeating Same Tasks | Spend Time Bending or Twisting Your Body</t>
+  </si>
+  <si>
+    <t>Air Traffic Controllers | Aircraft Cargo Handling Supervisors | Aircraft Service Attendants | Airfield Operations Specialists | Airline Pilots, Copilots, and Flight Engineers | Ambulance Drivers and Attendants, Except Emergency Medical Technicians | Baggage Porters and Bellhops | Bus Drivers, Transit and Intercity | Commercial Pilots | Dispatchers, Except Police, Fire, and Ambulance | First-Line Supervisors of Passenger Attendants | Locker Room, Coatroom, and Dressing Room Attendants | Passenger Attendants | Railroad Conductors and Yardmasters | Reservation and Transportation Ticket Agents and Travel Clerks | Security Guards | Shuttle Drivers and Chauffeurs | Subway and Streetcar Operators | Transportation Security Screeners | Ushers, Lobby Attendants, and Ticket Takers</t>
+  </si>
+  <si>
+    <t>Monitor safety of the aircraft cabin. Provide services to airline passengers, explain safety information, serve food and beverages, and respond to emergency incidents.</t>
+  </si>
+  <si>
+    <t>Administer first aid to passengers in distress. | Announce and demonstrate safety and emergency procedures, such as the use of oxygen masks, seat belts, and life jackets. | Announce flight delays and descent preparations. | Answer passengers' questions about flights, aircraft, weather, travel routes and services, arrival times, or schedules. | Assist passengers entering or disembarking the aircraft. | Assist passengers in placing carry-on luggage in overhead, garment, or under-seat storage. | Attend preflight briefings concerning weather, altitudes, routes, emergency procedures, crew coordination, lengths of flights, food and beverage services offered, and numbers of passengers. | Check to ensure that food, beverages, blankets, reading material, emergency equipment, and other supplies are aboard and are in adequate supply. | Collect money for meals and beverages. | Conduct periodic trips through the cabin to ensure passenger comfort and to distribute reading material, headphones, pillows, playing cards, and blankets. | Determine special assistance needs of passengers, such as small children, the elderly, or persons with disabilities. | Direct and assist passengers in emergency procedures, such as evacuating a plane following an emergency landing. | Greet passengers boarding aircraft and direct them to assigned seats. | Heat and serve prepared foods. | Inspect and clean cabins, checking for any problems and making sure that cabins are in order. | Inspect passenger tickets to verify information and to obtain destination information. | Monitor passenger behavior to identify threats to the safety of the crew and other passengers. | Operate audio and video systems. | Prepare passengers and aircraft for landing, following procedures. | Prepare reports showing places of departure and destination, passenger ticket numbers, meal and beverage inventories, the conditions of cabin equipment, and any problems encountered by passengers. | Reassure passengers when situations, such as turbulence, are encountered. | Sell alcoholic beverages to passengers. | Take inventory of headsets, alcoholic beverages, and money collected. | Verify that first aid kits and other emergency equipment, including fire extinguishers and oxygen bottles, are in working order. | Walk aisles of planes to verify that passengers have complied with federal regulations prior to takeoffs and landings.</t>
+  </si>
+  <si>
+    <t>53-3011.00</t>
+  </si>
+  <si>
+    <t>Ambulance Drivers and Attendants, Except Emergency Medical Technicians</t>
+  </si>
+  <si>
+    <t>Ambulance Attendant | Ambulance Driver | CPR Ambulance Driver (Cardio Pulmonary Resuscitation Ambulance Driver) | Chair Car Driver | Driver | Driver Medic | EMS Driver (Emergency Medical Services Driver) | Emergency Care Attendant (ECA) | First Responder | Medical Van Driver (Medi-Van Driver)</t>
+  </si>
+  <si>
+    <t>Computer aided dispatch software | Mapping software | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft Word</t>
+  </si>
+  <si>
+    <t>Critical Thinking | Active Listening | Reading Comprehension | Speaking | Active Learning | Monitoring</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | English Language | Public Safety and Security | Administration and Management | Law and Government | Transportation | Education and Training | Medicine and Dentistry</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Problem Sensitivity | Oral Expression | Deductive Reasoning | Near Vision | Speech Recognition | Speech Clarity | Far Vision | Static Strength | Reaction Time | Response Orientation | Multilimb Coordination | Arm-Hand Steadiness | Time Sharing | Spatial Orientation | Information Ordering | Inductive Reasoning | Written Comprehension | Manual Dexterity | Selective Attention | Perceptual Speed | Flexibility of Closure | Category Flexibility | Depth Perception | Trunk Strength | Control Precision</t>
+  </si>
+  <si>
+    <t>Health and Safety of Other Workers | Contact With Others | Physical Proximity | Importance of Being Exact or Accurate | Impact of Decisions on Co-workers or Company Results | Frequency of Decision Making | Face-to-Face Discussions with Individuals and Within Teams | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Outdoors, Exposed to All Weather Conditions | Work With or Contribute to a Work Group or Team | Determine Tasks, Priorities and Goals | In an Enclosed Vehicle or Operate Enclosed Equipment | Freedom to Make Decisions | Deal With External Customers or the Public in General | Consequence of Error | Telephone Conversations | Exposed to Disease or Infections | Importance of Repeating Same Tasks | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Coordinate or Lead Others in Accomplishing Work Activities | Time Pressure | Dealing With Unpleasant, Angry, or Discourteous People | Exposed to Contaminants | Outdoors, Under Cover</t>
+  </si>
+  <si>
+    <t>Acute Care Nurses | Anesthesiologist Assistants | Dispatchers, Except Police, Fire, and Ambulance | Emergency Management Directors | Emergency Medical Technicians | Emergency Medicine Physicians | Home Health Aides | Licensed Practical and Licensed Vocational Nurses | Lifeguards, Ski Patrol, and Other Recreational Protective Service Workers | Medical Assistants | Medical and Health Services Managers | Nursing Assistants | Orderlies | Paramedics | Personal Care Aides | Physical Therapist Aides | Public Safety Telecommunicators | Registered Nurses | Surgical Assistants | Surgical Technologists</t>
+  </si>
+  <si>
+    <t>Drive ambulance or assist ambulance driver in transporting sick, injured, or convalescent persons. Assist in lifting patients.</t>
+  </si>
+  <si>
+    <t>Accompany and assist emergency medical technicians on calls. | Administer first aid, such as bandaging, splinting, or administering oxygen. | Clean and wash rigs, ambulances, or equipment. | Drive ambulances or assist ambulance drivers in transporting sick, injured, or convalescent persons. | Earn and maintain appropriate certifications. | Perform minor maintenance on emergency medical services vehicles, such as ambulances. | Place patients on stretchers, and load stretchers into ambulances, usually with assistance from other attendants. | Remove and replace soiled linens or equipment to maintain sanitary conditions. | Replace supplies and disposable items on ambulances. | Report facts concerning accidents or emergencies to hospital personnel or law enforcement officials. | Restrain or shackle violent patients.</t>
+  </si>
+  <si>
+    <t>53-3031.00</t>
+  </si>
+  <si>
+    <t>Driver/Sales Workers</t>
+  </si>
+  <si>
+    <t>Delivery Man | Driver | Driver Salesman | Pizza Delivery Driver | Route Delivery Driver | Route Driver | Route Sales Driver | Route Sales Representative | Route Salesman | Sales Route Driver</t>
+  </si>
+  <si>
+    <t>Computer Directions Route Sales Tracker | GEOCOMtms A.Maze Planning | IBM Domino | Microsoft Excel | Microsoft Office software | MobiTech Systems Route Sales Trakker | Regulussoft Route Accounting | Route planning software | Soft Essentials Vending Essentials | bMobile Technology Route Manager | bMobile Technology Sales</t>
+  </si>
+  <si>
+    <t>Active Listening | Speaking | Critical Thinking | Reading Comprehension</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | Food Production | English Language | Transportation | Public Safety and Security | Administration and Management</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Oral Expression | Near Vision | Speech Clarity | Speech Recognition | Problem Sensitivity | Deductive Reasoning | Written Comprehension | Far Vision | Trunk Strength | Static Strength | Control Precision | Finger Dexterity | Arm-Hand Steadiness | Category Flexibility | Information Ordering | Inductive Reasoning</t>
+  </si>
+  <si>
+    <t>Outdoors, Exposed to All Weather Conditions | Time Pressure | Exposed to Very Hot or Cold Temperatures | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Face-to-Face Discussions with Individuals and Within Teams | Importance of Repeating Same Tasks | Contact With Others | Deal With External Customers or the Public in General | Spend Time Making Repetitive Motions | Importance of Being Exact or Accurate | Spend Time Bending or Twisting Your Body | In an Enclosed Vehicle or Operate Enclosed Equipment | Determine Tasks, Priorities and Goals | Spend Time Walking or Running | Telephone Conversations | Exposed to Extremely Bright or Inadequate Lighting Conditions | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Impact of Decisions on Co-workers or Company Results | Spend Time Standing | Frequency of Decision Making | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets</t>
+  </si>
+  <si>
+    <t>Buyers and Purchasing Agents, Farm Products | Cargo and Freight Agents | Cashiers | Counter and Rental Clerks | Couriers and Messengers | Customer Service Representatives | Dispatchers, Except Police, Fire, and Ambulance | Door-to-Door Sales Workers, News and Street Vendors, and Related Workers | Fast Food and Counter Workers | Heavy and Tractor-Trailer Truck Drivers | Laborers and Freight, Stock, and Material Movers, Hand | Light Truck Drivers | Order Clerks | Parking Attendants | Postal Service Clerks | Postal Service Mail Carriers | Retail Salespersons | Sales Representatives of Services, Except Advertising, Insurance, Financial Services, and Travel | Shipping, Receiving, and Inventory Clerks | Stockers and Order Fillers</t>
+  </si>
+  <si>
+    <t>Drive truck or other vehicle over established routes or within an established territory and sell or deliver goods, such as food products, including restaurant take-out items, or pick up or deliver items such as commercial laundry. May also take orders, collect payment, or stock merchandise at point of delivery.</t>
+  </si>
+  <si>
+    <t>Arrange merchandise and sales promotion displays or issue sales promotion materials to customers. | Collect coins from vending machines, refill machines, and remove aged merchandise. | Collect money from customers, make change, and record transactions on customer receipts. | Drive trucks to deliver such items as food, medical supplies, or newspapers. | Inform regular customers of new products or services and price changes. | Listen to and resolve customers' complaints regarding products or services. | Maintain trucks and food-dispensing equipment and clean inside of machines that dispense food or beverages. | Record sales or delivery information on daily sales or delivery record. | Review lists of dealers, customers, or station drops and load trucks. | Sell food specialties, such as sandwiches and beverages, to office workers and patrons of sports events. | Write customer orders and sales contracts according to company guidelines.</t>
+  </si>
+  <si>
+    <t>53-3032.00</t>
+  </si>
+  <si>
+    <t>Heavy and Tractor-Trailer Truck Drivers</t>
+  </si>
+  <si>
+    <t>CDL Driver (Commercial Driver's License Driver) | Driver | Line Haul Driver | Log Truck Driver | Over the Road Driver (OTR Driver) | Production Truck Driver | Road Driver | Semi Truck Driver | Tractor Trailer Driver | Truck Driver</t>
+  </si>
+  <si>
+    <t>3M Post-it App | ADP ezLaborManager | ALK Technologies PC*Miler | Computerized inventory tracking software | Eko | Evernote | Fog Line Software Truckn Pro | Inventory tracking software | MarcoSoft Quo Vadis | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft Windows | Microsoft Word | Omnitracs Performance Monitoring | PeopleNet | SAP software | TruckersHelper | YouTube | ddlsoftware.com drivers daily log program DDL</t>
+  </si>
+  <si>
+    <t>Monitoring | Critical Thinking | Speaking | Reading Comprehension</t>
+  </si>
+  <si>
+    <t>Transportation | Public Safety and Security | Customer and Personal Service | English Language | Law and Government</t>
+  </si>
+  <si>
+    <t>Far Vision | Spatial Orientation | Control Precision | Multilimb Coordination | Response Orientation | Rate Control | Reaction Time | Problem Sensitivity | Near Vision | Depth Perception | Selective Attention | Deductive Reasoning | Oral Comprehension | Written Comprehension | Hearing Sensitivity | Glare Sensitivity | Peripheral Vision | Night Vision | Static Strength | Manual Dexterity | Arm-Hand Steadiness | Time Sharing | Visualization | Flexibility of Closure | Category Flexibility | Information Ordering | Oral Expression | Speech Clarity | Speech Recognition | Auditory Attention</t>
+  </si>
+  <si>
+    <t>In an Enclosed Vehicle or Operate Enclosed Equipment | Outdoors, Exposed to All Weather Conditions | Frequency of Decision Making | Impact of Decisions on Co-workers or Company Results | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Freedom to Make Decisions | Exposed to Very Hot or Cold Temperatures | Time Pressure | Contact With Others | Spend Time Sitting | Face-to-Face Discussions with Individuals and Within Teams | Consequence of Error | Importance of Being Exact or Accurate | Telephone Conversations | Determine Tasks, Priorities and Goals | Exposed to Contaminants | Deal With External Customers or the Public in General | Health and Safety of Other Workers | Spend Time Making Repetitive Motions | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Work With or Contribute to a Work Group or Team | Importance of Repeating Same Tasks</t>
+  </si>
+  <si>
+    <t>Bus Drivers, Transit and Intercity | Bus and Truck Mechanics and Diesel Engine Specialists | Crane and Tower Operators | Dispatchers, Except Police, Fire, and Ambulance | Highway Maintenance Workers | Hoist and Winch Operators | Industrial Truck and Tractor Operators | Laborers and Freight, Stock, and Material Movers, Hand | Light Truck Drivers | Loading and Moving Machine Operators, Underground Mining | Locomotive Engineers | Operating Engineers and Other Construction Equipment Operators | Pile Driver Operators | Rail Yard Engineers, Dinkey Operators, and Hostlers | Railroad Brake, Signal, and Switch Operators and Locomotive Firers | Railroad Conductors and Yardmasters | Refuse and Recyclable Material Collectors | Shuttle Drivers and Chauffeurs | Tank Car, Truck, and Ship Loaders | Taxi Drivers</t>
+  </si>
+  <si>
+    <t>Drive a tractor-trailer combination or a truck with a capacity of at least 26,001 pounds Gross Vehicle Weight (GVW). May be required to unload truck. Requires commercial drivers' license. Includes tow truck drivers.</t>
+  </si>
+  <si>
+    <t>Check all load-related documentation for completeness and accuracy. | Check conditions of trailers after contents have been unloaded to ensure that there has been no damage. | Check vehicles to ensure that mechanical, safety, and emergency equipment is in good working order. | Collect delivery instructions from appropriate sources, verifying instructions and routes. | Couple or uncouple trailers by changing trailer jack positions, connecting or disconnecting air or electrical lines, or manipulating fifth-wheel locks. | Crank trailer landing gear up or down to safely secure vehicles. | Drive trucks to weigh stations before and after loading and along routes in compliance with state regulations. | Drive trucks with capacities greater than 13 tons, including tractor-trailer combinations, to transport and deliver products, livestock, or other materials. | Follow appropriate safety procedures for transporting dangerous goods. | Follow special cargo-related procedures, such as checking refrigeration systems for frozen foods or providing food or water for livestock. | Give directions to laborers who are packing goods and moving them onto trailers. | Inspect loads to ensure that cargo is secure. | Install or remove special equipment, such as tire chains, grader blades, plow blades, or sanders. | Inventory and inspect goods to be moved to determine quantities and conditions. | Load or unload trucks or help others with loading or unloading, using special loading-related equipment or other equipment as necessary. | Maintain logs of working hours or of vehicle service or repair status, following applicable state and federal regulations. | Maneuver trucks into loading or unloading positions, following signals from loading crew and checking that vehicle and loading equipment are properly positioned. | Obtain receipts or signatures for delivered goods and collect payment for services when required. | Operate equipment, such as truck cab computers, CB radios, phones, or global positioning systems (GPS) equipment to exchange necessary information with bases, supervisors, or other drivers. | Operate idle reduction systems or auxiliary power systems to generate power from alternative sources, such as fuel cells, to reduce idling time, to heat or cool truck cabins, or to provide power for other equipment. | Perform basic vehicle maintenance tasks, such as adding oil, fuel, or radiator fluid, performing minor repairs, or washing trucks. | Perform emergency roadside repairs, such as changing tires or installing light bulbs, tire chains, or spark plugs. | Plan or adjust routes based on changing conditions, using computer equipment, global positioning systems (GPS) equipment, or other navigation devices, to minimize fuel consumption and carbon emissions. | Read and interpret maps to determine vehicle routes. | Read bills of lading to determine assignment details. | Remove debris from loaded trailers. | Report vehicle defects, accidents, traffic violations, or damage to the vehicles. | Secure cargo for transport, using ropes, blocks, chain, binders, or covers. | Wrap and secure goods using pads, packing paper, containers, or straps.</t>
+  </si>
+  <si>
+    <t>53-3033.00</t>
+  </si>
+  <si>
+    <t>Light Truck Drivers</t>
+  </si>
+  <si>
+    <t>Bulk Delivery Driver | Delivery Driver | Driver | Light Truck Driver | Package Car Driver | Package Delivery Driver | Route Driver | Service Provider | Truck Driver | Warehouse Driver</t>
+  </si>
+  <si>
+    <t>Automatic routing software | Computerized inventory tracking software | Eko | FreightDATA | IBM Domino | Inventory management systems | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft Windows | Package location and tracking software | Recordkeeping software | Vehicle location and tracking software</t>
+  </si>
+  <si>
+    <t>Active Listening | Speaking | Monitoring | Reading Comprehension | Critical Thinking</t>
+  </si>
+  <si>
+    <t>English Language | Transportation | Customer and Personal Service</t>
+  </si>
+  <si>
+    <t>Multilimb Coordination | Far Vision | Spatial Orientation | Problem Sensitivity | Near Vision | Stamina | Trunk Strength | Static Strength | Reaction Time | Control Precision | Manual Dexterity | Deductive Reasoning | Oral Expression | Oral Comprehension | Written Comprehension | Extent Flexibility | Response Orientation | Perceptual Speed | Information Ordering | Inductive Reasoning | Speech Clarity | Speech Recognition | Depth Perception</t>
+  </si>
+  <si>
+    <t>In an Enclosed Vehicle or Operate Enclosed Equipment | Contact With Others | Importance of Being Exact or Accurate | Telephone Conversations | Time Pressure | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Outdoors, Exposed to All Weather Conditions | Deal With External Customers or the Public in General | Frequency of Decision Making | Impact of Decisions on Co-workers or Company Results | Face-to-Face Discussions with Individuals and Within Teams | Spend Time Sitting</t>
+  </si>
+  <si>
+    <t>Bus Drivers, Transit and Intercity | Cargo and Freight Agents | Couriers and Messengers | Dispatchers, Except Police, Fire, and Ambulance | Driver/Sales Workers | First-Line Supervisors of Material-Moving Machine and Vehicle Operators | Heavy and Tractor-Trailer Truck Drivers | Industrial Truck and Tractor Operators | Parking Attendants | Postal Service Clerks | Postal Service Mail Carriers | Railroad Conductors and Yardmasters | Refuse and Recyclable Material Collectors | Shipping, Receiving, and Inventory Clerks | Shuttle Drivers and Chauffeurs | Stockers and Order Fillers | Tank Car, Truck, and Ship Loaders | Taxi Drivers | Transportation Inspectors | Transportation Vehicle, Equipment and Systems Inspectors, Except Aviation</t>
+  </si>
+  <si>
+    <t>Drive a light vehicle, such as a truck or van, with a capacity of less than 26,001 pounds Gross Vehicle Weight (GVW), primarily to pick up merchandise or packages from a distribution center and deliver. May load and unload vehicle.</t>
+  </si>
+  <si>
+    <t>Drive vehicles with capacities under three tons to transport materials to and from specified destinations, such as railroad stations, plants, residences, offices, or within industrial yards. | Inspect and maintain vehicle supplies and equipment, such as gas, oil, water, tires, lights, or brakes, to ensure that vehicles are in proper working condition. | Load and unload trucks, vans, or automobiles. | Maintain records, such as vehicle logs, records of cargo, or billing statements, in accordance with regulations. | Obey traffic laws and follow established traffic and transportation procedures. | Perform emergency repairs, such as changing tires or installing light bulbs, fuses, tire chains, or spark plugs. | Present bills and receipts and collect payments for goods delivered or loaded. | Read maps and follow written or verbal geographic directions. | Report any mechanical problems encountered with vehicles. | Report delays, accidents, or other traffic and transportation situations to bases or other vehicles, using telephones or mobile two-way radios. | Turn in receipts and money received from deliveries. | Use and maintain the tools or equipment found on commercial vehicles, such as weighing or measuring devices. | Verify the contents of inventory loads against shipping papers.</t>
+  </si>
+  <si>
+    <t>53-3051.00</t>
+  </si>
+  <si>
+    <t>Bus Drivers, School</t>
+  </si>
+  <si>
+    <t>Bus Drive Coordinator | Bus Driver | CDL Bus Driver (Commercial Driver's License Bus Driver) | Public School Bus Driver | SPED Bus Driver (Special Education Bus Driver) | SPED School Bus Driver (Special Education School Bus Driver) | School Bus Driver | School Van Driver | Shuttle Bus Driver | Student Driver</t>
+  </si>
+  <si>
+    <t>AOL MapQuest | Microsoft Windows | Web browser software</t>
+  </si>
+  <si>
+    <t>Active Listening | Critical Thinking | Monitoring | Speaking | Reading Comprehension</t>
+  </si>
+  <si>
+    <t>Transportation | Public Safety and Security | Customer and Personal Service | English Language | Mechanical | Law and Government | Geography</t>
+  </si>
+  <si>
+    <t>Far Vision | Near Vision | Reaction Time | Problem Sensitivity | Depth Perception | Speech Recognition | Peripheral Vision | Multilimb Coordination | Control Precision | Auditory Attention | Oral Comprehension | Spatial Orientation | Speech Clarity | Visual Color Discrimination | Rate Control | Response Orientation | Arm-Hand Steadiness | Time Sharing | Selective Attention | Information Ordering | Oral Expression | Deductive Reasoning</t>
+  </si>
+  <si>
+    <t>In an Enclosed Vehicle or Operate Enclosed Equipment | Frequency of Decision Making | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Spend Time Sitting | Contact With Others | Face-to-Face Discussions with Individuals and Within Teams | Importance of Being Exact or Accurate | Freedom to Make Decisions | Physical Proximity | Outdoors, Exposed to All Weather Conditions | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Spend Time Making Repetitive Motions | Time Pressure | Health and Safety of Other Workers | Impact of Decisions on Co-workers or Company Results | Consequence of Error</t>
+  </si>
+  <si>
+    <t>Air Traffic Controllers | Ambulance Drivers and Attendants, Except Emergency Medical Technicians | Bus Drivers, Transit and Intercity | Commercial Pilots | Crossing Guards and Flaggers | Dispatchers, Except Police, Fire, and Ambulance | Emergency Medical Technicians | Heavy and Tractor-Trailer Truck Drivers | Light Truck Drivers | Locomotive Engineers | Parking Enforcement Workers | Passenger Attendants | Rail Yard Engineers, Dinkey Operators, and Hostlers | Railroad Brake, Signal, and Switch Operators and Locomotive Firers | Railroad Conductors and Yardmasters | School Bus Monitors | Shuttle Drivers and Chauffeurs | Subway and Streetcar Operators | Taxi Drivers | Transit and Railroad Police</t>
+  </si>
+  <si>
+    <t>Drive a school bus to transport students. Ensure adherence to safety rules. May assist students in boarding or exiting.</t>
+  </si>
+  <si>
+    <t>Check the condition of a vehicle's tires, brakes, windshield wipers, lights, oil, fuel, water, and safety equipment to ensure that everything is in working order. | Comply with traffic regulations to operate vehicles in a safe and courteous manner. | Drive gasoline, diesel, or electrically powered multi-passenger vehicles to transport students between neighborhoods, schools, and school activities. | Escort small children across roads and highways. | Follow safety rules as students board and exit buses or cross streets near bus stops. | Keep bus interiors clean for students. | Maintain knowledge of first-aid procedures. | Maintain order among students during trips to ensure safety. | Make minor repairs to vehicles. | Pick up and drop off students at regularly scheduled neighborhood locations, following strict time schedules. | Prepare and submit reports that may include the number of students or trips, hours worked, mileage, or fuel consumption. | Read maps and follow written and verbal geographic directions. | Record bus routes. | Regulate heating, lighting, and ventilation systems for student comfort. | Report any bus malfunctions or needed repairs. | Report delays, accidents, or other traffic and transportation situations, using telephones or mobile two-way radios. | Report delinquent student behaviors to school administration.</t>
+  </si>
+  <si>
+    <t>53-3052.00</t>
+  </si>
+  <si>
+    <t>Bus Drivers, Transit and Intercity</t>
+  </si>
+  <si>
+    <t>Bus Driver | Bus Operator | Charter Bus Driver | Coach Operator | Motor Coach Driver | Motor Coach Operator | Transit Bus Driver | Transit Coach Operator | Transit Driver | Transit Operator</t>
+  </si>
+  <si>
+    <t>AOL MapQuest | Microsoft MapPoint | Microsoft Windows | Web browser software</t>
+  </si>
+  <si>
+    <t>Active Listening | Critical Thinking | Speaking | Monitoring</t>
+  </si>
+  <si>
+    <t>Transportation | Customer and Personal Service | Public Safety and Security | English Language | Law and Government</t>
+  </si>
+  <si>
+    <t>Far Vision | Control Precision | Multilimb Coordination | Depth Perception | Response Orientation | Reaction Time | Spatial Orientation | Near Vision | Rate Control | Problem Sensitivity | Selective Attention | Speech Clarity | Oral Comprehension | Oral Expression | Time Sharing | Peripheral Vision | Speech Recognition | Auditory Attention | Arm-Hand Steadiness | Written Comprehension | Glare Sensitivity | Night Vision | Information Ordering | Deductive Reasoning</t>
+  </si>
+  <si>
+    <t>Spend Time Sitting | In an Enclosed Vehicle or Operate Enclosed Equipment | Contact With Others | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Frequency of Decision Making | Impact of Decisions on Co-workers or Company Results | Physical Proximity | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Face-to-Face Discussions with Individuals and Within Teams | Consequence of Error | Spend Time Making Repetitive Motions | Deal With External Customers or the Public in General | Time Pressure | Importance of Being Exact or Accurate | Freedom to Make Decisions | Dealing With Unpleasant, Angry, or Discourteous People | Exposed to Contaminants</t>
+  </si>
+  <si>
+    <t>Air Traffic Controllers | Airfield Operations Specialists | Baggage Porters and Bellhops | Bus Drivers, School | Dispatchers, Except Police, Fire, and Ambulance | Flight Attendants | Heavy and Tractor-Trailer Truck Drivers | Light Truck Drivers | Locomotive Engineers | Parking Attendants | Passenger Attendants | Rail Yard Engineers, Dinkey Operators, and Hostlers | Railroad Brake, Signal, and Switch Operators and Locomotive Firers | Railroad Conductors and Yardmasters | Reservation and Transportation Ticket Agents and Travel Clerks | School Bus Monitors | Shuttle Drivers and Chauffeurs | Subway and Streetcar Operators | Taxi Drivers | Transit and Railroad Police</t>
+  </si>
+  <si>
+    <t>Drive bus or motor coach, including regular route operations, charters, and private carriage. May assist passengers with baggage. May collect fares or tickets.</t>
+  </si>
+  <si>
+    <t>Advise passengers to be seated and orderly while on vehicles. | Announce stops to passengers. | Assist passengers, such as elderly or individuals with disabilities, on and off bus, ensure they are seated properly, help carry baggage, and answer questions about bus schedules or routes. | Collect tickets or cash fares from passengers. | Drive vehicles over specified routes or to specified destinations according to time schedules, complying with traffic regulations to ensure that passengers have a smooth and safe ride. | Handle passenger emergencies or disruptions. | Inspect vehicles and check gas, oil, and water levels prior to departure. | Load and unload baggage in baggage compartments. | Maintain cleanliness of bus or motor coach. | Park vehicles at loading areas so that passengers can board. | Read maps to plan bus routes. | Record information, such as cash receipts and ticket fares, and maintain log book. | Regulate heating, lighting, and ventilating systems for passenger comfort. | Report delays or accidents.</t>
+  </si>
+  <si>
+    <t>53-3053.00</t>
+  </si>
+  <si>
+    <t>Shuttle Drivers and Chauffeurs</t>
+  </si>
+  <si>
+    <t>Airport Shuttle Driver | Car Driver | Chauffeur | Driver | Limo Driver (Limousine Driver) | Motor Coach Driver | Shuttle Bus Driver | Shuttle Driver | Special Needs Bus Driver | Van Driver</t>
+  </si>
+  <si>
+    <t>AOL MapQuest | Actsoft Comet Tracker | Digital Dispatch | Easy Dispatch | EventHelix WebTaxi | Facebook | GPC Autocab | Global positioning system GPS software | Microsoft Excel | Microsoft Office software | Microsoft Windows | Mobile Knowledge Cabmate | PC Dispatch | Penchant Software dispatchOffice | Piccolo Software PiccoloTaxi | TSS Wireless Fleet Management Suite | TranWare Enterprise Suite | Web browser software</t>
+  </si>
+  <si>
+    <t>Active Listening | Monitoring | Critical Thinking | Speaking</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | Transportation | Public Safety and Security | English Language | Personnel and Human Resources | Administrative | Administration and Management | Education and Training | Production and Processing | Law and Government | Psychology | Economics and Accounting | Communications and Media | Mathematics | Sales and Marketing</t>
+  </si>
+  <si>
+    <t>Near Vision | Far Vision | Multilimb Coordination | Control Precision | Problem Sensitivity | Oral Comprehension | Depth Perception | Speech Clarity | Spatial Orientation | Selective Attention | Rate Control | Reaction Time | Speech Recognition | Peripheral Vision | Arm-Hand Steadiness | Time Sharing | Information Ordering | Inductive Reasoning | Deductive Reasoning | Oral Expression | Response Orientation | Perceptual Speed | Auditory Attention | Night Vision</t>
+  </si>
+  <si>
+    <t>In an Enclosed Vehicle or Operate Enclosed Equipment | Physical Proximity | Deal With External Customers or the Public in General | Outdoors, Exposed to All Weather Conditions | Contact With Others | Time Pressure | Importance of Being Exact or Accurate | Freedom to Make Decisions | Impact of Decisions on Co-workers or Company Results | Consequence of Error | Spend Time Sitting | Frequency of Decision Making | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Work With or Contribute to a Work Group or Team | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Face-to-Face Discussions with Individuals and Within Teams | Health and Safety of Other Workers</t>
+  </si>
+  <si>
+    <t>Baggage Porters and Bellhops | Bus Drivers, School | Bus Drivers, Transit and Intercity | Bus and Truck Mechanics and Diesel Engine Specialists | Couriers and Messengers | Dispatchers, Except Police, Fire, and Ambulance | Driver/Sales Workers | Heavy and Tractor-Trailer Truck Drivers | Industrial Truck and Tractor Operators | Light Truck Drivers | Loading and Moving Machine Operators, Underground Mining | Locomotive Engineers | Parking Attendants | Passenger Attendants | Rail Car Repairers | Railroad Conductors and Yardmasters | Reservation and Transportation Ticket Agents and Travel Clerks | Subway and Streetcar Operators | Taxi Drivers | Transportation Vehicle, Equipment and Systems Inspectors, Except Aviation</t>
+  </si>
+  <si>
+    <t>Drive a motor vehicle to transport passengers on a planned or scheduled basis. May collect a fare. Includes nonemergency medical transporters and hearse drivers.</t>
+  </si>
+  <si>
+    <t>Arrange to pick up particular customers or groups on a regular schedule. | Check the condition of a vehicle's tires, brakes, windshield wipers, lights, oil, fuel, water, and safety equipment to ensure that everything is in working order. | Collect fares or vouchers from passengers, and make change or issue receipts as necessary. | Communicate with dispatchers by radio, telephone, or computer to exchange information and receive requests for passenger service. | Complete accident reports when necessary. | Comply with traffic regulations to operate vehicles in a safe and courteous manner. | Drive shuttle busses, limousines, company cars, or privately owned vehicles to transport passengers. | Follow relevant safety regulations and state laws governing vehicle operation, and ensure that passengers follow safety regulations. | Maintain knowledge of first-aid procedures. | Notify dispatchers or company mechanics of vehicle problems. | Operate vehicles with specialized equipment, such as wheelchair lifts, to transport and secure passengers with special needs. | Perform errands for customers or employers, such as delivering or picking up mail and packages. | Perform minor vehicle repairs, such as cleaning spark plugs, or take vehicles to mechanics for servicing. | Perform routine vehicle maintenance, such as regulating tire pressure and adding gasoline, oil, and water. | Pick up and drop off passengers at regularly scheduled neighborhood locations, following strict time schedules. | Pick up or meet passengers according to requests, appointments, or schedules. | Prepare and submit reports that may include the number of passengers or trips, hours worked, mileage driven fuel consumed, or fares received. | Provide passengers with assistance entering and exiting vehicles, and help them with any luggage. | Provide passengers with information or advice about the local area, points of interest, hotels, or restaurants. | Read maps and follow written and verbal geographic directions. | Record vehicle routes. | Regulate heating, lighting, and ventilation systems for passenger comfort. | Report any vehicle malfunctions or needed repairs. | Report delays, accidents, or other traffic and transportation situations, using telephones or mobile two-way radios. | Test vehicle equipment, such as lights, brakes, horns, or windshield wipers, to ensure proper operation. | Vacuum and clean interiors, and wash and polish exteriors of automobiles.</t>
+  </si>
+  <si>
+    <t>53-3054.00</t>
+  </si>
+  <si>
+    <t>Taxi Drivers</t>
+  </si>
+  <si>
+    <t>Cab Driver | Taxi Cab Driver | Taxi Driver</t>
+  </si>
+  <si>
+    <t>Actsoft Comet Tracker | Digital Dispatch | Easy Dispatch | EventHelix WebTaxi | Facebook | GPC Autocab | Microsoft Excel | Microsoft Office software | Microsoft Windows | Mobile Knowledge Cabmate | PC Dispatch | Penchant Software dispatchOffice | Piccolo Software PiccoloTaxi | TSS Wireless Fleet Management Suite | TranWare Enterprise Suite</t>
+  </si>
+  <si>
+    <t>Monitoring | Active Listening | Critical Thinking | Reading Comprehension | Speaking</t>
+  </si>
+  <si>
+    <t>Transportation | Customer and Personal Service | Geography | English Language | Public Safety and Security | Law and Government | Mathematics</t>
+  </si>
+  <si>
+    <t>Manual Dexterity | Finger Dexterity | Arm-Hand Steadiness | Multilimb Coordination | Control Precision | Static Strength | Trunk Strength | Stamina | Near Vision | Far Vision | Depth Perception | Gross Body Coordination | Gross Body Equilibrium | Extent Flexibility | Reaction Time | Problem Sensitivity | Oral Comprehension | Selective Attention | Oral Expression | Speech Clarity | Spatial Orientation | Time Sharing</t>
+  </si>
+  <si>
+    <t>In an Enclosed Vehicle or Operate Enclosed Equipment | Spend Time Sitting | Exposed to Whole Body Vibration | Exposed to Contaminants | Consequence of Error | Importance of Being Exact or Accurate | Health and Safety of Other Workers | Outdoors, Exposed to All Weather Conditions | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Exposed to Very Hot or Cold Temperatures | Freedom to Make Decisions | Frequency of Decision Making | Contact With Others | Face-to-Face Discussions with Individuals and Within Teams | Telephone Conversations | Time Pressure | Deal With External Customers or the Public in General | Dealing With Unpleasant, Angry, or Discourteous People | Physical Proximity</t>
+  </si>
+  <si>
+    <t>Bus Drivers, School | Bus Drivers, Transit and Intercity | Bus and Truck Mechanics and Diesel Engine Specialists | Couriers and Messengers | Dispatchers, Except Police, Fire, and Ambulance | Driver/Sales Workers | Heavy and Tractor-Trailer Truck Drivers | Industrial Truck and Tractor Operators | Light Truck Drivers | Loading and Moving Machine Operators, Underground Mining | Locomotive Engineers | Parking Attendants | Passenger Attendants | Rail Car Repairers | Rail Yard Engineers, Dinkey Operators, and Hostlers | Railroad Brake, Signal, and Switch Operators and Locomotive Firers | Railroad Conductors and Yardmasters | Shuttle Drivers and Chauffeurs | Subway and Streetcar Operators | Transportation Vehicle, Equipment and Systems Inspectors, Except Aviation</t>
+  </si>
+  <si>
+    <t>Drive a motor vehicle to transport passengers on an unplanned basis and charge a fare, usually based on a meter.</t>
+  </si>
+  <si>
+    <t>Collect fares or vouchers from passengers, and make change or issue receipts as necessary. | Communicate with dispatchers by radio, telephone, or computer to exchange information and receive requests for passenger service. | Complete accident reports when necessary. | Determine fares based on trip distances and times, using taximeters and fee schedules, and announce fares to passengers. | Drive taxicabs or privately owned vehicles to transport passengers. | Follow relevant safety regulations and state laws governing vehicle operation, and ensure that passengers follow safety regulations. | Notify dispatchers or company mechanics of vehicle problems. | Perform minor vehicle repairs, such as cleaning spark plugs, or take vehicles to mechanics for servicing. | Perform routine vehicle maintenance, such as regulating tire pressure and adding gasoline, oil, and water. | Pick up passengers at prearranged locations, at taxi stands, or by cruising streets in high-traffic areas. | Provide passengers with assistance entering and exiting vehicles, and help them with any luggage. | Provide passengers with information or advice about the local area, points of interest, hotels, or restaurants. | Report to taxicab services or garages to receive vehicle assignments. | Test vehicle equipment, such as lights, brakes, horns, or windshield wipers, to ensure proper operation. | Turn the taximeter on when passengers enter the cab, and turn it off when they reach the final destination. | Vacuum and clean interiors and wash and polish exteriors of automobiles.</t>
+  </si>
+  <si>
+    <t>53-3099.00</t>
+  </si>
+  <si>
+    <t>Motor Vehicle Operators, All Other</t>
+  </si>
+  <si>
+    <t>Armored Vehicle Driver | Delivery Driver | Fleet Driver | Motor Vehicle Operator | Shuttle Operator | Specialty Vehicle Driver | Tow Truck Driver | Transport Driver | Utility Vehicle Driver | Vehicle Operator</t>
+  </si>
+  <si>
+    <t>Fleet management software | Transportation management software | Warehouse management system WMS | Microsoft Excel | Microsoft Word | Email software | Inventory management systems | Database software | Scheduling software | Web browser software | Microsoft Outlook | Enterprise resource planning ERP system</t>
+  </si>
+  <si>
+    <t>Transportation | Public Safety and Security | Customer and Personal Service | English Language | Geography | Mechanical | Law and Government</t>
+  </si>
+  <si>
+    <t>Manual Dexterity | Finger Dexterity | Arm-Hand Steadiness | Multilimb Coordination | Control Precision | Static Strength | Trunk Strength | Stamina | Near Vision | Far Vision | Depth Perception | Gross Body Coordination | Gross Body Equilibrium | Extent Flexibility | Reaction Time | Problem Sensitivity | Oral Comprehension | Selective Attention</t>
+  </si>
+  <si>
+    <t>In an Enclosed Vehicle or Operate Enclosed Equipment | Spend Time Sitting | Exposed to Whole Body Vibration | Exposed to Contaminants | Consequence of Error | Importance of Being Exact or Accurate | Health and Safety of Other Workers | Outdoors, Exposed to All Weather Conditions | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Exposed to Very Hot or Cold Temperatures | Freedom to Make Decisions | Frequency of Decision Making | Contact With Others | Face-to-Face Discussions with Individuals and Within Teams | Telephone Conversations | Time Pressure</t>
+  </si>
+  <si>
+    <t>Heavy and Tractor-Trailer Truck Drivers | Light Truck Drivers | Driver/Sales Workers | Shuttle Drivers and Chauffeurs | Taxi Drivers | Bus Drivers, School | Bus Drivers, Transit and Intercity | Ambulance Drivers and Attendants, Except Emergency Medical Technicians | Industrial Truck and Tractor Operators | Parking Attendants | Automotive and Watercraft Service Attendants | Laborers and Freight, Stock, and Material Movers, Hand | Refuse and Recyclable Material Collectors | Couriers and Messengers | Cargo and Freight Agents | Dispatchers, Except Police, Fire, and Ambulance | Transportation Inspectors | First-Line Supervisors of Transportation Workers, All Other | Transportation, Storage, and Distribution Managers | Crane and Tower Operators</t>
+  </si>
+  <si>
+    <t>All motor vehicle operators not listed separately.</t>
+  </si>
+  <si>
+    <t>Operate motor vehicles in roles not classified separately. | Drive vehicles safely over assigned routes in varied traffic and weather conditions. | Inspect vehicles before and after trips and report defects. | Load, secure, and unload cargo, equipment, or passengers. | Follow traffic laws, company policies, and route instructions. | Maintain logs of trips, mileage, fuel, hours, and deliveries. | Communicate with dispatchers regarding schedules, delays, and problems. | Perform minor maintenance such as checking fluids, tires, and lights. | Collect payments, obtain signatures, and process delivery documentation. | Assist passengers or customers with loading, boarding, and special needs. | Respond to breakdowns, accidents, and emergencies according to procedures. | Keep vehicles clean, fueled, and properly equipped. | Plan routes to optimize time, fuel, and service commitments. | Comply with licensing, medical certification, and safety training requirements.</t>
+  </si>
+  <si>
+    <t>53-4011.00</t>
+  </si>
+  <si>
+    <t>Locomotive Engineers</t>
+  </si>
+  <si>
+    <t>Locomotive Engineer | Passenger Locomotive Engineer | Railroad Engineer | Through Freight Engineer | Train Engineer | Trainmaster | Transportation Specialist</t>
+  </si>
+  <si>
+    <t>Electronic train management systems ETMS | Microsoft Excel | Microsoft Word | Route mapping software | Time tracking software</t>
+  </si>
+  <si>
+    <t>Active Listening | Monitoring | Speaking | Critical Thinking | Reading Comprehension | Active Learning | Writing</t>
+  </si>
+  <si>
+    <t>Transportation | Public Safety and Security | English Language | Education and Training | Customer and Personal Service</t>
+  </si>
+  <si>
+    <t>Far Vision | Selective Attention | Control Precision | Response Orientation | Near Vision | Depth Perception | Problem Sensitivity | Reaction Time | Perceptual Speed | Multilimb Coordination | Oral Comprehension | Oral Expression | Rate Control | Auditory Attention | Flexibility of Closure | Information Ordering | Inductive Reasoning | Manual Dexterity | Speech Recognition | Hearing Sensitivity | Written Comprehension | Deductive Reasoning | Time Sharing | Speech Clarity | Arm-Hand Steadiness | Spatial Orientation | Written Expression | Glare Sensitivity | Visual Color Discrimination | Finger Dexterity | Visualization</t>
+  </si>
+  <si>
+    <t>Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Face-to-Face Discussions with Individuals and Within Teams | Health and Safety of Other Workers | Work With or Contribute to a Work Group or Team | In an Enclosed Vehicle or Operate Enclosed Equipment | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Contact With Others | Importance of Being Exact or Accurate | Telephone Conversations | Exposed to Very Hot or Cold Temperatures | Outdoors, Exposed to All Weather Conditions | Time Pressure | Spend Time Sitting | Freedom to Make Decisions | Frequency of Decision Making | Exposed to Contaminants | Coordinate or Lead Others in Accomplishing Work Activities | Consequence of Error | Exposed to Hazardous Equipment | Impact of Decisions on Co-workers or Company Results | Exposed to Whole Body Vibration | Spend Time Making Repetitive Motions | Determine Tasks, Priorities and Goals | Work Outcomes and Results of Other Workers | Exposed to Extremely Bright or Inadequate Lighting Conditions | Importance of Repeating Same Tasks</t>
+  </si>
+  <si>
+    <t>Air Traffic Controllers | Aviation Inspectors | Bus and Truck Mechanics and Diesel Engine Specialists | Dispatchers, Except Police, Fire, and Ambulance | Heavy and Tractor-Trailer Truck Drivers | Hoist and Winch Operators | Industrial Truck and Tractor Operators | Operating Engineers and Other Construction Equipment Operators | Power Distributors and Dispatchers | Rail Yard Engineers, Dinkey Operators, and Hostlers | Railroad Brake, Signal, and Switch Operators and Locomotive Firers | Railroad Conductors and Yardmasters | Ship Engineers | Signal and Track Switch Repairers | Stationary Engineers and Boiler Operators | Subway and Streetcar Operators | Tank Car, Truck, and Ship Loaders | Traffic Technicians | Transportation Inspectors | Transportation Vehicle, Equipment and Systems Inspectors, Except Aviation</t>
+  </si>
+  <si>
+    <t>Drive electric, diesel-electric, steam, or gas-turbine-electric locomotives to transport passengers or freight. Interpret train orders, electronic or manual signals, and railroad rules and regulations.</t>
+  </si>
+  <si>
+    <t>Call out train signals to assistants to verify meanings. | Check to ensure that brake examination tests are conducted at shunting stations. | Check to ensure that documentation, such as procedure manuals or logbooks, are in the driver's cab and available for staff use. | Confer with conductors or traffic control center personnel via radiophones to issue or receive information concerning stops, delays, or oncoming trains. | Inspect locomotives after runs to detect damaged or defective equipment. | Inspect locomotives to verify adequate fuel, sand, water, or other supplies before each run or to check for mechanical problems. | Interpret train orders, signals, or railroad rules and regulations that govern the operation of locomotives. | Monitor gauges or meters that measure speed, amperage, battery charge, or air pressure in brake lines or in main reservoirs. | Monitor train loading procedures to ensure that freight or rolling stock are loaded or unloaded without damage. | Observe tracks to detect obstructions. | Operate locomotives to transport freight or passengers between stations or to assemble or disassemble trains within rail yards. | Prepare reports regarding any problems encountered, such as accidents, signaling problems, unscheduled stops, or delays. | Receive starting signals from conductors and use controls such as throttles or air brakes to drive electric, diesel-electric, steam, or gas turbine-electric locomotives. | Respond to emergency conditions or breakdowns, following applicable safety procedures and rules.</t>
+  </si>
+  <si>
+    <t>53-4013.00</t>
+  </si>
+  <si>
+    <t>Rail Yard Engineers, Dinkey Operators, and Hostlers</t>
+  </si>
+  <si>
+    <t>Carman | Engineer | Hostler | Rail Yard Engineer | Railcar Switcher | Railroad Engineer | Switchman | Yard Engineer</t>
+  </si>
+  <si>
+    <t>Positive train control PTC systems | RailComm DocYard | Railcar inspection management software | Railyard inventory software | Railyard management software RMS | Softrail AEI Automatic Yard Tracking System | Softrail AEI Rail &amp; Road Manager | Web browser software</t>
+  </si>
+  <si>
+    <t>Monitoring | Speaking | Active Listening | Critical Thinking | Reading Comprehension | Active Learning</t>
+  </si>
+  <si>
+    <t>Transportation | Public Safety and Security | Administration and Management | Mechanical | English Language | Customer and Personal Service</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Problem Sensitivity | Far Vision | Control Precision | Reaction Time | Response Orientation | Near Vision | Visual Color Discrimination | Oral Expression | Speech Clarity | Selective Attention | Rate Control | Manual Dexterity | Arm-Hand Steadiness | Deductive Reasoning | Multilimb Coordination | Depth Perception | Speech Recognition | Auditory Attention | Trunk Strength | Visualization | Perceptual Speed | Flexibility of Closure | Information Ordering | Time Sharing | Spatial Orientation | Inductive Reasoning | Written Comprehension | Finger Dexterity | Static Strength</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Work With or Contribute to a Work Group or Team | Health and Safety of Other Workers | Face-to-Face Discussions with Individuals and Within Teams | Outdoors, Exposed to All Weather Conditions | Consequence of Error | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Contact With Others | Exposed to Contaminants | Impact of Decisions on Co-workers or Company Results | Coordinate or Lead Others in Accomplishing Work Activities | Exposed to Very Hot or Cold Temperatures | Work Outcomes and Results of Other Workers | Freedom to Make Decisions | In an Enclosed Vehicle or Operate Enclosed Equipment | Spend Time Making Repetitive Motions | Spend Time Sitting | Indoors, Not Environmentally Controlled | Importance of Being Exact or Accurate | Frequency of Decision Making</t>
+  </si>
+  <si>
+    <t>Bus and Truck Mechanics and Diesel Engine Specialists | Crane and Tower Operators | Dispatchers, Except Police, Fire, and Ambulance | Excavating and Loading Machine and Dragline Operators, Surface Mining | Heavy and Tractor-Trailer Truck Drivers | Hoist and Winch Operators | Industrial Truck and Tractor Operators | Laborers and Freight, Stock, and Material Movers, Hand | Loading and Moving Machine Operators, Underground Mining | Locomotive Engineers | Mobile Heavy Equipment Mechanics, Except Engines | Operating Engineers and Other Construction Equipment Operators | Rail Car Repairers | Railroad Brake, Signal, and Switch Operators and Locomotive Firers | Railroad Conductors and Yardmasters | Ship Engineers | Signal and Track Switch Repairers | Subway and Streetcar Operators | Tank Car, Truck, and Ship Loaders | Transportation Vehicle, Equipment and Systems Inspectors, Except Aviation</t>
+  </si>
+  <si>
+    <t>Drive switching or other locomotive or dinkey engines within railroad yard, industrial plant, quarry, construction project, or similar location.</t>
+  </si>
+  <si>
+    <t>Apply and release hand brakes. | Confer with conductors and other workers via radiotelephones or computers to exchange switching information. | Couple and uncouple air hoses and electrical connections between cars. | Drive engines within railroad yards or other establishments to couple, uncouple, or switch railroad cars. | Drive locomotives to and from various stations in roundhouses to have locomotives cleaned, serviced, repaired, or supplied. | Inspect engines before and after use to ensure proper operation. | Inspect the condition of stationary trains, rolling stock, and equipment. | Inspect track for defects such as broken rails and switch malfunctions. | Observe and respond to wayside and cab signals, including color light signals, position signals, torpedoes, flags, and hot box detectors. | Observe water levels and oil, air, and steam pressure gauges to ensure proper operation of equipment. | Operate flatcars equipped with derricks or railcars to transport personnel or equipment. | Operate track switches, derails, automatic switches, and retarders to change routing of train or cars. | Perform routine repair and maintenance duties. | Provide assistance in aligning drawbars, using available equipment to lift, pull, or push on the drawbars. | Provide assistance in the installation or repair of rails and ties. | Pull knuckles to open them for coupling. | Read switching instructions and daily car schedules to determine work to be performed, or receive orders from yard conductors. | Receive, relay, and act upon instructions and inquiries from train operations and customer service center personnel. | Record numbers of cars available, numbers of cars sent to repair stations, and types of service needed. | Report arrival and departure times, train delays, work order completion, and time on duty. | Ride on moving cars by holding onto grab irons and standing on ladder steps. | Signal crew members for movement of engines or trains, using lanterns, hand signals, radios, or telephones. | Spot cars for loading and unloading at customer locations.</t>
+  </si>
+  <si>
+    <t>53-4022.00</t>
+  </si>
+  <si>
+    <t>Railroad Brake, Signal, and Switch Operators and Locomotive Firers</t>
+  </si>
+  <si>
+    <t>Brakeman | Carman | Fireman | Locomotive Switch Operator | Railroad Brakeman | Railroad Switchman | Terminal Carman | Trainman</t>
+  </si>
+  <si>
+    <t>Electronic train management system software | Electronic train management systems ETMS | Google Android | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Route mapping software | Time tracking software</t>
+  </si>
+  <si>
+    <t>Monitoring | Critical Thinking | Active Listening | Reading Comprehension</t>
+  </si>
+  <si>
+    <t>Transportation | Public Safety and Security | Mechanical | English Language</t>
+  </si>
+  <si>
+    <t>Control Precision | Near Vision | Arm-Hand Steadiness | Far Vision | Oral Comprehension | Reaction Time | Perceptual Speed | Problem Sensitivity | Multilimb Coordination | Manual Dexterity | Speech Recognition | Rate Control | Response Orientation | Speech Clarity | Written Comprehension | Oral Expression | Deductive Reasoning | Inductive Reasoning | Information Ordering | Auditory Attention | Visual Color Discrimination | Flexibility of Closure | Finger Dexterity | Time Sharing | Selective Attention | Visualization | Hearing Sensitivity | Trunk Strength</t>
+  </si>
+  <si>
+    <t>Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Exposed to Contaminants | Outdoors, Exposed to All Weather Conditions | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Face-to-Face Discussions with Individuals and Within Teams | In an Enclosed Vehicle or Operate Enclosed Equipment | Consequence of Error | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Health and Safety of Other Workers | Exposed to Hazardous Equipment | Work With or Contribute to a Work Group or Team | Exposed to Extremely Bright or Inadequate Lighting Conditions | Freedom to Make Decisions | Impact of Decisions on Co-workers or Company Results | Contact With Others | Time Pressure | Frequency of Decision Making | Exposed to Whole Body Vibration | Telephone Conversations | Importance of Being Exact or Accurate | Exposed to Very Hot or Cold Temperatures | Exposed to Hazardous Conditions | Spend Time Making Repetitive Motions | Spend Time Sitting | Importance of Repeating Same Tasks | Determine Tasks, Priorities and Goals | Work Outcomes and Results of Other Workers | Coordinate or Lead Others in Accomplishing Work Activities</t>
+  </si>
+  <si>
+    <t>Bus and Truck Mechanics and Diesel Engine Specialists | Conveyor Operators and Tenders | Crane and Tower Operators | Electrical Power-Line Installers and Repairers | Heavy and Tractor-Trailer Truck Drivers | Hoist and Winch Operators | Industrial Truck and Tractor Operators | Loading and Moving Machine Operators, Underground Mining | Locomotive Engineers | Mobile Heavy Equipment Mechanics, Except Engines | Operating Engineers and Other Construction Equipment Operators | Rail Car Repairers | Rail Yard Engineers, Dinkey Operators, and Hostlers | Railroad Conductors and Yardmasters | Sailors and Marine Oilers | Ship Engineers | Signal and Track Switch Repairers | Subway and Streetcar Operators | Tank Car, Truck, and Ship Loaders | Transportation Vehicle, Equipment and Systems Inspectors, Except Aviation</t>
+  </si>
+  <si>
+    <t>Operate or monitor railroad track switches or locomotive instruments. May couple or uncouple rolling stock to make up or break up trains. Watch for and relay traffic signals. May inspect couplings, air hoses, journal boxes, and hand brakes. May watch for dragging equipment or obstacles on rights-of-way.</t>
+  </si>
+  <si>
+    <t>Check to see that trains are equipped with supplies such as fuel, water, and sand. | Climb ladders to tops of cars to set brakes. | Conduct brake tests to determine the condition of brakes on trains. | Connect air hoses to cars, using wrenches. | Inspect couplings, air hoses, journal boxes, and handbrakes to ensure that they are securely fastened and functioning properly. | Inspect locomotives to detect damaged or worn parts. | Inspect tracks, cars, and engines for defects and to determine service needs, sending engines and cars for repairs as necessary. | Make minor repairs to couplings, air hoses, and journal boxes, using hand tools. | Monitor oil, temperature, and pressure gauges on dashboards to determine if engines are operating safely and efficiently. | Monitor trains as they go around curves to detect dragging equipment and smoking journal boxes. | Observe signals from other crew members so that work activities can be coordinated. | Observe tracks from left sides of locomotives to detect obstructions on tracks. | Observe train signals along routes and verify their meanings for engineers. | Operate and drive locomotives, diesel switch engines, dinkey engines, flatcars, and railcars in train yards and at industrial sites. | Operate locomotives in emergency situations. | Provide passengers with assistance entering and exiting trains. | Pull or push track switches to reroute cars. | Raise levers to couple and uncouple cars for makeup and breakup of trains. | Receive oral or written instructions from yardmasters or yard conductors indicating track assignments and cars to be switched. | Record numbers of cars available, numbers of cars sent to repair stations, and types of service needed. | Refuel and lubricate engines. | Ride atop cars that have been shunted, and turn handwheels to control speeds or stop cars at specified positions. | Set flares, flags, lanterns, or torpedoes in front and at rear of trains during emergency stops to warn oncoming trains. | Signal locomotive engineers to start or stop trains when coupling or uncoupling cars, using hand signals, lanterns, or radio communication. | Signal other workers to set brakes and to throw track switches when switching cars from trains to way stations. | Start diesel engines to warm engines before runs.</t>
+  </si>
+  <si>
+    <t>53-4031.00</t>
+  </si>
+  <si>
+    <t>Railroad Conductors and Yardmasters</t>
+  </si>
+  <si>
+    <t>Conductor | Freight Conductor | Railroad Conductor | Train Master | Trainman | Yardmaster</t>
+  </si>
+  <si>
+    <t>Automated equipment identification AEI software | Bourque Data Systems YardMaster | Freight reservation software | Inventory tracking software | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Positive train control PTC systems | RailComm DocYard | SAIC government services and IT support software | Softrail AEI Automatic Yard Tracking System | Softrail AEI Rail &amp; Road Manager</t>
+  </si>
+  <si>
+    <t>Speaking | Monitoring | Critical Thinking | Active Listening | Reading Comprehension | Active Learning | Writing</t>
+  </si>
+  <si>
+    <t>Public Safety and Security | Transportation | English Language | Education and Training | Law and Government</t>
+  </si>
+  <si>
+    <t>Oral Expression | Problem Sensitivity | Oral Comprehension | Far Vision | Speech Recognition | Speech Clarity | Near Vision | Information Ordering | Inductive Reasoning | Deductive Reasoning | Written Comprehension | Reaction Time | Auditory Attention | Control Precision | Selective Attention | Visualization | Perceptual Speed | Category Flexibility | Written Expression | Flexibility of Closure | Depth Perception | Time Sharing</t>
+  </si>
+  <si>
+    <t>Face-to-Face Discussions with Individuals and Within Teams | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Outdoors, Exposed to All Weather Conditions | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Contact With Others | Work With or Contribute to a Work Group or Team | In an Enclosed Vehicle or Operate Enclosed Equipment | Frequency of Decision Making | Exposed to Contaminants | Telephone Conversations | Consequence of Error | Health and Safety of Other Workers | Exposed to Very Hot or Cold Temperatures | Importance of Being Exact or Accurate | Impact of Decisions on Co-workers or Company Results | Coordinate or Lead Others in Accomplishing Work Activities | Spend Time Sitting | Freedom to Make Decisions | Exposed to Extremely Bright or Inadequate Lighting Conditions | Work Outcomes and Results of Other Workers | Exposed to Hazardous Equipment | Importance of Repeating Same Tasks | Physical Proximity</t>
+  </si>
+  <si>
+    <t>Air Traffic Controllers | Aircraft Cargo Handling Supervisors | Airfield Operations Specialists | Bus Drivers, Transit and Intercity | Dispatchers, Except Police, Fire, and Ambulance | First-Line Supervisors of Material-Moving Machine and Vehicle Operators | First-Line Supervisors of Passenger Attendants | Heavy and Tractor-Trailer Truck Drivers | Highway Maintenance Workers | Light Truck Drivers | Locomotive Engineers | Power Distributors and Dispatchers | Rail Yard Engineers, Dinkey Operators, and Hostlers | Railroad Brake, Signal, and Switch Operators and Locomotive Firers | Signal and Track Switch Repairers | Subway and Streetcar Operators | Traffic Technicians | Transit and Railroad Police | Transportation Inspectors | Transportation Vehicle, Equipment and Systems Inspectors, Except Aviation</t>
+  </si>
+  <si>
+    <t>Coordinate activities of switch-engine crew within railroad yard, industrial plant, or similar location. Conductors coordinate activities of train crew on passenger or freight trains. Yardmasters review train schedules and switching orders and coordinate activities of workers engaged in railroad traffic operations, such as the makeup or breakup of trains and yard switching.</t>
+  </si>
+  <si>
+    <t>Arrange for the removal of defective cars from trains at stations or stops. | Confer with engineers regarding train routes, timetables, and cargoes, and to discuss alternative routes when there are rail defects or obstructions. | Confirm routes and destination information for freight cars. | Direct and instruct workers engaged in yard activities, such as switching tracks, coupling and uncoupling cars, and routing inbound and outbound traffic. | Direct engineers to move cars to fit planned train configurations, combining or separating cars to make up or break up trains. | Document and prepare reports of accidents, unscheduled stops, or delays. | Inspect each car periodically during runs. | Inspect freight cars for compliance with sealing procedures, and record car numbers and seal numbers. | Instruct workers to set warning signals in front and at rear of trains during emergency stops. | Keep records of the contents and destination of each train car, and make sure that cars are added or removed at proper points on routes. | Observe yard traffic to determine tracks available to accommodate inbound and outbound traffic. | Operate controls to activate track switches and traffic signals. | Receive information regarding train or rail problems from dispatchers or from electronic monitoring devices. | Receive instructions from dispatchers regarding trains' routes, timetables, and cargoes. | Record departure and arrival times, messages, tickets and revenue collected, and passenger accommodations and destinations. | Review schedules, switching orders, way bills, and shipping records to obtain cargo loading and unloading information and to plan work. | Signal engineers to begin train runs, stop trains, or change speed, using telecommunications equipment or hand signals. | Supervise and coordinate crew activities to transport freight and passengers and to provide boarding, porter, maid, and meal services to passengers. | Supervise workers in the inspection and maintenance of mechanical equipment to ensure efficient and safe train operation. | Verify accuracy of timekeeping instruments with engineers to ensure trains depart on time.</t>
+  </si>
+  <si>
+    <t>53-4041.00</t>
+  </si>
+  <si>
+    <t>Subway and Streetcar Operators</t>
+  </si>
+  <si>
+    <t>Combined Rail Operator | Light Rail Operator | Light Rail Train Operator | Light Rail Vehicle Operator (LRV Operator) | Rail Operator | Rapid Transit Operator (RTO) | Streetcar Operator | Train Operator | Transit Operator | Trolley Operator</t>
+  </si>
+  <si>
+    <t>Microsoft Office software</t>
+  </si>
+  <si>
+    <t>Active Listening | Speaking | Monitoring | Reading Comprehension | Active Learning | Critical Thinking</t>
+  </si>
+  <si>
+    <t>Transportation | Public Safety and Security | Customer and Personal Service | English Language</t>
+  </si>
+  <si>
+    <t>Control Precision | Multilimb Coordination | Reaction Time | Rate Control | Near Vision | Far Vision | Auditory Attention | Problem Sensitivity | Response Orientation | Selective Attention | Arm-Hand Steadiness | Deductive Reasoning | Perceptual Speed | Oral Expression | Manual Dexterity | Flexibility of Closure | Depth Perception | Oral Comprehension | Speech Clarity | Information Ordering | Time Sharing | Category Flexibility | Inductive Reasoning | Written Comprehension | Visual Color Discrimination | Finger Dexterity | Speech Recognition | Hearing Sensitivity</t>
+  </si>
+  <si>
+    <t>In an Enclosed Vehicle or Operate Enclosed Equipment | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Importance of Being Exact or Accurate | Contact With Others | Spend Time Making Repetitive Motions | Deal With External Customers or the Public in General | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Frequency of Decision Making | Dealing With Unpleasant, Angry, or Discourteous People | Spend Time Sitting | Health and Safety of Other Workers | Impact of Decisions on Co-workers or Company Results | Consequence of Error | Outdoors, Exposed to All Weather Conditions | Importance of Repeating Same Tasks | Work With or Contribute to a Work Group or Team | Exposed to Contaminants | Time Pressure | Exposed to Hazardous Conditions | Pace Determined by Speed of Equipment | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Exposed to Very Hot or Cold Temperatures | Exposed to Extremely Bright or Inadequate Lighting Conditions</t>
+  </si>
+  <si>
+    <t>Air Traffic Controllers | Airfield Operations Specialists | Bus Drivers, Transit and Intercity | Bus and Truck Mechanics and Diesel Engine Specialists | Commercial Pilots | Crossing Guards and Flaggers | Dispatchers, Except Police, Fire, and Ambulance | Heavy and Tractor-Trailer Truck Drivers | Light Truck Drivers | Locomotive Engineers | Parking Attendants | Passenger Attendants | Rail Yard Engineers, Dinkey Operators, and Hostlers | Railroad Brake, Signal, and Switch Operators and Locomotive Firers | Railroad Conductors and Yardmasters | Shuttle Drivers and Chauffeurs | Taxi Drivers | Traffic Technicians | Transit and Railroad Police | Transportation Vehicle, Equipment and Systems Inspectors, Except Aviation</t>
+  </si>
+  <si>
+    <t>Operate subway or elevated suburban trains with no separate locomotive, or electric-powered streetcar, to transport passengers. May handle fares.</t>
+  </si>
+  <si>
+    <t>Attend meetings on driver and passenger safety to learn ways in which job performance might be affected. | Complete reports, including shift summaries and incident or accident reports. | Direct emergency evacuation procedures. | Drive and control rail-guided public transportation, such as subways, elevated trains, and electric-powered streetcars, trams, or trolleys, to transport passengers. | Greet passengers, provide information, and answer questions concerning fares, schedules, transfers, and routings. | Make announcements to passengers, such as notifications of upcoming stops or schedule delays. | Monitor lights indicating obstructions or other trains ahead and watch for car and truck traffic at crossings to stay alert to potential hazards. | Operate controls to open and close transit vehicle doors. | Regulate vehicle speed and the time spent at each stop to maintain schedules. | Report delays, mechanical problems, and emergencies to supervisors or dispatchers, using radios.</t>
+  </si>
+  <si>
+    <t>53-4099.00</t>
+  </si>
+  <si>
+    <t>Rail Transportation Workers, All Other</t>
+  </si>
+  <si>
+    <t>Rail Operations Worker | Rail Transportation Worker | Rail Worker | Railroad Worker | Switch Operator | Track Worker | Train Crew Member | Yard Worker | Rail Service Worker | Terminal Rail Worker</t>
+  </si>
+  <si>
+    <t>Fleet management software | Transportation management software | Warehouse management system WMS | Microsoft Excel | Microsoft Word | Email software | Inventory management systems | Database software | Scheduling software | Web browser software | Microsoft Outlook | Enterprise resource planning ERP system | Radar software</t>
+  </si>
+  <si>
+    <t>Transportation | Public Safety and Security | Mechanical | English Language | Telecommunications | Geography | Mathematics</t>
+  </si>
+  <si>
+    <t>In an Enclosed Vehicle or Operate Enclosed Equipment | Spend Time Sitting | Exposed to Whole Body Vibration | Exposed to Contaminants | Consequence of Error | Importance of Being Exact or Accurate | Health and Safety of Other Workers | Outdoors, Exposed to All Weather Conditions | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Exposed to Very Hot or Cold Temperatures | Freedom to Make Decisions | Frequency of Decision Making | Contact With Others | Face-to-Face Discussions with Individuals and Within Teams | Telephone Conversations | Time Pressure | Spend Time Standing | Spend Time Walking or Running | Exposed to Hazardous Equipment | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets</t>
+  </si>
+  <si>
+    <t>Locomotive Engineers | Railroad Conductors and Yardmasters | Rail Yard Engineers, Dinkey Operators, and Hostlers | Railroad Brake, Signal, and Switch Operators and Locomotive Firers | Subway and Streetcar Operators | Signal and Track Switch Repairers | Rail Car Repairers | Rail-Track Laying and Maintenance Equipment Operators | Transit and Railroad Police | Transportation Inspectors | Transportation Vehicle, Equipment and Systems Inspectors, Except Aviation | Dispatchers, Except Police, Fire, and Ambulance | Cargo and Freight Agents | Industrial Truck and Tractor Operators | Crane and Tower Operators | Conveyor Operators and Tenders | First-Line Supervisors of Transportation Workers, All Other | Transportation, Storage, and Distribution Managers | Laborers and Freight, Stock, and Material Movers, Hand | Bridge and Lock Tenders</t>
+  </si>
+  <si>
+    <t>All rail transportation workers not listed separately.</t>
+  </si>
+  <si>
+    <t>Perform rail transportation work in roles not classified separately. | Couple and uncouple rail cars and set hand brakes and air hoses. | Operate track switches to route cars and locomotives within yards. | Signal engineers using radio, hand signals, and lanterns. | Inspect rail cars, couplings, brakes, and running gear for defects. | Ride cars during switching operations and control movement speed. | Verify car numbers, contents, seals, and shipping documentation. | Assist with the assembly and breakdown of trains in classification yards. | Follow railroad operating rules, signals, and safety regulations. | Report equipment defects, track hazards, and unsafe conditions. | Maintain records of car movements, switching lists, and work performed. | Assist in securing loads, blocking, and bracing freight. | Respond to emergencies, derailments, and service interruptions. | Perform minor servicing of rail equipment and yard facilities.</t>
+  </si>
+  <si>
+    <t>53-5011.00</t>
+  </si>
+  <si>
+    <t>Sailors and Marine Oilers</t>
+  </si>
+  <si>
+    <t>Able Bodied Seaman (AB Seaman) | Able Bodied Watchman (AB Watchman) | Able Seaman | Boat Crew Deck Hand | Bosun | Deck Hand | Deckhand | Deckhand Engineer | Oiler | Tankerman</t>
+  </si>
+  <si>
+    <t>Computerized maintenance management system CMMS | KNMI TurboWin | Kongsberg Maritime K-Log Deck Logbook | Log book software | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Windows | Microsoft Word</t>
+  </si>
+  <si>
+    <t>Monitoring | Active Listening | Critical Thinking | Speaking</t>
+  </si>
+  <si>
+    <t>Public Safety and Security | Transportation | Mechanical</t>
+  </si>
+  <si>
+    <t>Far Vision | Control Precision | Oral Comprehension | Problem Sensitivity | Perceptual Speed | Depth Perception | Auditory Attention | Arm-Hand Steadiness | Multilimb Coordination | Manual Dexterity | Visual Color Discrimination | Selective Attention | Near Vision | Flexibility of Closure | Hearing Sensitivity | Speech Clarity | Speech Recognition | Gross Body Equilibrium | Extent Flexibility | Static Strength | Reaction Time | Visualization | Information Ordering | Inductive Reasoning | Deductive Reasoning | Oral Expression | Stamina | Trunk Strength | Rate Control | Finger Dexterity | Time Sharing | Spatial Orientation | Category Flexibility | Written Comprehension | Sound Localization | Glare Sensitivity</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Outdoors, Exposed to All Weather Conditions | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Exposed to Very Hot or Cold Temperatures | Exposed to Contaminants | Health and Safety of Other Workers | Contact With Others | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Face-to-Face Discussions with Individuals and Within Teams | Importance of Being Exact or Accurate | Consequence of Error | Spend Time Standing | Work Outcomes and Results of Other Workers | Work With or Contribute to a Work Group or Team | Time Pressure | Spend Time Bending or Twisting Your Body | Exposed to Minor Burns, Cuts, Bites, or Stings | Physical Proximity | Spend Time Walking or Running | Determine Tasks, Priorities and Goals | Exposed to Hazardous Equipment | Spend Time Making Repetitive Motions | Impact of Decisions on Co-workers or Company Results | Frequency of Decision Making | Exposed to Cramped Work Space, Awkward Positions | Coordinate or Lead Others in Accomplishing Work Activities</t>
+  </si>
+  <si>
+    <t>Bus and Truck Mechanics and Diesel Engine Specialists | Captains, Mates, and Pilots of Water Vessels | Commercial Divers | Crane and Tower Operators | Dredge Operators | Fishing and Hunting Workers | Helpers--Extraction Workers | Hoist and Winch Operators | Industrial Truck and Tractor Operators | Maintenance Workers, Machinery | Marine Engineers and Naval Architects | Motorboat Mechanics and Service Technicians | Motorboat Operators | Operating Engineers and Other Construction Equipment Operators | Railroad Brake, Signal, and Switch Operators and Locomotive Firers | Riggers | Rotary Drill Operators, Oil and Gas | Roustabouts, Oil and Gas | Ship Engineers | Tank Car, Truck, and Ship Loaders</t>
+  </si>
+  <si>
+    <t>Stand watch to look for obstructions in path of vessel, measure water depth, turn wheel on bridge, or use emergency equipment as directed by captain, mate, or pilot. Break out, rig, overhaul, and store cargo-handling gear, stationary rigging, and running gear. Perform a variety of maintenance tasks to preserve the painted surface of the ship and to maintain line and ship equipment. Must hold government-issued certification and tankerman certification when working aboard liquid-carrying vessels. Includes able seamen and ordinary seamen.</t>
+  </si>
+  <si>
+    <t>Attach hoses and operate pumps to transfer substances to and from liquid cargo tanks. | Break out, rig, and stow cargo-handling gear, stationary rigging, or running gear. | Chip and clean rust spots on decks, superstructures, or sides of ships, using wire brushes and hand or air chipping machines. | Clean and polish wood trim, brass, or other metal parts. | Examine machinery to verify specified pressures or lubricant flows. | Give directions to crew members engaged in cleaning wheelhouses or quarterdecks. | Handle lines to moor vessels to wharfs, to tie up vessels to other vessels, or to rig towing lines. | Load or unload materials, vehicles, or passengers from vessels. | Lower and man lifeboats when emergencies occur. | Lubricate machinery, equipment, or engine parts, such as gears, shafts, or bearings. | Maintain a ship's engines under the direction of the ship's engineering officers. | Maintain government-issued certifications, as required. | Measure depth of water in shallow or unfamiliar waters, using leadlines, and telephone or shout depth information to vessel bridges. | Operate, maintain, or repair ship equipment, such as winches, cranes, derricks, or weapons system. | Overhaul lifeboats or lifeboat gear and lower or raise lifeboats with winches or falls. | Paint or varnish decks, superstructures, lifeboats, or sides of ships. | Participate in shore patrols. | Provide engineers with assistance in repairing or adjusting machinery. | Read pressure and temperature gauges or displays and record data in engineering logs. | Record data in ships' logs, such as weather conditions or distances traveled. | Relay specified signals to other ships, using visual signaling devices, such as blinker lights or semaphores. | Splice and repair ropes, wire cables, or cordage, using marlinespikes, wire cutters, twine, and hand tools. | Stand by wheels when ships are on automatic pilot, and verify accuracy of courses, using magnetic compasses. | Stand gangway watches to prevent unauthorized persons from boarding ships while in port. | Stand watch in ships' bows or bridge wings to look for obstructions in a ship's path or to locate navigational aids, such as buoys or lighthouses. | Steer ships under the direction of commanders or navigating officers or direct helmsmen to steer, following designated courses. | Sweep, mop, and wash down decks to remove oil, dirt, and debris, using brooms, mops, brushes, and hoses. | Tie barges together into tow units for tugboats to handle, inspecting barges periodically during voyages and disconnecting them when destinations are reached.</t>
+  </si>
+  <si>
+    <t>53-5021.00</t>
+  </si>
+  <si>
+    <t>Captains, Mates, and Pilots of Water Vessels</t>
+  </si>
+  <si>
+    <t>Boat Captain | Captain | Ferry Boat Captain | First Mate | Harbor Pilot | Mate | River Pilot | Ship Pilot | Tugboat Captain | Vessel Master</t>
+  </si>
+  <si>
+    <t>Apple macOS | Autodesk Revit | Computerized maintenance management system CMMS | FURUNO navigational chart software | Groundwater modeling system GMS | JRC navigation software | Jeppesen Marine Nobeltec Admiral | KNMI TurboWin | Log book software | Maptech The CAPN | Microsoft Excel | Microsoft Office Outlook | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Navigational chart software | SHIPNEXT</t>
+  </si>
+  <si>
+    <t>Speaking | Monitoring | Active Listening | Critical Thinking | Reading Comprehension | Writing | Active Learning</t>
+  </si>
+  <si>
+    <t>Transportation | Public Safety and Security | Mechanical | Law and Government | English Language | Geography | Administration and Management | Customer and Personal Service | Education and Training</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Oral Expression | Problem Sensitivity | Deductive Reasoning | Spatial Orientation | Far Vision | Speech Clarity | Near Vision | Written Comprehension | Control Precision | Arm-Hand Steadiness | Speech Recognition | Information Ordering | Inductive Reasoning | Perceptual Speed | Flexibility of Closure | Written Expression | Depth Perception | Manual Dexterity | Selective Attention | Time Sharing | Multilimb Coordination | Rate Control | Reaction Time | Glare Sensitivity | Category Flexibility | Visualization | Auditory Attention | Gross Body Equilibrium | Trunk Strength | Response Orientation | Finger Dexterity | Speed of Closure | Visual Color Discrimination | Extent Flexibility</t>
+  </si>
+  <si>
+    <t>Face-to-Face Discussions with Individuals and Within Teams | Frequency of Decision Making | Impact of Decisions on Co-workers or Company Results | Contact With Others | Freedom to Make Decisions | Health and Safety of Other Workers | Work With or Contribute to a Work Group or Team | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Telephone Conversations | Determine Tasks, Priorities and Goals | Outdoors, Exposed to All Weather Conditions | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Consequence of Error | In an Enclosed Vehicle or Operate Enclosed Equipment | Importance of Being Exact or Accurate | Work Outcomes and Results of Other Workers | Exposed to Extremely Bright or Inadequate Lighting Conditions | Time Pressure | Coordinate or Lead Others in Accomplishing Work Activities | Exposed to Contaminants | Physical Proximity | Indoors, Not Environmentally Controlled | E-Mail | Importance of Repeating Same Tasks | Exposed to Very Hot or Cold Temperatures</t>
+  </si>
+  <si>
+    <t>Aircraft Cargo Handling Supervisors | Airfield Operations Specialists | Airline Pilots, Copilots, and Flight Engineers | Bridge and Lock Tenders | Commercial Divers | Commercial Pilots | Dredge Operators | Fishing and Hunting Workers | Hoist and Winch Operators | Locomotive Engineers | Marine Engineers and Naval Architects | Motorboat Operators | Rail Yard Engineers, Dinkey Operators, and Hostlers | Railroad Brake, Signal, and Switch Operators and Locomotive Firers | Railroad Conductors and Yardmasters | Riggers | Sailors and Marine Oilers | Ship Engineers | Tank Car, Truck, and Ship Loaders | Transportation Inspectors</t>
+  </si>
+  <si>
+    <t>Command or supervise operations of ships and water vessels, such as tugboats and ferryboats. Required to hold license issued by U.S. Coast Guard.</t>
+  </si>
+  <si>
+    <t>Advise ships' masters on harbor rules and customs procedures. | Arrange for ships to be fueled, restocked with supplies, or repaired. | Assign watches or living quarters to crew members. | Calculate sightings of land, using electronic sounding devices and following contour lines on charts. | Conduct safety drills such as man overboard or fire drills. | Consult maps, charts, weather reports, or navigation equipment to determine and direct ship movements. | Direct courses and speeds of ships, based on specialized knowledge of local winds, weather, water depths, tides, currents, and hazards. | Direct or coordinate crew members or workers performing activities such as loading or unloading cargo, steering vessels, operating engines, or operating, maintaining, or repairing ship equipment. | Dock or undock vessels, sometimes maneuvering through narrow spaces, such as locks. | Inspect vessels to ensure efficient and safe operation of vessels and equipment and conformance to regulations. | Interview and hire crew members. | Learn to operate new technology systems and procedures through instruction, simulators, or models. | Maintain boats or equipment on board, such as engines, winches, navigational systems, fire extinguishers, or life preservers. | Maintain records of daily activities, personnel reports, ship positions and movements, ports of call, weather and sea conditions, pollution control efforts, or cargo or passenger status. | Measure depths of water, using depth-measuring equipment. | Observe loading or unloading of cargo or equipment to ensure that handling and storage are performed according to specifications. | Operate ship-to-shore radios to exchange information needed for ship operations. | Perform various marine duties, such as checking for oil spills or other pollutants around ports or harbors or patrolling beaches. | Prevent ships under navigational control from engaging in unsafe operations. | Provide assistance in maritime rescue operations. | Purchase supplies or equipment. | Read gauges to verify sufficient levels of hydraulic fluid, air pressure, or oxygen. | Report to appropriate authorities any violations of federal or state pilotage laws. | Serve as a vessel's docking master upon arrival at a port or at a berth. | Signal crew members or deckhands to rig tow lines, open or close gates or ramps, or pull guard chains across entries. | Signal passing vessels, using whistles, flashing lights, flags, or radios. | Stand watches on vessels during specified periods while vessels are under way. | Steer and operate vessels, using radios, depth finders, radars, lights, buoys, or lighthouses. | Supervise crews in cleaning or maintaining decks, superstructures, or bridges. | Tow and maneuver barges or signal tugboats to tow barges to destinations.</t>
+  </si>
+  <si>
+    <t>53-5022.00</t>
+  </si>
+  <si>
+    <t>Motorboat Operators</t>
+  </si>
+  <si>
+    <t>Boat Operator | Crew Boat Operator | Harbor Pilot | Launch Operator | Launchman | Motorboat Operator | River Pilot | Shoreboat Driver | Water Taxi Business Operator | Water Taxi Operator</t>
+  </si>
+  <si>
+    <t>Autopilot software | Cartography software | Echo sounder software | Global positioning system GPS software | Radar software | Roam Devices Roam Marine Monitor Hub | SEA.AI Offshore ONE | Web browser software</t>
+  </si>
+  <si>
+    <t>Speaking | Monitoring | Active Listening | Critical Thinking</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | English Language | Education and Training | Public Safety and Security | Transportation | Mechanical</t>
+  </si>
+  <si>
+    <t>Control Precision | Spatial Orientation | Far Vision | Problem Sensitivity | Perceptual Speed | Arm-Hand Steadiness | Manual Dexterity | Speech Clarity | Auditory Attention | Oral Expression | Multilimb Coordination | Deductive Reasoning | Selective Attention | Response Orientation | Reaction Time | Near Vision | Depth Perception | Time Sharing | Speech Recognition | Glare Sensitivity | Rate Control | Finger Dexterity | Flexibility of Closure | Oral Comprehension | Visualization | Information Ordering | Inductive Reasoning | Hearing Sensitivity | Peripheral Vision | Visual Color Discrimination | Trunk Strength | Static Strength</t>
+  </si>
+  <si>
+    <t>Frequency of Decision Making | Freedom to Make Decisions | Impact of Decisions on Co-workers or Company Results | Face-to-Face Discussions with Individuals and Within Teams | Health and Safety of Other Workers | Determine Tasks, Priorities and Goals | Importance of Being Exact or Accurate | Deal With External Customers or the Public in General | Contact With Others | Outdoors, Exposed to All Weather Conditions | Time Pressure | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Work Outcomes and Results of Other Workers | Physical Proximity | Coordinate or Lead Others in Accomplishing Work Activities | Work With or Contribute to a Work Group or Team | Exposed to Very Hot or Cold Temperatures | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Importance of Repeating Same Tasks | Exposed to Contaminants | In an Open Vehicle or Operating Equipment | Dealing With Unpleasant, Angry, or Discourteous People</t>
+  </si>
+  <si>
+    <t>Aircraft Cargo Handling Supervisors | Bridge and Lock Tenders | Bus and Truck Mechanics and Diesel Engine Specialists | Captains, Mates, and Pilots of Water Vessels | Commercial Pilots | Dredge Operators | Fishing and Hunting Workers | Heavy and Tractor-Trailer Truck Drivers | Highway Maintenance Workers | Hoist and Winch Operators | Industrial Truck and Tractor Operators | Locomotive Engineers | Motorboat Mechanics and Service Technicians | Rail Yard Engineers, Dinkey Operators, and Hostlers | Railroad Brake, Signal, and Switch Operators and Locomotive Firers | Riggers | Sailors and Marine Oilers | Ship Engineers | Tank Car, Truck, and Ship Loaders | Transportation Inspectors</t>
+  </si>
+  <si>
+    <t>Operate small motor-driven boats. May assist in navigational activities.</t>
+  </si>
+  <si>
+    <t>Arrange repairs, fuel, and supplies for vessels. | Clean boats and repair hulls and superstructures, using hand tools, paint, and brushes. | Direct safety operations in emergency situations. | Follow safety procedures to ensure the protection of passengers, cargo, and vessels. | Issue directions for loading, unloading, and seating in boats. | Maintain desired courses, using compasses or electronic navigational aids. | Maintain equipment such as range markers, fire extinguishers, boat fenders, lines, pumps, and fittings. | Operate engine throttles and steering mechanisms to guide boats on desired courses. | Organize and direct the activities of crew members. | Oversee operation of vessels used for carrying passengers, motor vehicles, or goods across rivers, harbors, lakes, and coastal waters. | Perform general labor duties such as repairing booms. | Report any observed navigational hazards to authorities. | Secure boats to docks with mooring lines, and cast off lines to enable departure. | Service motors by performing tasks such as changing oil and lubricating parts. | Take depth soundings in turning basins. | Tow, push, or guide other boats, barges, logs, or rafts.</t>
+  </si>
+  <si>
+    <t>53-5031.00</t>
+  </si>
+  <si>
+    <t>Ship Engineers</t>
+  </si>
+  <si>
+    <t>Barge Engineer | Engineer | Ferry Engineer | Harbor Engineer | Port Engineer | Ship Engineer | Towboat Engineer | Tug Boat Engineer | Vessel Engineer</t>
+  </si>
+  <si>
+    <t>Apple macOS | Computer aided dispatch software | Computerized maintenance management system CMMS | Damen DAMOS | Electronic data interchange EDI software | Kongsberg Maritime K-LOG Electronic Logbooks | Marine Software Marine Planned Maintenance | Marine Software Marine Safety Manager | Microsoft Access | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Word | Oracle Database | SAP software | Salesforce software | Wonderware software</t>
+  </si>
+  <si>
+    <t>Critical Thinking | Active Listening | Monitoring | Speaking | Active Learning | Reading Comprehension | Writing</t>
+  </si>
+  <si>
+    <t>Mechanical | English Language | Engineering and Technology | Public Safety and Security | Transportation | Mathematics | Computers and Electronics</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Oral Expression | Problem Sensitivity | Deductive Reasoning | Near Vision | Written Comprehension | Control Precision | Speech Clarity | Speech Recognition | Inductive Reasoning | Information Ordering | Auditory Attention | Hearing Sensitivity | Reaction Time | Multilimb Coordination | Finger Dexterity | Manual Dexterity | Arm-Hand Steadiness | Selective Attention | Visualization | Flexibility of Closure | Category Flexibility | Written Expression | Perceptual Speed | Originality | Fluency of Ideas | Response Orientation | Time Sharing | Far Vision | Extent Flexibility | Trunk Strength | Static Strength | Rate Control</t>
+  </si>
+  <si>
+    <t>Health and Safety of Other Workers | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Face-to-Face Discussions with Individuals and Within Teams | Impact of Decisions on Co-workers or Company Results | Consequence of Error | Outdoors, Exposed to All Weather Conditions | Indoors, Not Environmentally Controlled | Work With or Contribute to a Work Group or Team | Exposed to Hazardous Equipment | Frequency of Decision Making | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Exposed to Contaminants | Exposed to Cramped Work Space, Awkward Positions | Exposed to Very Hot or Cold Temperatures | Freedom to Make Decisions | Contact With Others | Exposed to Hazardous Conditions | Determine Tasks, Priorities and Goals | Telephone Conversations | Importance of Repeating Same Tasks | Time Pressure | Physical Proximity | Outdoors, Under Cover | Coordinate or Lead Others in Accomplishing Work Activities | Importance of Being Exact or Accurate | Work Outcomes and Results of Other Workers | Exposed to Extremely Bright or Inadequate Lighting Conditions</t>
+  </si>
+  <si>
+    <t>Aerospace Engineering and Operations Technologists and Technicians | Aircraft Mechanics and Service Technicians | Aircraft Structure, Surfaces, Rigging, and Systems Assemblers | Avionics Technicians | Bus and Truck Mechanics and Diesel Engine Specialists | Electrical and Electronics Repairers, Commercial and Industrial Equipment | Hydroelectric Plant Technicians | Locomotive Engineers | Maintenance and Repair Workers, General | Marine Engineers and Naval Architects | Mobile Heavy Equipment Mechanics, Except Engines | Motorboat Mechanics and Service Technicians | Operating Engineers and Other Construction Equipment Operators | Petroleum Pump System Operators, Refinery Operators, and Gaugers | Power Distributors and Dispatchers | Power Plant Operators | Sailors and Marine Oilers | Stationary Engineers and Boiler Operators | Transportation Vehicle, Equipment and Systems Inspectors, Except Aviation | Wellhead Pumpers</t>
+  </si>
+  <si>
+    <t>Supervise and coordinate activities of crew engaged in operating and maintaining engines, boilers, deck machinery, and electrical, sanitary, and refrigeration equipment aboard ship.</t>
+  </si>
+  <si>
+    <t>Act as a liaison between a ship's captain and shore personnel to ensure that schedules and budgets are maintained and that the ship is operated safely and efficiently. | Clean engine parts and keep engine rooms clean. | Fabricate engine replacement parts, such as valves, stay rods, or bolts, using metalworking machinery. | Install engine controls, propeller shafts, or propellers. | Maintain complete records of engineering department activities, including machine operations. | Maintain electrical power, heating, ventilation, refrigeration, water, or sewerage systems. | Maintain or repair engines, electric motors, pumps, winches, or other mechanical or electrical equipment, or assist other crew members with maintenance or repair duties. | Monitor and test operations of engines or other equipment so that malfunctions and their causes can be identified. | Monitor engine, machinery, or equipment indicators when vessels are underway, and report abnormalities to appropriate shipboard staff. | Monitor the availability, use, or condition of lifesaving equipment or pollution preventatives to ensure that international regulations are followed. | Operate or maintain off-loading liquid pumps or valves. | Order and receive engine room stores, such as oil or spare parts, maintain inventories, and record usage of supplies. | Perform general marine vessel maintenance or repair work, such as repairing leaks, finishing interiors, refueling, or maintaining decks. | Perform or participate in emergency drills, as required. | Record orders for changes in ship speed or direction, and note gauge readings or test data, such as revolutions per minute or voltage output, in engineering logs or bellbooks. | Start engines to propel ships, and regulate engines and power transmissions to control speeds of ships, according to directions from captains or bridge computers. | Supervise marine engine technicians engaged in the maintenance or repair of mechanical or electrical marine vessels, and inspect their work to ensure that it is performed properly.</t>
+  </si>
+  <si>
+    <t>53-6011.00</t>
+  </si>
+  <si>
+    <t>Bridge and Lock Tenders</t>
+  </si>
+  <si>
+    <t>Bridge Operator | Bridge Tender | Lock Tender</t>
+  </si>
+  <si>
+    <t>Email software | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft Word | Oracle PeopleSoft | SAP software | Virtual private networking VPN software</t>
+  </si>
+  <si>
+    <t>Monitoring | Critical Thinking | Speaking | Active Listening</t>
+  </si>
+  <si>
+    <t>Public Safety and Security | English Language</t>
+  </si>
+  <si>
+    <t>Information Ordering | Near Vision | Auditory Attention | Far Vision | Control Precision | Selective Attention | Speech Clarity | Speech Recognition | Hearing Sensitivity | Reaction Time | Arm-Hand Steadiness | Perceptual Speed | Problem Sensitivity | Oral Expression | Oral Comprehension</t>
+  </si>
+  <si>
+    <t>Indoors, Environmentally Controlled | Telephone Conversations | Contact With Others | Consequence of Error | Freedom to Make Decisions | Importance of Being Exact or Accurate | Face-to-Face Discussions with Individuals and Within Teams | Impact of Decisions on Co-workers or Company Results | Determine Tasks, Priorities and Goals | E-Mail | Health and Safety of Other Workers | Frequency of Decision Making | Deal With External Customers or the Public in General | Importance of Repeating Same Tasks</t>
+  </si>
+  <si>
+    <t>Captains, Mates, and Pilots of Water Vessels | Crane and Tower Operators | Dredge Operators | Electrical Power-Line Installers and Repairers | Highway Maintenance Workers | Hoist and Winch Operators | Industrial Truck and Tractor Operators | Locksmiths and Safe Repairers | Locomotive Engineers | Motorboat Operators | Operating Engineers and Other Construction Equipment Operators | Rail Yard Engineers, Dinkey Operators, and Hostlers | Railroad Brake, Signal, and Switch Operators and Locomotive Firers | Railroad Conductors and Yardmasters | Riggers | Sailors and Marine Oilers | Security Guards | Ship Engineers | Signal and Track Switch Repairers | Tank Car, Truck, and Ship Loaders</t>
+  </si>
+  <si>
+    <t>Operate and tend bridges, canal locks, and lighthouses to permit marine passage on inland waterways, near shores, and at danger points in waterway passages. May supervise such operations. Includes drawbridge operators, lock operators, and slip bridge operators.</t>
+  </si>
+  <si>
+    <t>Attach ropes or cable lines to bitts on lock decks or wharfs to secure vessels. | Check that bridges are clear of vehicles and pedestrians prior to opening. | Clean and lubricate equipment, and make minor repairs and adjustments. | Control machinery to open and close canal locks and dams, railroad or highway drawbridges, or horizontally or vertically adjustable bridges. | Direct movements of vessels in locks or bridge areas, using signals, telecommunication equipment, or loudspeakers. | Inspect canal and bridge equipment, and areas, such as roadbeds, for damage or defects, reporting problems to supervisors as necessary. | Log data, such as water levels and weather conditions. | Maintain and guard stations in bridges to check waterways for boat traffic. | Move levers to activate traffic signals, navigation lights, and alarms. | Observe approaching vessels to determine size and speed, and listen for whistle signals indicating desire to pass. | Observe position and progress of vessels to ensure best use of lock spaces or bridge opening spaces. | Perform maintenance duties, such as sweeping, painting, and yard work to keep facilities clean and in order. | Prepare accident reports. | Raise drawbridges and observe passage of water traffic or lower drawbridges and raise automobile gates. | Record names, types, and destinations of vessels passing through bridge openings or locks, and numbers of trains or vehicles crossing bridges. | Stop automobile and pedestrian traffic on bridges, and lower automobile gates prior to moving bridges. | Turn valves to increase or decrease water levels in locks. | Write and submit maintenance work requisitions.</t>
+  </si>
+  <si>
+    <t>53-6021.00</t>
+  </si>
+  <si>
+    <t>Parking Attendants</t>
+  </si>
+  <si>
+    <t>Hiker | Parking Attendant | Parking Cashier | Parking Lot Attendant | Parking Ramp Attendant | Valet Attendant | Valet Parker | Valet Parking Attendant</t>
+  </si>
+  <si>
+    <t>CorePark Valet | Email software | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft Word | Payment processing software | SMS Valet</t>
+  </si>
+  <si>
+    <t>Speaking | Active Listening</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | English Language | Transportation</t>
+  </si>
+  <si>
+    <t>Far Vision | Oral Comprehension | Oral Expression | Speech Recognition | Near Vision | Speech Clarity | Problem Sensitivity | Spatial Orientation | Inductive Reasoning | Deductive Reasoning | Control Precision | Selective Attention | Information Ordering | Depth Perception | Multilimb Coordination</t>
+  </si>
+  <si>
+    <t>Contact With Others | Face-to-Face Discussions with Individuals and Within Teams | Deal With External Customers or the Public in General | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | In an Enclosed Vehicle or Operate Enclosed Equipment | Importance of Being Exact or Accurate | Physical Proximity | Spend Time Walking or Running | Work With or Contribute to a Work Group or Team | Spend Time Making Repetitive Motions | Telephone Conversations | Outdoors, Exposed to All Weather Conditions | Impact of Decisions on Co-workers or Company Results | Coordinate or Lead Others in Accomplishing Work Activities | Dealing With Unpleasant, Angry, or Discourteous People | Exposed to Contaminants</t>
+  </si>
+  <si>
+    <t>Amusement and Recreation Attendants | Baggage Porters and Bellhops | Bus Drivers, Transit and Intercity | Cashiers | Concierges | Counter and Rental Clerks | Dispatchers, Except Police, Fire, and Ambulance | Driver/Sales Workers | Food Servers, Nonrestaurant | Heavy and Tractor-Trailer Truck Drivers | Hotel, Motel, and Resort Desk Clerks | Industrial Truck and Tractor Operators | Light Truck Drivers | Locker Room, Coatroom, and Dressing Room Attendants | Parking Enforcement Workers | Passenger Attendants | Railroad Conductors and Yardmasters | Reservation and Transportation Ticket Agents and Travel Clerks | Shuttle Drivers and Chauffeurs | Taxi Drivers</t>
+  </si>
+  <si>
+    <t>Park vehicles or issue tickets for customers in a parking lot or garage. May park or tend vehicles in environments such as a car dealership or rental car facility. May collect fee.</t>
+  </si>
+  <si>
+    <t>Call emergency responders or the proper authorities and provide motorist assistance, such as giving directions or helping jump start a stalled vehicle. | Direct motorists to parking areas or parking spaces, using hand signals or flashlights as necessary. | Escort customers to their vehicles to ensure their safety. | Explain and calculate parking charges, collect fees from customers, and respond to customer complaints. | Greet customers and open their car doors. | Inspect vehicles to detect any damage. | Issue ticket stubs or place numbered tags on windshields, log tags or attach tag to customers' keys, and give customers matching tags for locating parked vehicles. | Keep parking areas clean and orderly to ensure that space usage is maximized. | Lift, position, and remove barricades to open or close parking areas. | Park and retrieve automobiles for customers in parking lots, storage garages, or new car lots. | Patrol parking areas to prevent vehicle damage and vehicle or property thefts. | Perform cash handling tasks, such as making change, balancing and recording cash drawer, or distributing tips. | Perform maintenance on cars in storage to protect tires, batteries, or exteriors from deterioration. | Provide customer assistance and information, such as giving directions or handling wheelchairs. | Take numbered tags from customers, locate vehicles, and deliver vehicles, or provide customers with instructions for locating vehicles.</t>
+  </si>
+  <si>
+    <t>53-6031.00</t>
+  </si>
+  <si>
+    <t>Automotive and Watercraft Service Attendants</t>
+  </si>
+  <si>
+    <t>Attendant | Dock Attendant | Dock Hand | Fuel Attendant | Fuel Dock Attendant | Gas Attendant | Gas Pumper | Marine Fuel Dock Attendant | Service Station Attendant</t>
+  </si>
+  <si>
+    <t>Apple Safari | Inventory management systems | Microsoft Edge | Microsoft Excel | Microsoft Outlook | Microsoft Windows | Mozilla Firefox | Software libraries | Timekeeping software | Web browser software</t>
+  </si>
+  <si>
+    <t>Active Listening | Speaking | Critical Thinking</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | Mechanical | Sales and Marketing | Administration and Management | Mathematics | Administrative</t>
+  </si>
+  <si>
+    <t>Oral Expression | Oral Comprehension | Near Vision | Manual Dexterity | Finger Dexterity | Control Precision | Trunk Strength | Speech Recognition | Extent Flexibility | Stamina | Static Strength | Multilimb Coordination | Arm-Hand Steadiness | Information Ordering | Deductive Reasoning | Far Vision | Visualization | Problem Sensitivity | Speech Clarity</t>
+  </si>
+  <si>
+    <t>Face-to-Face Discussions with Individuals and Within Teams | Telephone Conversations | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Time Pressure | Spend Time Standing | Exposed to Contaminants | Frequency of Decision Making | Contact With Others | Impact of Decisions on Co-workers or Company Results | Importance of Being Exact or Accurate | Exposed to Hazardous Equipment | Outdoors, Exposed to All Weather Conditions | Deal With External Customers or the Public in General | Freedom to Make Decisions | Work With or Contribute to a Work Group or Team | Exposed to Minor Burns, Cuts, Bites, or Stings | Spend Time Walking or Running | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Indoors, Not Environmentally Controlled | Spend Time Making Repetitive Motions | Determine Tasks, Priorities and Goals | Spend Time Kneeling, Crouching, Stooping, or Crawling | Consequence of Error | Health and Safety of Other Workers | Dealing With Unpleasant, Angry, or Discourteous People | Exposed to Very Hot or Cold Temperatures</t>
+  </si>
+  <si>
+    <t>Aircraft Service Attendants | Automotive Service Technicians and Mechanics | Bus and Truck Mechanics and Diesel Engine Specialists | Cleaners of Vehicles and Equipment | Control and Valve Installers and Repairers, Except Mechanical Door | Electric Motor, Power Tool, and Related Repairers | Engine and Other Machine Assemblers | Gas Compressor and Gas Pumping Station Operators | Home Appliance Repairers | Maintenance Workers, Machinery | Mobile Heavy Equipment Mechanics, Except Engines | Motorboat Mechanics and Service Technicians | Outdoor Power Equipment and Other Small Engine Mechanics | Petroleum Pump System Operators, Refinery Operators, and Gaugers | Pump Operators, Except Wellhead Pumpers | Rail Car Repairers | Roustabouts, Oil and Gas | Service Unit Operators, Oil and Gas | Stationary Engineers and Boiler Operators | Tire Repairers and Changers</t>
+  </si>
+  <si>
+    <t>Service automobiles, buses, trucks, boats, and other automotive or marine vehicles with fuel, lubricants, and accessories. Collect payment for services and supplies. May lubricate vehicle, change motor oil, refill antifreeze, or replace lights or other accessories, such as windshield wiper blades or fan belts. May repair or replace tires.</t>
+  </si>
+  <si>
+    <t>Activate fuel pumps and fill fuel tanks of vehicles with gasoline or diesel fuel to specified levels. | Check tire pressure and levels of fuel, motor oil, transmission, radiator, battery, or other fluids, adding air or fluids as required. | Clean parking areas, offices, restrooms, or equipment, and remove trash. | Clean windshields. | Collect cash payments from customers, and make change or charge purchases to customers' credit cards, providing customers with receipts. | Grease and lubricate vehicles or specified units, such as springs, universal joints, or steering knuckles, using grease guns or spray lubricants. | Maintain customer records and follow up periodically with telephone, mail, or personal reminders of services due. | Order stock, and price and shelve incoming goods. | Perform minor repairs, such as adjusting brakes, replacing spark plugs, or changing engine oil or filters. | Prepare daily reports of fuel, oil, and accessory sales. | Provide customers with information about local roads or highways. | Rotate, test, and repair or replace tires. | Sell and install accessories, such as batteries, windshield wiper blades, fan belts, bulbs, or headlamps. | Test and charge batteries.</t>
+  </si>
+  <si>
+    <t>53-6032.00</t>
+  </si>
+  <si>
+    <t>Aircraft Service Attendants</t>
+  </si>
+  <si>
+    <t>Aircraft Fueler | Aircraft Refueler | Aircraft Service Attendant | Aircraft Servicer | Aviation Fueler | Fuel Service Technician | Line Service Technician | Ramp Service Agent | Into-Plane Fueler | Aircraft Line Technician</t>
+  </si>
+  <si>
+    <t>Access Software AIRPAX | Computerized aircraft log manager CALM | Engine analysis software | Maintenance information databases | Maintenance planning software | Maintenance record software | Microsoft Excel | Microsoft Office software | Microsoft Windows | Microsoft Word | Supply system software | Technical manual database software</t>
+  </si>
+  <si>
+    <t>Transportation | Public Safety and Security | Mechanical | English Language | Chemistry | Customer and Personal Service | Mathematics</t>
+  </si>
+  <si>
+    <t>Manual Dexterity | Finger Dexterity | Arm-Hand Steadiness | Multilimb Coordination | Control Precision | Static Strength | Trunk Strength | Stamina | Near Vision | Far Vision | Depth Perception | Gross Body Coordination | Gross Body Equilibrium | Extent Flexibility | Reaction Time | Problem Sensitivity | Oral Comprehension | Selective Attention | Auditory Attention</t>
+  </si>
+  <si>
+    <t>Outdoors, Exposed to All Weather Conditions | Exposed to Very Hot or Cold Temperatures | Exposed to Contaminants | Exposed to Hazardous Conditions | Exposed to Hazardous Equipment | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Spend Time Standing | Spend Time Walking or Running | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | In an Open Vehicle or Operating Equipment | Consequence of Error | Importance of Being Exact or Accurate | Health and Safety of Other Workers | Time Pressure | Work With or Contribute to a Work Group or Team | Face-to-Face Discussions with Individuals and Within Teams | Contact With Others | Importance of Repeating Same Tasks</t>
+  </si>
+  <si>
+    <t>Aerospace Engineering and Operations Technologists and Technicians | Aerospace Engineers | Aircraft Cargo Handling Supervisors | Aircraft Mechanics and Service Technicians | Aircraft Structure, Surfaces, Rigging, and Systems Assemblers | Airline Pilots, Copilots, and Flight Engineers | Automotive and Watercraft Service Attendants | Avionics Technicians | Bus and Truck Mechanics and Diesel Engine Specialists | Cleaners of Vehicles and Equipment | Commercial Pilots | Electro-Mechanical and Mechatronics Technologists and Technicians | Highway Maintenance Workers | Industrial Truck and Tractor Operators | Maintenance Workers, Machinery | Maintenance and Repair Workers, General | Mobile Heavy Equipment Mechanics, Except Engines | Rail Car Repairers | Ship Engineers | Stationary Engineers and Boiler Operators</t>
+  </si>
+  <si>
+    <t>Service aircraft with fuel. May de-ice aircraft, refill water and cooling agents, empty sewage tanks, service air and oxygen systems, or clean and polish exterior.</t>
+  </si>
+  <si>
+    <t>Apply de-icing fluid to aircraft from baskets lifted by truck-mounted cranes. | Change aircraft oil, coolant, or other fluids. | Clean aircraft interiors by picking up waste, wiping down windows, or vacuuming. | Climb ladders to reach aircraft surfaces to be cleaned. | Complete forms describing tasks completed. | De-grease aircraft exteriors. | Empty aircraft lavatory systems or refill them with sanitizer fluid. | Guide aircraft to designated areas using hand signals, batons, or other methods. | Inspect aircraft components to locate cracks, breaks, leaks, or other problems. | Load baggage or cargo for crew or passengers. | Mix cleaning compounds or solutions. | Polish aircraft exteriors. | Radio to flight dispatchers or other personnel to discuss incoming or outgoing aircraft. | Refill aircraft potable water tanks. | Refuel aircraft using hoses connected to fuel trucks. | Remove exhaust stains from aircraft using cleaning fluids. | Tow aircraft to gates or hangars using tugs, tractors, or other vehicles. | Wash the aircraft exteriors using lifts, cranes, detergent, or other equipment.</t>
+  </si>
+  <si>
+    <t>53-6041.00</t>
+  </si>
+  <si>
+    <t>Traffic Technicians</t>
+  </si>
+  <si>
+    <t>Field Traffic Investigator | Traffic Analyst | Traffic Control Technician | Traffic Investigator | Traffic Signal Technician (TST) | Traffic Survey Technician | Traffic Technician | Transportation Planning Technician | Transportation Technician</t>
+  </si>
+  <si>
+    <t>Autodesk AutoCAD | Bentley MicroStation | C++ | Computer aided design and drafting software CADD | Dowling Associates TRAFFIX | ESRI ArcGIS software | ESRI ArcView | Geographic information system GIS systems | JAMAR Technologies PETRAPro | Microsoft Access | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Windows | Microsoft Word | Oracle Database | Pd' Programming Intersection Magic | Python | R | SAS | Salesforce software | Structure query language SQL | Tableau | The MathWorks MATLAB | Traffic control software | Traffic signal software | Trafficware SimTraffic</t>
+  </si>
+  <si>
+    <t>Active Listening | Critical Thinking | Speaking | Reading Comprehension | Writing | Monitoring | Active Learning</t>
+  </si>
+  <si>
+    <t>Public Safety and Security | Transportation | Computers and Electronics | English Language | Engineering and Technology | Law and Government | Mathematics | Customer and Personal Service | Administrative | Education and Training | Mechanical | Design | Building and Construction</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Oral Expression | Problem Sensitivity | Inductive Reasoning | Written Comprehension | Deductive Reasoning | Speech Clarity | Speech Recognition | Near Vision | Far Vision | Selective Attention | Visualization | Perceptual Speed | Flexibility of Closure | Category Flexibility | Information Ordering | Written Expression | Mathematical Reasoning | Originality | Fluency of Ideas | Number Facility</t>
+  </si>
+  <si>
+    <t>E-Mail | Importance of Being Exact or Accurate | In an Enclosed Vehicle or Operate Enclosed Equipment | Indoors, Environmentally Controlled | Face-to-Face Discussions with Individuals and Within Teams | Time Pressure | Telephone Conversations | Work With or Contribute to a Work Group or Team | Freedom to Make Decisions | Outdoors, Exposed to All Weather Conditions | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Frequency of Decision Making | Contact With Others | Importance of Repeating Same Tasks | Impact of Decisions on Co-workers or Company Results | Deal With External Customers or the Public in General | Coordinate or Lead Others in Accomplishing Work Activities | Determine Tasks, Priorities and Goals | Exposed to Hazardous Equipment | Spend Time Sitting</t>
+  </si>
+  <si>
+    <t>Air Traffic Controllers | Aviation Inspectors | Civil Engineering Technologists and Technicians | Civil Engineers | Construction and Building Inspectors | Electrical and Electronics Repairers, Commercial and Industrial Equipment | First-Line Supervisors of Material-Moving Machine and Vehicle Operators | Geodetic Surveyors | Highway Maintenance Workers | Locomotive Engineers | Logistics Engineers | Power Distributors and Dispatchers | Railroad Conductors and Yardmasters | Signal and Track Switch Repairers | Surveying and Mapping Technicians | Transportation Engineers | Transportation Inspectors | Transportation Planners | Transportation Vehicle, Equipment and Systems Inspectors, Except Aviation | Transportation, Storage, and Distribution Managers</t>
+  </si>
+  <si>
+    <t>Conduct field studies to determine traffic volume, speed, effectiveness of signals, adequacy of lighting, and other factors influencing traffic conditions, under direction of traffic engineer.</t>
+  </si>
+  <si>
+    <t>Analyze data related to traffic flow, accident rates, or proposed development to determine the most efficient methods to expedite traffic flow. | Compute time settings for traffic signals or speed restrictions, using standard formulas. | Develop plans or long-range strategies for providing adequate parking space. | Establish procedures for street closures or for repair or construction projects. | Gather and compile data from hand count sheets, machine count tapes, or radar speed checks and code data for computer input. | Interact with the public to answer traffic-related questions, respond to complaints or requests, or discuss traffic control ordinances, plans, policies, or procedures. | Lay out pavement markings for striping crews. | Maintain or make minor adjustments or field repairs to equipment used in surveys, including the replacement of parts on traffic data gathering devices. | Measure and record the speed of vehicular traffic, using electrical timing devices or radar equipment. | Monitor street or utility projects for compliance to traffic control permit conditions. | Operate counters and record data to assess the volume, type, and movement of vehicular or pedestrian traffic at specified times. | Place and secure automatic counters, using power tools, and retrieve counters after counting periods end. | Plan, design, and improve components of traffic control systems to accommodate current or projected traffic and to increase usability and efficiency. | Prepare drawings of proposed signal installations or other control devices, using drafting instruments or computer-automated drafting equipment. | Prepare graphs, charts, diagrams, or other aids to illustrate observations or conclusions. | Prepare work orders for repair, maintenance, or changes in traffic systems. | Provide technical supervision regarding traffic control devices to other traffic technicians or laborers. | Provide traffic information, such as road conditions, to the public. | Review traffic control or barricade plans to issue permits for parades or other special events or for construction work that affects rights of way, providing assistance with plan preparation or revision, as necessary. | Study factors affecting traffic conditions, such as lighting or sign and marking visibility, to assess their effectiveness. | Study traffic delays by noting times of delays, the numbers of vehicles affected, and vehicle speed through the delay area. | Time stoplights or other delays, using stopwatches. | Visit development or work sites to determine projects' effect on traffic and the adequacy of traffic control and safety plans or to suggest traffic control measures.</t>
+  </si>
+  <si>
+    <t>53-6051.00</t>
+  </si>
+  <si>
+    <t>Transportation Inspectors</t>
+  </si>
+  <si>
+    <t>Cargo Surveyor | Inspector | Marine Cargo Surveyor | Marine Surveyor | Petroleum Inspector</t>
+  </si>
+  <si>
+    <t>Adobe Acrobat | Email software | Google Android | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft Word | Web browser software</t>
+  </si>
+  <si>
+    <t>Critical Thinking | Speaking | Writing | Reading Comprehension | Active Listening | Monitoring</t>
+  </si>
+  <si>
+    <t>Transportation | English Language | Customer and Personal Service | Mathematics | Public Safety and Security | Administration and Management | Mechanical | Law and Government</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Oral Expression | Problem Sensitivity | Deductive Reasoning | Near Vision | Written Comprehension | Written Expression | Inductive Reasoning | Information Ordering | Speech Recognition | Far Vision | Speech Clarity | Category Flexibility | Flexibility of Closure | Selective Attention | Visualization | Perceptual Speed</t>
+  </si>
+  <si>
+    <t>Telephone Conversations | Importance of Being Exact or Accurate | E-Mail | Determine Tasks, Priorities and Goals | Contact With Others | Freedom to Make Decisions | Impact of Decisions on Co-workers or Company Results | Outdoors, Exposed to All Weather Conditions | Frequency of Decision Making | Face-to-Face Discussions with Individuals and Within Teams | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | In an Enclosed Vehicle or Operate Enclosed Equipment | Time Pressure | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Deal With External Customers or the Public in General | Work Outcomes and Results of Other Workers | Indoors, Not Environmentally Controlled | Written Letters and Memos | Exposed to Contaminants</t>
+  </si>
+  <si>
+    <t>Agricultural Inspectors | Aircraft Cargo Handling Supervisors | Airfield Operations Specialists | Aviation Inspectors | Cargo and Freight Agents | Construction and Building Inspectors | First-Line Supervisors of Helpers, Laborers, and Material Movers, Hand | First-Line Supervisors of Material-Moving Machine and Vehicle Operators | Freight Forwarders | Government Property Inspectors and Investigators | Inspectors, Testers, Sorters, Samplers, and Weighers | Locomotive Engineers | Marine Engineers and Naval Architects | Occupational Health and Safety Specialists | Railroad Conductors and Yardmasters | Ship Engineers | Shipping, Receiving, and Inventory Clerks | Tank Car, Truck, and Ship Loaders | Transportation Vehicle, Equipment and Systems Inspectors, Except Aviation | Transportation, Storage, and Distribution Managers</t>
+  </si>
+  <si>
+    <t>Inspect equipment or goods in connection with the safe transport of cargo or people. Includes rail transportation inspectors, such as freight inspectors, rail inspectors, and other inspectors of transportation vehicles not elsewhere classified.</t>
+  </si>
+  <si>
+    <t>Advise crews in techniques of stowing dangerous and heavy cargo. | Calculate gross and net tonnage, hold capacities, volumes of stored fuel and water, cargo weights, and vessel stability factors, using mathematical formulas. | Check temperatures and humidities of shipping and storage areas to ensure that they are at appropriate levels to protect cargo. | Determine cargo transportation capabilities by reading documents that set forth cargo loading and securing procedures, capacities, and stability factors. | Direct crews to reload freight or to insert additional bracing or packing as necessary. | Inspect loaded cargo, cargo lashed to decks or in storage facilities, and cargo handling devices to determine compliance with health and safety regulations and need for maintenance. | Inspect shipments to ensure that freight is securely braced and blocked. | Measure heights and widths of loads to ensure they will pass over bridges or through tunnels on scheduled routes. | Measure vessels' holds and depths of fuel and water in tanks, using sounding lines and tape measures. | Notify workers of any special treatment required for shipments. | Observe loading of freight to ensure that crews comply with procedures. | Post warning signs on vehicles containing explosives or flammable or radioactive materials. | Prepare and submit reports after completion of freight shipments. | Read draft markings to determine depths of vessels in water. | Recommend remedial procedures to correct any violations found during inspections. | Record details about freight conditions, handling of freight, and any problems encountered. | Visually inspect cargo for damage upon arrival or discharge.</t>
+  </si>
+  <si>
+    <t>53-6051.01</t>
+  </si>
+  <si>
+    <t>Aviation Inspectors</t>
+  </si>
+  <si>
+    <t>Aircraft Inspector | Aircraft Quality Control Inspector (Aircraft QC Inspector) | Airworthiness Safety Inspector | Aviation Safety Inspector (ASI) | Avionics Safety Inspector | Inspector | Manufacturing Aviation Safety Inspector (Manufacturing ASI) | Quality Control Inspector (QC Inspector) | Quality Inspector | RTS Inspector (Return to Service Inspector)</t>
+  </si>
+  <si>
+    <t>Adobe InDesign | Adobe Photoshop | Aircraft regulation databases | Dassault Systemes CATIA | IBM WebSphere MQ | Microsoft Access | Microsoft Active Server Pages ASP | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Robotic workstation software | SAP software | SAS | Technical Data Management System TDMS</t>
+  </si>
+  <si>
+    <t>Critical Thinking | Reading Comprehension | Active Listening | Speaking | Writing | Monitoring | Active Learning</t>
+  </si>
+  <si>
+    <t>English Language | Mechanical | Public Safety and Security | Customer and Personal Service | Transportation | Education and Training | Production and Processing | Engineering and Technology | Mathematics | Administration and Management | Law and Government | Computers and Electronics | Design | Physics | Administrative | Telecommunications</t>
+  </si>
+  <si>
+    <t>Inductive Reasoning | Problem Sensitivity | Oral Comprehension | Deductive Reasoning | Near Vision | Written Comprehension | Oral Expression | Speech Clarity | Written Expression | Speech Recognition | Information Ordering | Far Vision | Visualization | Perceptual Speed | Category Flexibility | Flexibility of Closure | Selective Attention | Auditory Attention | Hearing Sensitivity | Visual Color Discrimination | Control Precision | Manual Dexterity | Arm-Hand Steadiness | Time Sharing | Fluency of Ideas</t>
+  </si>
+  <si>
+    <t>E-Mail | Telephone Conversations | Face-to-Face Discussions with Individuals and Within Teams | Frequency of Decision Making | Consequence of Error | Impact of Decisions on Co-workers or Company Results | Importance of Being Exact or Accurate | Contact With Others | Determine Tasks, Priorities and Goals | Freedom to Make Decisions | Importance of Repeating Same Tasks | Deal With External Customers or the Public in General | Coordinate or Lead Others in Accomplishing Work Activities | Health and Safety of Other Workers | Work With or Contribute to a Work Group or Team | Time Pressure | Work Outcomes and Results of Other Workers | Physical Proximity | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Indoors, Environmentally Controlled | Exposed to Very Hot or Cold Temperatures | Exposed to Contaminants | Indoors, Not Environmentally Controlled | Exposed to Cramped Work Space, Awkward Positions | Written Letters and Memos | Level of Competition | Outdoors, Exposed to All Weather Conditions | Exposed to Extremely Bright or Inadequate Lighting Conditions | Spend Time Standing</t>
+  </si>
+  <si>
+    <t>Aerospace Engineering and Operations Technologists and Technicians | Aerospace Engineers | Aircraft Mechanics and Service Technicians | Aircraft Structure, Surfaces, Rigging, and Systems Assemblers | Airfield Operations Specialists | Automotive Engineering Technicians | Avionics Technicians | Commercial Pilots | Construction and Building Inspectors | Electrical and Electronics Installers and Repairers, Transportation Equipment | Electrical and Electronics Repairers, Commercial and Industrial Equipment | Government Property Inspectors and Investigators | Health and Safety Engineers, Except Mining Safety Engineers and Inspectors | Industrial Engineers | Inspectors, Testers, Sorters, Samplers, and Weighers | Locomotive Engineers | Occupational Health and Safety Specialists | Ship Engineers | Transportation Inspectors | Transportation Vehicle, Equipment and Systems Inspectors, Except Aviation</t>
+  </si>
+  <si>
+    <t>Inspect aircraft, maintenance procedures, air navigational aids, air traffic controls, and communications equipment to ensure conformance with Federal safety regulations.</t>
+  </si>
+  <si>
+    <t>Analyze training programs and conduct oral and written examinations to ensure the competency of persons operating, installing, and repairing aircraft equipment. | Approve or deny issuance of certificates of airworthiness. | Conduct flight test programs to test equipment, instruments, and systems under a variety of conditions, using both manual and automatic controls. | Examine aircraft access plates and doors for security. | Examine landing gear, tires, and exteriors of fuselage, wings, and engines for evidence of damage or corrosion and the need for repairs. | Examine maintenance records and flight logs to determine if service and maintenance checks and overhauls were performed at prescribed intervals. | Inspect new, repaired, or modified aircraft to identify damage or defects and to assess airworthiness and conformance to standards, using checklists, hand tools, and test instruments. | Inspect work of aircraft mechanics performing maintenance, modification, or repair and overhaul of aircraft and aircraft mechanical systems to ensure adherence to standards and procedures. | Investigate air accidents and complaints to determine causes. | Prepare and maintain detailed repair, inspection, investigation, and certification records and reports. | Recommend changes in rules, policies, standards, and regulations, based on knowledge of operating conditions, aircraft improvements, and other factors. | Recommend replacement, repair, or modification of aircraft equipment. | Start aircraft and observe gauges, meters, and other instruments to detect evidence of malfunctions.</t>
+  </si>
+  <si>
+    <t>53-6051.07</t>
+  </si>
+  <si>
+    <t>Transportation Vehicle, Equipment and Systems Inspectors, Except Aviation</t>
+  </si>
+  <si>
+    <t>Car Inspector | Carman | Emissions Inspector | Inspector | Quality Assurance Inspector | Railroad Track Inspector | Safety Officer | Smog Technician | Transit Vehicle Inspector</t>
+  </si>
+  <si>
+    <t>ASPEN | Commercial driver's license information system CDLIS | Diagnostic scanner software | Inspection Selection System ISS | Law enforcement database software | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Past Inspection Query PIQ | Structured query language SQL | Vehicle identification number VIN database | Vehicle inspection databases</t>
+  </si>
+  <si>
+    <t>Active Listening | Critical Thinking | Speaking | Reading Comprehension</t>
+  </si>
+  <si>
+    <t>Mechanical | Transportation | English Language | Public Safety and Security</t>
+  </si>
+  <si>
+    <t>Near Vision | Problem Sensitivity | Oral Comprehension | Arm-Hand Steadiness | Flexibility of Closure | Deductive Reasoning | Oral Expression | Speech Clarity | Auditory Attention | Hearing Sensitivity | Selective Attention | Inductive Reasoning</t>
+  </si>
+  <si>
+    <t>Face-to-Face Discussions with Individuals and Within Teams | Contact With Others | Frequency of Decision Making | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Spend Time Standing | Impact of Decisions on Co-workers or Company Results | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Importance of Being Exact or Accurate | Time Pressure | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | Consequence of Error | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Work With or Contribute to a Work Group or Team | Exposed to Minor Burns, Cuts, Bites, or Stings | Work Outcomes and Results of Other Workers | Physical Proximity | Indoors, Not Environmentally Controlled | Coordinate or Lead Others in Accomplishing Work Activities | Spend Time Walking or Running | Health and Safety of Other Workers | Exposed to Contaminants | Exposed to Hazardous Conditions | Outdoors, Exposed to All Weather Conditions | Telephone Conversations | In an Enclosed Vehicle or Operate Enclosed Equipment | Level of Competition</t>
+  </si>
+  <si>
+    <t>Aerospace Engineering and Operations Technologists and Technicians | Aircraft Mechanics and Service Technicians | Automotive Engineering Technicians | Automotive Service Technicians and Mechanics | Aviation Inspectors | Bus and Truck Mechanics and Diesel Engine Specialists | Calibration Technologists and Technicians | Construction and Building Inspectors | Electrical and Electronics Installers and Repairers, Transportation Equipment | Electrical and Electronics Repairers, Commercial and Industrial Equipment | Health and Safety Engineers, Except Mining Safety Engineers and Inspectors | Inspectors, Testers, Sorters, Samplers, and Weighers | Locomotive Engineers | Maintenance and Repair Workers, General | Occupational Health and Safety Specialists | Rail Car Repairers | Railroad Conductors and Yardmasters | Ship Engineers | Stationary Engineers and Boiler Operators | Transportation Inspectors</t>
+  </si>
+  <si>
+    <t>Inspect and monitor transportation equipment, vehicles, or systems to ensure compliance with regulations and safety standards.</t>
+  </si>
+  <si>
+    <t>Attach onboard diagnostics (OBD) scanner cables to vehicles to conduct emissions inspections. | Conduct remote inspections of motor vehicles, using handheld controllers and remotely directed vehicle inspection devices. | Conduct vehicle or transportation equipment tests, using diagnostic equipment. | Conduct visual inspections of emission control equipment and smoke emitted from gasoline or diesel vehicles. | Examine carrier operating rules, employee qualification guidelines, or carrier training and testing programs for compliance with regulations or safety standards. | Identify modifications to engines, fuel systems, emissions control equipment, or other vehicle systems to determine the impact of modifications on inspection procedures or conclusions. | Inspect repairs to transportation vehicles or equipment to ensure that repair work was performed properly. | Inspect vehicles or equipment to ensure compliance with rules, standards, or regulations. | Inspect vehicles or other equipment for evidence of abuse, damage, or mechanical malfunction. | Investigate complaints regarding safety violations. | Investigate incidents or violations, such as delays, accidents, and equipment failures. | Issue notices and recommend corrective actions when infractions or problems are found. | Prepare reports on investigations or inspections and actions taken. | Review commercial vehicle logs, shipping papers, or driver and equipment records to detect any problems or to ensure compliance with regulations.</t>
+  </si>
+  <si>
+    <t>53-6061.00</t>
+  </si>
+  <si>
+    <t>Passenger Attendants</t>
+  </si>
+  <si>
+    <t>Bus Aide | Bus Assistant | Bus Attendant | Bus Monitor | Fare Enforcement Officer | Transportation Aide</t>
+  </si>
+  <si>
+    <t>Appointment scheduling software | Email software | Microsoft Office software | Microsoft Windows | Microsoft Word | Time tracking software</t>
+  </si>
+  <si>
+    <t>Speaking | Active Listening | Monitoring | Reading Comprehension</t>
+  </si>
+  <si>
+    <t>Transportation | English Language | Public Safety and Security | Customer and Personal Service</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Oral Expression | Speech Recognition | Speech Clarity | Problem Sensitivity | Deductive Reasoning | Selective Attention | Inductive Reasoning | Written Comprehension</t>
+  </si>
+  <si>
+    <t>Physical Proximity | Contact With Others | Dealing With Unpleasant, Angry, or Discourteous People | Exposed to Very Hot or Cold Temperatures | Spend Time Sitting | Frequency of Decision Making | Face-to-Face Discussions with Individuals and Within Teams | Exposed to Contaminants</t>
+  </si>
+  <si>
+    <t>Aircraft Cargo Handling Supervisors | Airfield Operations Specialists | Baggage Porters and Bellhops | Bus Drivers, Transit and Intercity | Concierges | Dispatchers, Except Police, Fire, and Ambulance | First-Line Supervisors of Passenger Attendants | Flight Attendants | Hosts and Hostesses, Restaurant, Lounge, and Coffee Shop | Hotel, Motel, and Resort Desk Clerks | Locker Room, Coatroom, and Dressing Room Attendants | Orderlies | Parking Attendants | Railroad Conductors and Yardmasters | Reservation and Transportation Ticket Agents and Travel Clerks | School Bus Monitors | Shuttle Drivers and Chauffeurs | Subway and Streetcar Operators | Taxi Drivers | Ushers, Lobby Attendants, and Ticket Takers</t>
+  </si>
+  <si>
+    <t>Provide services to ensure the safety of passengers aboard ships, buses, trains, or within the station or terminal. Perform duties such as explaining the use of safety equipment, serving meals or beverages, or answering questions related to travel.</t>
+  </si>
+  <si>
+    <t>Adjust window shades or seat cushions at the request of passengers. | Count and verify tickets and seat reservations and record numbers of passengers boarding and disembarking. | Determine or facilitate seating arrangements. | Explain and demonstrate safety procedures and safety equipment use. | Greet passengers boarding transportation equipment and announce routes and stops. | Open and close doors for passengers. | Perform equipment safety checks prior to departure. | Provide boarding assistance to elderly, sick, or injured people. | Provide customers with information on routes, gates, prices, timetables, terminals, or concourses. | Respond to passengers' questions, requests, or complaints. | Secure passengers for transportation by buckling seatbelts or fastening wheelchairs with tie-down straps. | Signal transportation operators to stop or to proceed.</t>
+  </si>
+  <si>
+    <t>53-6099.00</t>
+  </si>
+  <si>
+    <t>Transportation Workers, All Other</t>
+  </si>
+  <si>
+    <t>Fueler | Ground Support Worker | Terminal Attendant | Transit Worker | Transportation Attendant | Transportation Support Worker | Transportation Worker | Vehicle Attendant | Ramp Agent | Gate Attendant</t>
+  </si>
+  <si>
+    <t>Transportation | Public Safety and Security | Customer and Personal Service | English Language | Mechanical | Geography</t>
+  </si>
+  <si>
+    <t>Outdoors, Exposed to All Weather Conditions | Spend Time Standing | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Exposed to Very Hot or Cold Temperatures | Exposed to Contaminants | Exposed to Hazardous Equipment | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Spend Time Bending or Twisting Your Body | Spend Time Kneeling, Crouching, Stooping, or Crawling | Spend Time Climbing Ladders, Scaffolds, or Poles | Exposed to High Places | Health and Safety of Other Workers | Physical Proximity | Contact With Others | Deal With External Customers or the Public in General | Time Pressure | Telephone Conversations | In an Enclosed Vehicle or Operate Enclosed Equipment</t>
+  </si>
+  <si>
+    <t>Aircraft Service Attendants | Parking Attendants | Automotive and Watercraft Service Attendants | Passenger Attendants | Bridge and Lock Tenders | Traffic Technicians | Transportation Inspectors | Aviation Inspectors | Transportation Vehicle, Equipment and Systems Inspectors, Except Aviation | Airfield Operations Specialists | Flight Attendants | Industrial Truck and Tractor Operators | Laborers and Freight, Stock, and Material Movers, Hand | Cleaners of Vehicles and Equipment | Cargo and Freight Agents | Dispatchers, Except Police, Fire, and Ambulance | Light Truck Drivers | First-Line Supervisors of Transportation Workers, All Other | First-Line Supervisors of Passenger Attendants | Transportation, Storage, and Distribution Managers</t>
+  </si>
+  <si>
+    <t>All transportation workers not listed separately.</t>
+  </si>
+  <si>
+    <t>Perform transportation support work in roles not classified separately. | Service vehicles, aircraft, and vessels with fuel, water, and supplies. | Direct and guide vehicles into position using signals and marshalling equipment. | Load, unload, and secure baggage, cargo, and equipment. | Inspect equipment and report damage, leaks, or safety hazards. | Assist passengers with boarding, seating, and special requirements. | Operate ground support equipment, tugs, and service vehicles. | Clean and prepare vehicles and passenger areas between trips. | Maintain records of servicing, fuel dispensed, and equipment usage. | Follow safety, security, and hazardous materials handling procedures. | Communicate with operations staff using radios and signals. | Monitor terminal areas for safety, security, and traffic flow. | Assist with de-icing, tie-down, and weather-related preparations. | Respond to delays, emergencies, and irregular operations.</t>
+  </si>
+  <si>
+    <t>53-7011.00</t>
+  </si>
+  <si>
+    <t>Conveyor Operators and Tenders</t>
+  </si>
+  <si>
+    <t>Chipper Operator | Debarker Operator | Flumer | Line Operator | Machine Operator | Package Line Operator | Packaging Line Operator | Packing Line Operator | Process Operator | Strapper Operator</t>
+  </si>
+  <si>
+    <t>Control system software | Conveyor control software | Intelligrated InControlWare | Microsoft Excel | Microsoft Windows | SAP software | Sortation software</t>
+  </si>
+  <si>
+    <t>English Language | Mechanical | Public Safety and Security | Production and Processing</t>
+  </si>
+  <si>
+    <t>Control Precision | Oral Comprehension | Problem Sensitivity | Deductive Reasoning | Oral Expression | Inductive Reasoning | Multilimb Coordination | Perceptual Speed | Selective Attention | Near Vision | Speech Clarity | Far Vision | Static Strength | Manual Dexterity | Arm-Hand Steadiness | Flexibility of Closure | Written Expression | Visualization | Information Ordering | Depth Perception | Trunk Strength | Rate Control | Finger Dexterity | Hearing Sensitivity</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Pace Determined by Speed of Equipment | Importance of Being Exact or Accurate | Exposed to Contaminants | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Impact of Decisions on Co-workers or Company Results | Health and Safety of Other Workers | Work With or Contribute to a Work Group or Team | Time Pressure | Determine Tasks, Priorities and Goals | Exposed to Very Hot or Cold Temperatures | Frequency of Decision Making | Outdoors, Exposed to All Weather Conditions | Spend Time Standing | Coordinate or Lead Others in Accomplishing Work Activities</t>
+  </si>
+  <si>
+    <t>Adhesive Bonding Machine Operators and Tenders | Agricultural Equipment Operators | Crane and Tower Operators | Crushing, Grinding, and Polishing Machine Setters, Operators, and Tenders | Extruding and Drawing Machine Setters, Operators, and Tenders, Metal and Plastic | Extruding and Forming Machine Setters, Operators, and Tenders, Synthetic and Glass Fibers | Extruding, Forming, Pressing, and Compacting Machine Setters, Operators, and Tenders | Furnace, Kiln, Oven, Drier, and Kettle Operators and Tenders | Hoist and Winch Operators | Industrial Machinery Mechanics | Industrial Truck and Tractor Operators | Laborers and Freight, Stock, and Material Movers, Hand | Loading and Moving Machine Operators, Underground Mining | Machine Feeders and Offbearers | Maintenance Workers, Machinery | Operating Engineers and Other Construction Equipment Operators | Packaging and Filling Machine Operators and Tenders | Paper Goods Machine Setters, Operators, and Tenders | Rolling Machine Setters, Operators, and Tenders, Metal and Plastic | Tank Car, Truck, and Ship Loaders</t>
+  </si>
+  <si>
+    <t>Control or tend conveyors or conveyor systems that move materials or products to and from stockpiles, processing stations, departments, or vehicles. May control speed and routing of materials or products.</t>
+  </si>
+  <si>
+    <t>Affix identifying information to materials or products, using hand tools. | Clean, sterilize, and maintain equipment, machinery, and work stations, using hand tools, shovels, brooms, chemicals, hoses, and lubricants. | Collect samples of materials or products, checking them to ensure conformance to specifications or sending them to laboratories for analysis. | Contact workers in work stations or other departments to request movement of materials, products, or machinery, or to notify them of incoming shipments and their estimated delivery times. | Distribute materials, supplies, and equipment to work stations, using lifts and trucks. | Inform supervisors of equipment malfunctions that need to be addressed. | Join sections of conveyor frames at temporary working areas, and connect power units. | Load, unload, or adjust materials or products on conveyors by hand, by using lifts, hoists, and scoops, or by opening gates, chutes, or hoppers. | Manipulate controls, levers, and valves to start pumps, auxiliary equipment, or conveyors, and to adjust equipment positions, speeds, timing, and material flows. | Move, assemble, and connect hoses or nozzles to material hoppers, storage tanks, conveyor sections or chutes, and pumps. | Observe conveyor operations and monitor lights, dials, and gauges to maintain specified operating levels and to detect equipment malfunctions. | Observe packages moving along conveyors to identify packages, detect defective packaging, and perform quality control. | Position deflector bars, gates, chutes, or spouts to divert flow of materials from one conveyor onto another conveyor. | Press console buttons to deflect packages to predetermined accumulators or reject lines. | Read production and delivery schedules, and confer with supervisors, to determine sorting and transfer procedures, arrangement of packages on pallets, and destinations of loaded pallets. | Record production data such as weights, types, quantities, and storage locations of materials, as well as equipment performance problems and downtime. | Repair or replace equipment components or parts such as blades, rolls, and pumps. | Stop equipment or machinery and clear jams, using poles, bars, and hand tools, or remove damaged materials from conveyors. | Thread strapping through strapping tools and secure battens with strapping to form protective pallets around extrusions. | Weigh or measure materials and products, using scales or other measuring instruments, or read scales on conveyors that continually weigh products, to verify specified tonnages and prevent overloads.</t>
+  </si>
+  <si>
+    <t>53-7021.00</t>
+  </si>
+  <si>
+    <t>Crane and Tower Operators</t>
+  </si>
+  <si>
+    <t>Crane Operator | Heavy Equipment Operator | Machine Operator | Mobile Crane Operator | Overhead Crane Operator | Port Crane Operator | Scrap Crane Operator | Winchman | Woodyard Crane Operator</t>
+  </si>
+  <si>
+    <t>Crane operation control software | Inventory tracking software | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft Windows</t>
+  </si>
+  <si>
+    <t>Critical Thinking | Monitoring | Active Listening | Reading Comprehension | Speaking</t>
+  </si>
+  <si>
+    <t>Mechanical | Mathematics</t>
+  </si>
+  <si>
+    <t>Control Precision | Multilimb Coordination | Far Vision | Depth Perception | Rate Control | Reaction Time | Arm-Hand Steadiness | Problem Sensitivity | Response Orientation | Manual Dexterity | Selective Attention | Near Vision | Oral Expression | Speech Clarity | Speech Recognition | Visual Color Discrimination | Visualization | Perceptual Speed | Oral Comprehension | Glare Sensitivity | Finger Dexterity | Time Sharing | Spatial Orientation | Information Ordering | Deductive Reasoning</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Health and Safety of Other Workers | Contact With Others | Face-to-Face Discussions with Individuals and Within Teams | Importance of Being Exact or Accurate | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Work With or Contribute to a Work Group or Team | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Exposed to Contaminants | Indoors, Not Environmentally Controlled | Frequency of Decision Making | Freedom to Make Decisions | Exposed to Hazardous Equipment | Impact of Decisions on Co-workers or Company Results | Consequence of Error | Determine Tasks, Priorities and Goals | Exposed to Very Hot or Cold Temperatures | Time Pressure | Outdoors, Exposed to All Weather Conditions | Pace Determined by Speed of Equipment | In an Enclosed Vehicle or Operate Enclosed Equipment | Exposed to High Places | Work Outcomes and Results of Other Workers | Telephone Conversations | Spend Time Making Repetitive Motions</t>
+  </si>
+  <si>
+    <t>Aircraft Structure, Surfaces, Rigging, and Systems Assemblers | Construction Laborers | Continuous Mining Machine Operators | Conveyor Operators and Tenders | Excavating and Loading Machine and Dragline Operators, Surface Mining | Hoist and Winch Operators | Industrial Machinery Mechanics | Industrial Truck and Tractor Operators | Laborers and Freight, Stock, and Material Movers, Hand | Loading and Moving Machine Operators, Underground Mining | Machine Feeders and Offbearers | Maintenance Workers, Machinery | Millwrights | Mobile Heavy Equipment Mechanics, Except Engines | Operating Engineers and Other Construction Equipment Operators | Pile Driver Operators | Riggers | Structural Iron and Steel Workers | Tank Car, Truck, and Ship Loaders | Woodworking Machine Setters, Operators, and Tenders, Except Sawing</t>
+  </si>
+  <si>
+    <t>Operate mechanical boom and cable or tower and cable equipment to lift and move materials, machines, or products in many directions.</t>
+  </si>
+  <si>
+    <t>Clean, lubricate, and maintain mechanisms such as cables, pulleys, or grappling devices, making repairs, as necessary. | Determine load weights and check them against lifting capacities to prevent overload. | Direct helpers engaged in placing blocking or outrigging under cranes. | Direct truck drivers backing vehicles into loading bays and cover, uncover, or secure loads for delivery. | Inspect and adjust crane mechanisms or lifting accessories to prevent malfunctions or damage. | Inspect bundle packaging for conformance to regulations or customer requirements, and remove and batch packaging tickets. | Inspect cables or grappling devices for wear and install or replace cables, as needed. | Load or unload bundles from trucks, or move containers to storage bins, using moving equipment. | Move levers, depress foot pedals, or turn dials to operate cranes, cherry pickers, electromagnets, or other moving equipment for lifting, moving, or placing loads. | Review daily work or delivery schedules to determine orders, sequences of deliveries, or special loading instructions. | Weigh bundles, using floor scales, and record weights for company records.</t>
+  </si>
+  <si>
+    <t>53-7031.00</t>
+  </si>
+  <si>
+    <t>Dredge Operators</t>
+  </si>
+  <si>
+    <t>Dredge Operator | Dredger</t>
+  </si>
+  <si>
+    <t>Global positioning system GPS software | HYPACK DREDGEPACK | Programmable logic controller PLC software | Teledyne Odom Hydrographic ODOM eChart | Trimble HYDROpro | Web browser software</t>
+  </si>
+  <si>
+    <t>Critical Thinking</t>
+  </si>
+  <si>
+    <t>Mechanical | English Language | Public Safety and Security | Administration and Management</t>
+  </si>
+  <si>
+    <t>Control Precision | Multilimb Coordination | Depth Perception | Reaction Time | Manual Dexterity | Arm-Hand Steadiness | Near Vision | Far Vision | Problem Sensitivity | Hearing Sensitivity | Finger Dexterity | Selective Attention | Information Ordering | Speech Clarity | Speech Recognition | Auditory Attention</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Face-to-Face Discussions with Individuals and Within Teams | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Outdoors, Exposed to All Weather Conditions | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Contact With Others | Frequency of Decision Making | Exposed to Very Hot or Cold Temperatures | Exposed to Hazardous Equipment | Work With or Contribute to a Work Group or Team | Spend Time Making Repetitive Motions | Freedom to Make Decisions | Impact of Decisions on Co-workers or Company Results | Outdoors, Under Cover | Exposed to Minor Burns, Cuts, Bites, or Stings | Spend Time Sitting</t>
+  </si>
+  <si>
+    <t>Construction Laborers | Continuous Mining Machine Operators | Conveyor Operators and Tenders | Crane and Tower Operators | Derrick Operators, Oil and Gas | Earth Drillers, Except Oil and Gas | Excavating and Loading Machine and Dragline Operators, Surface Mining | Helpers--Extraction Workers | Hoist and Winch Operators | Industrial Truck and Tractor Operators | Maintenance Workers, Machinery | Operating Engineers and Other Construction Equipment Operators | Pile Driver Operators | Pump Operators, Except Wellhead Pumpers | Riggers | Rotary Drill Operators, Oil and Gas | Roustabouts, Oil and Gas | Sailors and Marine Oilers | Service Unit Operators, Oil and Gas | Wellhead Pumpers</t>
+  </si>
+  <si>
+    <t>Operate dredge to remove sand, gravel, or other materials in order to excavate and maintain navigable channels in waterways.</t>
+  </si>
+  <si>
+    <t>Direct or assist workers placing shore anchors and cables, laying additional pipes from dredges to shore, and pumping water from pontoons. | Lower anchor poles to verify depths of excavations, using winches, or scan depth gauges to determine depths of excavations. | Move levers to position dredges for excavation, to engage hydraulic pumps, to raise and lower suction booms, and to control rotation of cutterheads. | Pump water to clear machinery pipelines. | Start and stop engines to operate equipment. | Start power winches that draw in or let out cables to change positions of dredges, or pull in and let out cables manually.</t>
+  </si>
+  <si>
+    <t>53-7041.00</t>
+  </si>
+  <si>
+    <t>Hoist and Winch Operators</t>
+  </si>
+  <si>
+    <t>Hoist Operator | Hoistman | Material Handler | Service Operator | Winch Derrick Operator</t>
+  </si>
+  <si>
+    <t>Microsoft Excel | Microsoft Word</t>
+  </si>
+  <si>
+    <t>Critical Thinking | Monitoring | Active Listening | Speaking</t>
+  </si>
+  <si>
+    <t>Mechanical</t>
+  </si>
+  <si>
+    <t>Problem Sensitivity | Reaction Time | Depth Perception | Arm-Hand Steadiness | Control Precision | Multilimb Coordination | Near Vision | Deductive Reasoning | Oral Expression | Oral Comprehension | Manual Dexterity | Selective Attention | Speech Recognition | Rate Control | Far Vision | Hearing Sensitivity | Speech Clarity | Visualization | Inductive Reasoning | Perceptual Speed | Information Ordering | Gross Body Equilibrium | Extent Flexibility | Finger Dexterity | Category Flexibility | Auditory Attention | Response Orientation</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Health and Safety of Other Workers | Importance of Being Exact or Accurate | Face-to-Face Discussions with Individuals and Within Teams | Time Pressure | Work With or Contribute to a Work Group or Team | Freedom to Make Decisions | Exposed to Hazardous Equipment | Exposed to Contaminants | Impact of Decisions on Co-workers or Company Results | Exposed to High Places | Frequency of Decision Making | Determine Tasks, Priorities and Goals | Spend Time Making Repetitive Motions | Consequence of Error | Spend Time Bending or Twisting Your Body | Pace Determined by Speed of Equipment | Exposed to Cramped Work Space, Awkward Positions | In an Enclosed Vehicle or Operate Enclosed Equipment | Exposed to Hazardous Conditions | Contact With Others | Exposed to Whole Body Vibration | Exposed to Very Hot or Cold Temperatures | Indoors, Not Environmentally Controlled</t>
+  </si>
+  <si>
+    <t>Construction Laborers | Conveyor Operators and Tenders | Crane and Tower Operators | Dredge Operators | Electrical Power-Line Installers and Repairers | Excavating and Loading Machine and Dragline Operators, Surface Mining | Industrial Machinery Mechanics | Industrial Truck and Tractor Operators | Laborers and Freight, Stock, and Material Movers, Hand | Lathe and Turning Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Loading and Moving Machine Operators, Underground Mining | Maintenance Workers, Machinery | Mobile Heavy Equipment Mechanics, Except Engines | Multiple Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Operating Engineers and Other Construction Equipment Operators | Pile Driver Operators | Riggers | Roustabouts, Oil and Gas | Tank Car, Truck, and Ship Loaders | Woodworking Machine Setters, Operators, and Tenders, Except Sawing</t>
+  </si>
+  <si>
+    <t>Operate or tend hoists or winches to lift and pull loads using power-operated cable equipment.</t>
+  </si>
+  <si>
+    <t>Apply hand or foot brakes and move levers to lock hoists or winches. | Attach, fasten, and disconnect cables or lines to loads, materials, and equipment, using hand tools. | Climb ladders to position and set up vehicle-mounted derricks. | Move levers, pedals, and throttles to stop, start, and regulate speeds of hoist or winch drums in response to hand, bell, buzzer, telephone, loud-speaker, or whistle signals, or by observing dial indicators or cable marks. | Move or reposition hoists, winches, loads and materials, manually or using equipment and machines such as trucks, cars, and hand trucks. | Observe equipment gauges and indicators and hand signals of other workers to verify load positions or depths. | Oil winch drums so that cables will wind smoothly. | Operate compressed air, diesel, electric, gasoline, or steam-driven hoists or winches to control movement of cableways, cages, derricks, draglines, loaders, railcars, or skips. | Repair, maintain, and adjust equipment, using hand tools. | Select loads or materials according to weight and size specifications. | Signal and assist other workers loading or unloading materials. | Start engines of hoists or winches and use levers and pedals to wind or unwind cable on drums. | Tend auxiliary equipment, such as jacks, slings, cables, or stop blocks, to facilitate moving items or materials for further processing.</t>
+  </si>
+  <si>
+    <t>53-7051.00</t>
+  </si>
+  <si>
+    <t>Industrial Truck and Tractor Operators</t>
+  </si>
+  <si>
+    <t>Checker Loader | Fork Lift Technician | Fork Truck Driver | Forklift Driver | Forklift Operator | Lift Truck Operator | Shag Truck Driver | Spotter Driver | Tow Motor Operator | Truck Driver</t>
+  </si>
+  <si>
+    <t>ATMS StockTrack PLUS | Argos Software ABECAS Insight WMS | Autodesk AutoCAD | BarControl Enterprise Manager iBEM | IntelliTrack Warehouse Management System (WMS) | Inventory management systems | Lilly Software Associates VISUAL DCMS | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft Word | Motek Priya | RedPrairie DLx Warehouse | SAP software | SSA Global Supply Chain Management | Symphony GOLD | Warehouse management system WMS</t>
+  </si>
+  <si>
+    <t>Mathematics</t>
+  </si>
+  <si>
+    <t>Control Precision | Multilimb Coordination | Far Vision | Response Orientation | Manual Dexterity | Rate Control | Reaction Time | Depth Perception | Problem Sensitivity | Auditory Attention | Near Vision | Trunk Strength | Static Strength | Arm-Hand Steadiness | Selective Attention | Visualization | Spatial Orientation | Perceptual Speed | Information Ordering | Deductive Reasoning | Finger Dexterity | Oral Expression | Oral Comprehension | Peripheral Vision</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Importance of Being Exact or Accurate | Time Pressure | Exposed to Very Hot or Cold Temperatures | Face-to-Face Discussions with Individuals and Within Teams | In an Open Vehicle or Operating Equipment | Consequence of Error | Frequency of Decision Making | Indoors, Not Environmentally Controlled | Spend Time Making Repetitive Motions | Freedom to Make Decisions | Impact of Decisions on Co-workers or Company Results | Health and Safety of Other Workers | Contact With Others | Determine Tasks, Priorities and Goals | Work With or Contribute to a Work Group or Team | Exposed to Contaminants | Spend Time Standing | Coordinate or Lead Others in Accomplishing Work Activities | Pace Determined by Speed of Equipment | Spend Time Bending or Twisting Your Body | Level of Competition | Outdoors, Exposed to All Weather Conditions | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable</t>
+  </si>
+  <si>
+    <t>Agricultural Equipment Operators | Bus and Truck Mechanics and Diesel Engine Specialists | Continuous Mining Machine Operators | Conveyor Operators and Tenders | Crane and Tower Operators | Engine and Other Machine Assemblers | Excavating and Loading Machine and Dragline Operators, Surface Mining | Heavy and Tractor-Trailer Truck Drivers | Helpers--Production Workers | Hoist and Winch Operators | Laborers and Freight, Stock, and Material Movers, Hand | Loading and Moving Machine Operators, Underground Mining | Machine Feeders and Offbearers | Mobile Heavy Equipment Mechanics, Except Engines | Operating Engineers and Other Construction Equipment Operators | Outdoor Power Equipment and Other Small Engine Mechanics | Paving, Surfacing, and Tamping Equipment Operators | Pile Driver Operators | Riggers | Tank Car, Truck, and Ship Loaders</t>
+  </si>
+  <si>
+    <t>Operate industrial trucks or tractors equipped to move materials around a warehouse, storage yard, factory, construction site, or similar location.</t>
+  </si>
+  <si>
+    <t>Inspect product load for accuracy and safely move it around the warehouse or facility to ensure timely and complete delivery. | Manually or mechanically load or unload materials from pallets, skids, platforms, cars, lifting devices, or other transport vehicles. | Move controls to drive gasoline- or electric-powered trucks, cars, or tractors and transport materials between loading, processing, and storage areas. | Move levers or controls that operate lifting devices, such as forklifts, lift beams with swivel-hooks, hoists, or elevating platforms, to load, unload, transport, or stack material. | Operate or tend automatic stacking, loading, packaging, or cutting machines. | Perform routine maintenance on vehicles or auxiliary equipment, such as cleaning, lubricating, recharging batteries, fueling, or replacing liquefied-gas tank. | Position lifting devices under, over, or around loaded pallets, skids, or boxes and secure material or products for transport to designated areas. | Turn valves and open chutes to dump, spray, or release materials from dump cars or storage bins into hoppers. | Weigh materials or products and record weight or other production data on tags or labels.</t>
+  </si>
+  <si>
+    <t>53-7061.00</t>
+  </si>
+  <si>
+    <t>Cleaners of Vehicles and Equipment</t>
+  </si>
+  <si>
+    <t>Aircraft Cleaner | Automotive Detailer (Auto Detailer) | Bus Cleaner | Car Detailer | Car Washer | Cleaner | Detail Technician (Detail Tech) | Detailer | Reconditioner | Sanitation Truck Cleaner</t>
+  </si>
+  <si>
+    <t>Bella FSM Auto Detailing Service Software | BookFresh | Green Cloud KleanTRAC | Inventory tracking software | Microsoft Windows | Thoughtful Systems Scheduling Manager for Auto Detailing</t>
+  </si>
+  <si>
+    <t>Monitoring | Active Listening | Speaking | Critical Thinking</t>
+  </si>
+  <si>
+    <t>Near Vision | Manual Dexterity | Extent Flexibility | Multilimb Coordination | Problem Sensitivity | Stamina | Trunk Strength | Control Precision | Finger Dexterity</t>
+  </si>
+  <si>
+    <t>In an Enclosed Vehicle or Operate Enclosed Equipment | Exposed to Contaminants | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Spend Time Making Repetitive Motions | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Indoors, Not Environmentally Controlled | Freedom to Make Decisions | Time Pressure | Spend Time Standing | Determine Tasks, Priorities and Goals | Face-to-Face Discussions with Individuals and Within Teams | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Spend Time Walking or Running | Outdoors, Under Cover | Exposed to Very Hot or Cold Temperatures | Importance of Being Exact or Accurate | Spend Time Bending or Twisting Your Body | Work With or Contribute to a Work Group or Team | Health and Safety of Other Workers | Contact With Others</t>
+  </si>
+  <si>
+    <t>Cleaning, Washing, and Metal Pickling Equipment Operators and Tenders | Coating, Painting, and Spraying Machine Setters, Operators, and Tenders | Control and Valve Installers and Repairers, Except Mechanical Door | Dishwashers | Electric Motor, Power Tool, and Related Repairers | Furnace, Kiln, Oven, Drier, and Kettle Operators and Tenders | Grinding and Polishing Workers, Hand | Grinding, Lapping, Polishing, and Buffing Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Home Appliance Repairers | Industrial Machinery Mechanics | Janitors and Cleaners, Except Maids and Housekeeping Cleaners | Laborers and Freight, Stock, and Material Movers, Hand | Laundry and Dry-Cleaning Workers | Machine Feeders and Offbearers | Maintenance Workers, Machinery | Metal-Refining Furnace Operators and Tenders | Pump Operators, Except Wellhead Pumpers | Separating, Filtering, Clarifying, Precipitating, and Still Machine Setters, Operators, and Tenders | Septic Tank Servicers and Sewer Pipe Cleaners | Tool Grinders, Filers, and Sharpeners</t>
+  </si>
+  <si>
+    <t>Wash or otherwise clean vehicles, machinery, and other equipment. Use such materials as water, cleaning agents, brushes, cloths, and hoses.</t>
+  </si>
+  <si>
+    <t>Apply paints, dyes, polishes, reconditioners, waxes, or masking materials to vehicles to preserve, protect, or restore color or condition. | Clean and polish vehicle windows. | Clean the plastic work inside cars, using paintbrushes. | Connect hoses or lines to pumps or other equipment. | Disassemble and reassemble machines or equipment or remove and reattach vehicle parts or trim, using hand tools. | Drive vehicles to or from workshops or customers' workplaces or homes. | Fit boot spoilers, side skirts, or mud flaps to cars. | Inspect parts, equipment, or vehicles for cleanliness, damage, and compliance with standards or regulations. | Lubricate machinery, vehicles, or equipment or perform minor repairs or adjustments, using hand tools. | Maintain inventories of supplies. | Mix cleaning solutions, abrasive compositions, or other compounds, according to formulas. | Monitor operation of cleaning machines and stop machines or notify supervisors when malfunctions occur. | Pre-soak or rinse machine parts, equipment, or vehicles by immersing objects in cleaning solutions or water, manually or using hoists. | Press buttons to activate cleaning equipment or machines. | Rinse objects and place them on drying racks or use cloth, squeegees, or air compressors to dry surfaces. | Scrub, scrape, or spray machine parts, equipment, or vehicles, using scrapers, brushes, clothes, cleaners, disinfectants, insecticides, acid, abrasives, vacuums, or hoses. | Sweep, shovel, or vacuum loose debris or salvageable scrap into containers and remove containers from work areas. | Transport materials, equipment, or supplies to or from work areas, using carts or hoists. | Turn valves or disconnect hoses to eliminate water, cleaning solutions, or vapors from machinery or tanks. | Turn valves or handles on equipment to regulate pressure or flow of water, air, steam, or abrasives from sprayer nozzles.</t>
+  </si>
+  <si>
+    <t>53-7062.00</t>
+  </si>
+  <si>
+    <t>Laborers and Freight, Stock, and Material Movers, Hand</t>
+  </si>
+  <si>
+    <t>Laborer | Loader | Material Handler | Merchandise Pick Up Associate | Merchandise Receiving Associate | Receiver | Receiving Associate | Shipping and Receiving Materials Handler | Warehouse Worker</t>
+  </si>
+  <si>
+    <t>Apple Safari | Autodesk AutoCAD | Data entry software | FaceTime | Google Docs | Handheld computer device software | IBM Notes | Inventory management systems | Inventory tracking software | Machine control software | Microsoft Edge | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft Publisher | Microsoft Word | Mozilla Firefox | Oracle Database | SAP software | Warehouse management system WMS</t>
+  </si>
+  <si>
+    <t>Monitoring | Active Listening | Speaking | Critical Thinking | Reading Comprehension</t>
+  </si>
+  <si>
+    <t>Administration and Management | Customer and Personal Service | Public Safety and Security | Transportation | Production and Processing | Mathematics</t>
+  </si>
+  <si>
+    <t>Static Strength | Trunk Strength | Multilimb Coordination | Near Vision | Extent Flexibility | Stamina | Manual Dexterity | Oral Comprehension | Arm-Hand Steadiness | Selective Attention | Deductive Reasoning | Problem Sensitivity | Oral Expression | Far Vision | Dynamic Strength | Control Precision</t>
+  </si>
+  <si>
+    <t>Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Exposed to Contaminants | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Exposed to Very Hot or Cold Temperatures | Importance of Being Exact or Accurate | Outdoors, Exposed to All Weather Conditions | Exposed to Hazardous Equipment | Work With or Contribute to a Work Group or Team | Face-to-Face Discussions with Individuals and Within Teams | Importance of Repeating Same Tasks | Spend Time Standing | Determine Tasks, Priorities and Goals | Spend Time Making Repetitive Motions | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | In an Open Vehicle or Operating Equipment | Frequency of Decision Making | Outdoors, Under Cover | Freedom to Make Decisions | Contact With Others | Exposed to Minor Burns, Cuts, Bites, or Stings | Time Pressure | Consequence of Error | Impact of Decisions on Co-workers or Company Results | Exposed to Hazardous Conditions | Health and Safety of Other Workers | Indoors, Not Environmentally Controlled</t>
+  </si>
+  <si>
+    <t>Adhesive Bonding Machine Operators and Tenders | Cleaners of Vehicles and Equipment | Construction Laborers | Conveyor Operators and Tenders | Crane and Tower Operators | Crushing, Grinding, and Polishing Machine Setters, Operators, and Tenders | Cutting and Slicing Machine Setters, Operators, and Tenders | Helpers--Extraction Workers | Helpers--Production Workers | Hoist and Winch Operators | Industrial Truck and Tractor Operators | Laundry and Dry-Cleaning Workers | Machine Feeders and Offbearers | Maintenance Workers, Machinery | Packaging and Filling Machine Operators and Tenders | Packers and Packagers, Hand | Recycling and Reclamation Workers | Shipping, Receiving, and Inventory Clerks | Tank Car, Truck, and Ship Loaders | Weighers, Measurers, Checkers, and Samplers, Recordkeeping</t>
+  </si>
+  <si>
+    <t>Manually move freight, stock, luggage, or other materials, or perform other general labor. Includes all manual laborers not elsewhere classified.</t>
+  </si>
+  <si>
+    <t>Adjust controls to guide, position, or move equipment, such as cranes, booms, or cameras. | Assemble product containers or crates, using hand tools and precut lumber. | Attach identifying tags to containers or mark them with identifying information. | Attach slings, hooks, or other devices to lift cargo and guide loads. | Carry needed tools or supplies from storage or trucks and return them after use. | Connect electrical equipment to power sources so that it can be tested before use. | Install protective devices, such as bracing, padding, or strapping, to prevent shifting or damage to items being transported. | Maintain equipment storage areas to ensure that inventory is protected. | Move freight, stock, or other materials to and from storage or production areas, loading docks, delivery vehicles, ships, or containers, by hand or using trucks, tractors, or other equipment. | Pack containers and re-pack damaged containers. | Read work orders or receive oral instructions to determine work assignments or material or equipment needs. | Record numbers of units handled or moved, using daily production sheets or work tickets. | Sort cargo before loading and unloading.</t>
+  </si>
+  <si>
+    <t>53-7062.04</t>
+  </si>
+  <si>
+    <t>Recycling and Reclamation Workers</t>
+  </si>
+  <si>
+    <t>Bobcat Driver | Box Sorter | Convenience Recycle Center Technician (Convenience Recycle Center Tech) | Deconstruction and Decontamination Waste Operations Specialist (D and D Waste Operations Specialist) | Non-Ferrous Material Handler | Sort Line Worker | Sorter | Transfer Station Operator</t>
+  </si>
+  <si>
+    <t>Microsoft Excel | Microsoft Office software | Microsoft Word | Work scheduling software</t>
+  </si>
+  <si>
+    <t>Active Listening | Monitoring</t>
+  </si>
+  <si>
+    <t>Production and Processing | Mechanical | Administration and Management | Public Safety and Security | Education and Training | Customer and Personal Service | English Language | Personnel and Human Resources</t>
+  </si>
+  <si>
+    <t>Manual Dexterity | Control Precision | Near Vision | Multilimb Coordination | Arm-Hand Steadiness | Category Flexibility | Finger Dexterity | Trunk Strength | Reaction Time | Rate Control | Selective Attention | Perceptual Speed | Flexibility of Closure | Information Ordering | Oral Expression | Oral Comprehension | Depth Perception | Far Vision | Speed of Limb Movement</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Exposed to Contaminants | Spend Time Standing | Outdoors, Exposed to All Weather Conditions | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Spend Time Making Repetitive Motions | Contact With Others | Face-to-Face Discussions with Individuals and Within Teams | Exposed to Very Hot or Cold Temperatures | Outdoors, Under Cover | Work With or Contribute to a Work Group or Team | In an Open Vehicle or Operating Equipment | Health and Safety of Other Workers | Determine Tasks, Priorities and Goals | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Spend Time Bending or Twisting Your Body | Spend Time Walking or Running | Work Outcomes and Results of Other Workers | Freedom to Make Decisions | Time Pressure</t>
+  </si>
+  <si>
+    <t>Chemical Plant and System Operators | Cleaners of Vehicles and Equipment | Cleaning, Washing, and Metal Pickling Equipment Operators and Tenders | Conveyor Operators and Tenders | Hazardous Materials Removal Workers | Helpers--Extraction Workers | Helpers--Production Workers | Industrial Machinery Mechanics | Industrial Truck and Tractor Operators | Laborers and Freight, Stock, and Material Movers, Hand | Laundry and Dry-Cleaning Workers | Machine Feeders and Offbearers | Maintenance Workers, Machinery | Maintenance and Repair Workers, General | Packaging and Filling Machine Operators and Tenders | Recycling Coordinators | Refuse and Recyclable Material Collectors | Separating, Filtering, Clarifying, Precipitating, and Still Machine Setters, Operators, and Tenders | Septic Tank Servicers and Sewer Pipe Cleaners | Water and Wastewater Treatment Plant and System Operators</t>
+  </si>
+  <si>
+    <t>Prepare and sort materials or products for recycling. Identify and remove hazardous substances. Dismantle components of products such as appliances.</t>
+  </si>
+  <si>
+    <t>Clean materials, such as metals, according to recycling requirements. | Clean recycling yard by sweeping, raking, picking up broken glass and loose paper debris, or moving barrels and bins. | Clean, inspect, or lubricate recyclable collection equipment or perform routine maintenance or minor repairs on recycling equipment, such as star gears, finger sorters, destoners, belts, and grinders. | Collect and sort recyclable construction materials, such as concrete, drywall, plastics, or wood, into containers. | Collect recyclable materials from curbside for delivery to designated facilities. | Deposit recoverable materials into chutes or place materials on conveyor belts. | Extract chemicals from discarded appliances, such as air conditioners or refrigerators, using specialized machinery, such as refrigerant recovery equipment. | Operate automated refuse or manual recycling collection vehicles. | Operate balers to compress recyclable materials into bundles or bales. | Operate forklifts, pallet jacks, power lifts, or front-end loaders to load bales, bundles, or other heavy items onto trucks for shipping to smelters or other recycled materials processing facilities. | Operate processing equipment, such as fiber-sorters and grinders, to sort, crush, or grind recyclable materials. | Record logs of recycled materials or waste chemicals removed from products. | Sort materials, such as metals, glass, wood, paper or plastics, into appropriate containers for recycling. | Sort metals to separate high-grade metals, such as copper, brass, and aluminum, for recycling.</t>
+  </si>
+  <si>
+    <t>53-7063.00</t>
+  </si>
+  <si>
+    <t>Machine Feeders and Offbearers</t>
+  </si>
+  <si>
+    <t>Cotton Tipper | Dryer Feeder | Feeder | Lug Loader | Machine Feeder | Offbearer | Sawmill Worker | Sewing Line Baler | Tube Puller</t>
+  </si>
+  <si>
+    <t>Machine operation software | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Work time tracking software</t>
+  </si>
+  <si>
+    <t>Monitoring</t>
+  </si>
+  <si>
+    <t>Production and Processing | Mechanical | Mathematics</t>
+  </si>
+  <si>
+    <t>Arm-Hand Steadiness | Control Precision | Rate Control | Reaction Time | Near Vision | Oral Expression | Problem Sensitivity | Oral Comprehension | Static Strength | Manual Dexterity | Information Ordering</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Spend Time Standing | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Pace Determined by Speed of Equipment | Face-to-Face Discussions with Individuals and Within Teams | Importance of Being Exact or Accurate | Contact With Others | Work With or Contribute to a Work Group or Team | Exposed to Contaminants | Time Pressure | Spend Time Making Repetitive Motions</t>
+  </si>
+  <si>
+    <t>Adhesive Bonding Machine Operators and Tenders | Crushing, Grinding, and Polishing Machine Setters, Operators, and Tenders | Cutters and Trimmers, Hand | Cutting and Slicing Machine Setters, Operators, and Tenders | Cutting, Punching, and Press Machine Setters, Operators, and Tenders, Metal and Plastic | Extruding and Forming Machine Setters, Operators, and Tenders, Synthetic and Glass Fibers | Extruding, Forming, Pressing, and Compacting Machine Setters, Operators, and Tenders | Furnace, Kiln, Oven, Drier, and Kettle Operators and Tenders | Grinding and Polishing Workers, Hand | Grinding, Lapping, Polishing, and Buffing Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Industrial Machinery Mechanics | Laborers and Freight, Stock, and Material Movers, Hand | Milling and Planing Machine Setters, Operators, and Tenders, Metal and Plastic | Packaging and Filling Machine Operators and Tenders | Packers and Packagers, Hand | Paper Goods Machine Setters, Operators, and Tenders | Rolling Machine Setters, Operators, and Tenders, Metal and Plastic | Textile Cutting Machine Setters, Operators, and Tenders | Tool Grinders, Filers, and Sharpeners | Woodworking Machine Setters, Operators, and Tenders, Except Sawing</t>
+  </si>
+  <si>
+    <t>Feed materials into or remove materials from machines or equipment that is automatic or tended by other workers.</t>
+  </si>
+  <si>
+    <t>Add chemicals, solutions, or ingredients to machines or equipment as required by the manufacturing process. | Clean and maintain machinery, equipment, and work areas to ensure proper functioning and safe working conditions. | Fasten, package, or stack materials and products, using hand tools and fastening equipment. | Identify and mark materials, products, and samples, following instructions. | Inspect materials and products for defects, and to ensure conformance to specifications. | Load materials and products into machines and equipment, or onto conveyors, using hand tools and moving devices. | Open and close gates of belt and pneumatic conveyors on machines that are fed directly from preceding machines. | Push dual control buttons and move controls to start, stop, or adjust machinery and equipment. | Record production and operational data, such as amount of materials processed. | Remove materials and products from machines and equipment, and place them in boxes, trucks or conveyors, using hand tools and moving devices. | Shovel or scoop materials into containers, machines, or equipment for processing, storage, or transport. | Transfer materials and products to and from machinery and equipment, using industrial trucks or hand trucks. | Weigh or measure materials or products to ensure conformance to specifications.</t>
+  </si>
+  <si>
+    <t>53-7064.00</t>
+  </si>
+  <si>
+    <t>Packers and Packagers, Hand</t>
+  </si>
+  <si>
+    <t>Bagger | Crater | Mini Shifter | Pack Out Operator | Packager | Packaging Specialist | Packer | Picker and Packer | Sacker | Selector Packer</t>
+  </si>
+  <si>
+    <t>Autodesk AutoCAD | Inventory tracking software | Microsoft Excel | Microsoft Office software | Microsoft Word | SAP software</t>
+  </si>
+  <si>
+    <t>Production and Processing | Customer and Personal Service</t>
+  </si>
+  <si>
+    <t>Near Vision | Trunk Strength | Problem Sensitivity | Speech Recognition | Static Strength | Multilimb Coordination | Manual Dexterity | Oral Comprehension</t>
+  </si>
+  <si>
+    <t>Face-to-Face Discussions with Individuals and Within Teams | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Importance of Being Exact or Accurate | Spend Time Standing | Indoors, Not Environmentally Controlled | Contact With Others | Time Pressure | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Work With or Contribute to a Work Group or Team | Spend Time Making Repetitive Motions | Importance of Repeating Same Tasks | Exposed to Contaminants | Health and Safety of Other Workers | Coordinate or Lead Others in Accomplishing Work Activities | Frequency of Decision Making | Work Outcomes and Results of Other Workers</t>
+  </si>
+  <si>
+    <t>Adhesive Bonding Machine Operators and Tenders | Crushing, Grinding, and Polishing Machine Setters, Operators, and Tenders | Cutters and Trimmers, Hand | Cutting and Slicing Machine Setters, Operators, and Tenders | Extruding, Forming, Pressing, and Compacting Machine Setters, Operators, and Tenders | Food and Tobacco Roasting, Baking, and Drying Machine Operators and Tenders | Graders and Sorters, Agricultural Products | Grinding and Polishing Workers, Hand | Helpers--Production Workers | Laborers and Freight, Stock, and Material Movers, Hand | Laundry and Dry-Cleaning Workers | Machine Feeders and Offbearers | Mixing and Blending Machine Setters, Operators, and Tenders | Molders, Shapers, and Casters, Except Metal and Plastic | Packaging and Filling Machine Operators and Tenders | Paper Goods Machine Setters, Operators, and Tenders | Separating, Filtering, Clarifying, Precipitating, and Still Machine Setters, Operators, and Tenders | Sewing Machine Operators | Weighers, Measurers, Checkers, and Samplers, Recordkeeping | Woodworking Machine Setters, Operators, and Tenders, Except Sawing</t>
+  </si>
+  <si>
+    <t>Pack or package by hand a wide variety of products and materials.</t>
+  </si>
+  <si>
+    <t>Assemble, line, and pad cartons, crates, and containers, using hand tools. | Clean containers, materials, supplies, or work areas, using cleaning solutions and hand tools. | Examine and inspect containers, materials, or products to ensure that product quality and packing specifications are met. | Load materials and products into package processing equipment. | Mark and label containers, container tags, or products, using marking tools. | Measure, weigh, and count products and materials. | Obtain, move, and sort products, materials, containers, and orders, using hand tools. | Place or pour products or materials into containers, using hand tools and equipment, or fill containers from spouts or chutes. | Record product, packaging, and order information on specified forms and records. | Remove completed or defective products or materials, placing them on moving equipment, such as conveyors, or in specified areas, such as loading docks. | Seal containers or materials, using glues, fasteners, nails, and hand tools. | Transport packages to customers' vehicles.</t>
+  </si>
+  <si>
+    <t>53-7065.00</t>
+  </si>
+  <si>
+    <t>Stockers and Order Fillers</t>
+  </si>
+  <si>
+    <t>Checker Stocker | Inventory Specialist | Inventory Technician (Inventory Tech) | Label Maker | Marking Clerk | Order Filler | Order Picker | Stock Clerk | Stocker | Warehouse Technician (Warehouse Tech)</t>
+  </si>
+  <si>
+    <t>Apple Safari | Data entry software | Eko | Email software | Google Docs | Handheld computer device software | Inventory management systems | Inventory tracking software | Microsoft Access | Microsoft Dynamics GP | Microsoft Edge | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft Windows | Microsoft Word | Mozilla Firefox | Oracle JD Edwards EnterpriseOne | Ordering software | SAP software | Voice picking software | Warehouse management system WMS | Work scheduling software</t>
+  </si>
+  <si>
+    <t>Active Listening | Reading Comprehension</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | English Language</t>
+  </si>
+  <si>
+    <t>Near Vision | Oral Comprehension | Trunk Strength | Speech Clarity | Extent Flexibility | Manual Dexterity | Oral Expression | Written Comprehension | Multilimb Coordination | Arm-Hand Steadiness | Selective Attention | Information Ordering | Speech Recognition | Static Strength</t>
+  </si>
+  <si>
+    <t>Face-to-Face Discussions with Individuals and Within Teams | Contact With Others | Indoors, Environmentally Controlled | Work With or Contribute to a Work Group or Team | Deal With External Customers or the Public in General | Importance of Being Exact or Accurate | Spend Time Standing | Telephone Conversations | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | Importance of Repeating Same Tasks</t>
+  </si>
+  <si>
+    <t>Cashiers | Counter and Rental Clerks | File Clerks | First-Line Supervisors of Helpers, Laborers, and Material Movers, Hand | First-Line Supervisors of Material-Moving Machine and Vehicle Operators | First-Line Supervisors of Retail Sales Workers | Laborers and Freight, Stock, and Material Movers, Hand | Logistics Analysts | Mail Clerks and Mail Machine Operators, Except Postal Service | Office Clerks, General | Order Clerks | Packers and Packagers, Hand | Postal Service Clerks | Postal Service Mail Sorters, Processors, and Processing Machine Operators | Procurement Clerks | Production, Planning, and Expediting Clerks | Recycling and Reclamation Workers | Retail Salespersons | Shipping, Receiving, and Inventory Clerks | Weighers, Measurers, Checkers, and Samplers, Recordkeeping</t>
+  </si>
+  <si>
+    <t>Receive, store, and issue merchandise, materials, equipment, and other items from stockroom, warehouse, or storage yard to fill shelves, racks, tables, or customers' orders. May operate power equipment to fill orders. May mark prices on merchandise and set up sales displays.</t>
+  </si>
+  <si>
+    <t>Answer customers' questions about merchandise and advise customers on merchandise selection. | Clean and maintain supplies, tools, equipment, and storage areas to ensure compliance with safety regulations. | Clean display cases, shelves, and aisles. | Compare merchandise invoices to items actually received to ensure that shipments are correct. | Complete order receipts. | Compute prices of items or groups of items. | Design and set up advertising signs and displays of merchandise on shelves, counters, or tables to attract customers and promote sales. | Determine proper storage methods, identification, and stock location, based on turnover, environmental factors, and physical capabilities of facilities. | Dispose of damaged or defective items, or return them to vendors. | Examine and inspect stock items for wear or defects, reporting any damage to supervisors. | Issue or distribute materials, products, parts, and supplies to customers or coworkers, based on information from incoming requisitions. | Itemize and total customer merchandise selection at checkout counter, using cash register, and accept cash or charge card for purchases. | Keep records of out-going orders. | Keep records on the use or damage of stock or stock-handling equipment. | Mark stock items, using identification tags, stamps, electric marking tools, or other labeling equipment. | Obtain merchandise from bins or shelves. | Operate equipment such as forklifts. | Pack and unpack items to be stocked on shelves in stockrooms, warehouses, or storage yards. | Pack customer purchases in bags or cartons. | Provide assistance or direction to other stockroom, warehouse, or storage yard workers. | Read orders to ascertain catalog numbers, sizes, colors, and quantities of merchandise. | Receive and count stock items, and record data manually or on computer. | Receive, unload, open, unpack, or issue sales floor merchandise. | Recommend disposal of excess, defective, or obsolete stock. | Requisition merchandise from supplier, based on available space, merchandise on hand, customer demand, or advertised specials. | Stamp, attach, or change price tags on merchandise, referring to price list. | Stock shelves, racks, cases, bins, and tables with new or transferred merchandise. | Store items in an orderly and accessible manner in warehouses, tool rooms, supply rooms, or other areas. | Take inventory or examine merchandise to identify items to be reordered or replenished. | Transport packages to customers' vehicles.</t>
+  </si>
+  <si>
+    <t>53-7071.00</t>
+  </si>
+  <si>
+    <t>Gas Compressor and Gas Pumping Station Operators</t>
+  </si>
+  <si>
+    <t>Compressor Operator | Compressor Station Operator | Compressor Technician | Fill Plant Operator | Filler | Liquefied Natural Gas Plant Operator (LNG Plant Operator) | Pipeline Technician | Plant Operator | Terminal Operator</t>
+  </si>
+  <si>
+    <t>Computerized maintenance management system CMMS | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft Word | Programmable logic controller PLC software</t>
+  </si>
+  <si>
+    <t>Critical Thinking | Monitoring | Reading Comprehension | Active Listening | Writing | Speaking</t>
+  </si>
+  <si>
+    <t>Production and Processing | Mechanical | Public Safety and Security | Administration and Management | Chemistry | English Language | Education and Training | Mathematics | Computers and Electronics | Physics | Engineering and Technology | Customer and Personal Service</t>
+  </si>
+  <si>
+    <t>Arm-Hand Steadiness | Manual Dexterity | Finger Dexterity | Problem Sensitivity | Near Vision | Multilimb Coordination | Control Precision | Perceptual Speed | Reaction Time | Information Ordering | Far Vision | Selective Attention | Flexibility of Closure | Inductive Reasoning | Deductive Reasoning | Oral Expression | Written Comprehension | Oral Comprehension | Speech Clarity | Auditory Attention | Rate Control | Written Expression | Time Sharing | Category Flexibility</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Outdoors, Exposed to All Weather Conditions | E-Mail | Health and Safety of Other Workers | Telephone Conversations | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Exposed to Contaminants | Exposed to Very Hot or Cold Temperatures | Work With or Contribute to a Work Group or Team | Face-to-Face Discussions with Individuals and Within Teams | Exposed to Hazardous Equipment | In an Enclosed Vehicle or Operate Enclosed Equipment | Consequence of Error | Determine Tasks, Priorities and Goals | Freedom to Make Decisions | Importance of Being Exact or Accurate | Exposed to Hazardous Conditions | Contact With Others | Outdoors, Under Cover | Impact of Decisions on Co-workers or Company Results | Frequency of Decision Making | Indoors, Not Environmentally Controlled | Time Pressure | Importance of Repeating Same Tasks | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Physical Proximity | Work Outcomes and Results of Other Workers | Pace Determined by Speed of Equipment</t>
+  </si>
+  <si>
+    <t>Biomass Plant Technicians | Chemical Equipment Operators and Tenders | Chemical Plant and System Operators | Control and Valve Installers and Repairers, Except Mechanical Door | Engine and Other Machine Assemblers | Furnace, Kiln, Oven, Drier, and Kettle Operators and Tenders | Gas Plant Operators | Geothermal Technicians | Heat Treating Equipment Setters, Operators, and Tenders, Metal and Plastic | Hydroelectric Plant Technicians | Industrial Machinery Mechanics | Maintenance Workers, Machinery | Metal-Refining Furnace Operators and Tenders | Petroleum Pump System Operators, Refinery Operators, and Gaugers | Power Plant Operators | Pump Operators, Except Wellhead Pumpers | Separating, Filtering, Clarifying, Precipitating, and Still Machine Setters, Operators, and Tenders | Stationary Engineers and Boiler Operators | Water and Wastewater Treatment Plant and System Operators | Wellhead Pumpers</t>
+  </si>
+  <si>
+    <t>Operate steam-, gas-, electric motor-, or internal combustion-engine driven compressors. Transmit, compress, or recover gases, such as butane, nitrogen, hydrogen, and natural gas.</t>
+  </si>
+  <si>
+    <t>Adjust valves and equipment to obtain specified performance. | Clean, lubricate, and adjust equipment, and replace filters and gaskets, using hand tools. | Connect pipelines between pumps and containers that are being filled or emptied. | Maintain each station by performing general housekeeping duties such as painting, washing, and cleaning. | Monitor meters and pressure gauges to determine consumption rate variations, temperatures, and pressures. | Move controls and turn valves to start compressor engines, pumps, and auxiliary equipment. | Operate power-driven pumps that transfer liquids, semi-liquids, gases, or powdered materials. | Read gas meters, and maintain records of the amounts of gas received and dispensed from holders. | Record instrument readings and operational changes in operating logs. | Respond to problems by adjusting control room equipment or instructing other personnel to adjust equipment at problem locations or in other control areas. | Submit daily reports on facility operations. | Take samples of gases and conduct chemical tests to determine gas quality and sulfur or moisture content, or send samples to laboratories for analysis. | Turn knobs or switches to regulate pressures.</t>
+  </si>
+  <si>
+    <t>53-7072.00</t>
+  </si>
+  <si>
+    <t>Pump Operators, Except Wellhead Pumpers</t>
+  </si>
+  <si>
+    <t>Boom Pump Operator | Chemical Pumper | Day Light Relief Operator | Outside Operator | Pipeline Dispatch Operator | Pipeline Operator | Pump Operator | Pump Station Operator | Pumper | Tank Farm Operator</t>
+  </si>
+  <si>
+    <t>Computerized maintenance management system CMMS | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft Word | Operational databases | Supervisory control and data acquisition SCADA software</t>
+  </si>
+  <si>
+    <t>Monitoring | Reading Comprehension | Active Listening | Speaking | Critical Thinking</t>
+  </si>
+  <si>
+    <t>Production and Processing | English Language | Mechanical | Mathematics</t>
+  </si>
+  <si>
+    <t>Near Vision | Oral Comprehension | Problem Sensitivity | Perceptual Speed | Oral Expression | Control Precision | Information Ordering | Written Expression | Manual Dexterity | Arm-Hand Steadiness | Selective Attention | Flexibility of Closure | Deductive Reasoning | Written Comprehension | Far Vision | Multilimb Coordination | Visualization | Category Flexibility | Inductive Reasoning | Finger Dexterity | Speech Clarity | Speech Recognition | Auditory Attention | Hearing Sensitivity | Depth Perception | Visual Color Discrimination | Extent Flexibility | Trunk Strength | Static Strength | Reaction Time | Rate Control</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Exposed to Contaminants | In an Enclosed Vehicle or Operate Enclosed Equipment | Outdoors, Exposed to All Weather Conditions | Face-to-Face Discussions with Individuals and Within Teams | Telephone Conversations | Health and Safety of Other Workers | Frequency of Decision Making | Contact With Others | Exposed to Hazardous Equipment | Exposed to Very Hot or Cold Temperatures | Impact of Decisions on Co-workers or Company Results | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Determine Tasks, Priorities and Goals | Importance of Repeating Same Tasks | Freedom to Make Decisions | Work With or Contribute to a Work Group or Team | Importance of Being Exact or Accurate | Spend Time Making Repetitive Motions | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Consequence of Error | Exposed to Hazardous Conditions</t>
+  </si>
+  <si>
+    <t>Biomass Plant Technicians | Chemical Equipment Operators and Tenders | Chemical Plant and System Operators | Cleaning, Washing, and Metal Pickling Equipment Operators and Tenders | Control and Valve Installers and Repairers, Except Mechanical Door | Furnace, Kiln, Oven, Drier, and Kettle Operators and Tenders | Gas Compressor and Gas Pumping Station Operators | Gas Plant Operators | Industrial Machinery Mechanics | Maintenance Workers, Machinery | Metal-Refining Furnace Operators and Tenders | Petroleum Pump System Operators, Refinery Operators, and Gaugers | Power Plant Operators | Separating, Filtering, Clarifying, Precipitating, and Still Machine Setters, Operators, and Tenders | Septic Tank Servicers and Sewer Pipe Cleaners | Service Unit Operators, Oil and Gas | Stationary Engineers and Boiler Operators | Tank Car, Truck, and Ship Loaders | Water and Wastewater Treatment Plant and System Operators | Wellhead Pumpers</t>
+  </si>
+  <si>
+    <t>Tend, control, or operate power-driven, stationary, or portable pumps and manifold systems to transfer gases, oil, other liquids, slurries, or powdered materials to and from various vessels and processes.</t>
+  </si>
+  <si>
+    <t>Add chemicals and solutions to tanks to ensure that specifications are met. | Clean, lubricate, and repair pumps and vessels, using hand tools and equipment. | Collect and deliver sample solutions for laboratory analysis. | Communicate with other workers, using signals, radios, or telephones, to start and stop flows of materials or substances. | Connect hoses and pipelines to pumps and vessels prior to material transfer, using hand tools. | Monitor gauges and flowmeters and inspect equipment to ensure that tank levels, temperatures, chemical amounts, and pressures are at specified levels, reporting abnormalities as necessary. | Plan movement of products through lines to processing, storage, and shipping units, using knowledge of interconnections and capacities of pipelines, valve manifolds, pumps, and tankage. | Pump two or more materials into one tank to blend mixtures. | Read operating schedules or instructions or receive verbal orders to determine amounts to be pumped. | Record operating data such as products and quantities pumped, stocks used, gauging results, and operating times. | Tend auxiliary equipment such as water treatment and refrigeration units, and heat exchangers. | Tend vessels that store substances such as gases, liquids, slurries, or powdered materials, checking levels of substances by using calibrated rods or by reading mercury gauges and tank charts. | Test materials and solutions, using testing equipment. | Turn valves and start pumps to start or regulate flows of substances such as gases, liquids, slurries, or powdered materials.</t>
+  </si>
+  <si>
+    <t>53-7073.00</t>
+  </si>
+  <si>
+    <t>Wellhead Pumpers</t>
+  </si>
+  <si>
+    <t>Field Operator | Lease Attendant | Lease Operator | Oilfield Plant Operator | Pumper | Well Field Technician | Well Head Pumper | Well Tender | Wellhead Pumper</t>
+  </si>
+  <si>
+    <t>Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft Word | Moxa software | Operational databases | SAP software | Supervisory control and data acquisition SCADA software</t>
+  </si>
+  <si>
+    <t>Monitoring | Critical Thinking | Speaking</t>
+  </si>
+  <si>
+    <t>Problem Sensitivity | Near Vision | Information Ordering | Control Precision | Multilimb Coordination | Reaction Time | Static Strength | Manual Dexterity | Perceptual Speed | Inductive Reasoning | Deductive Reasoning | Oral Expression | Arm-Hand Steadiness | Response Orientation | Speech Clarity | Speech Recognition | Trunk Strength</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Exposed to Contaminants | Outdoors, Exposed to All Weather Conditions | In an Enclosed Vehicle or Operate Enclosed Equipment | Telephone Conversations | Exposed to Hazardous Conditions | Determine Tasks, Priorities and Goals | Freedom to Make Decisions | Exposed to Very Hot or Cold Temperatures | Frequency of Decision Making | Face-to-Face Discussions with Individuals and Within Teams | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Contact With Others | Exposed to Minor Burns, Cuts, Bites, or Stings | Impact of Decisions on Co-workers or Company Results | E-Mail | Exposed to Hazardous Equipment | Work With or Contribute to a Work Group or Team | Importance of Being Exact or Accurate | Consequence of Error | Exposed to Extremely Bright or Inadequate Lighting Conditions | Importance of Repeating Same Tasks | Time Pressure</t>
+  </si>
+  <si>
+    <t>Biofuels Processing Technicians | Biomass Plant Technicians | Chemical Plant and System Operators | Derrick Operators, Oil and Gas | Earth Drillers, Except Oil and Gas | Gas Compressor and Gas Pumping Station Operators | Gas Plant Operators | Geothermal Production Managers | Geothermal Technicians | Hydroelectric Plant Technicians | Petroleum Engineers | Petroleum Pump System Operators, Refinery Operators, and Gaugers | Power Plant Operators | Pump Operators, Except Wellhead Pumpers | Rotary Drill Operators, Oil and Gas | Roustabouts, Oil and Gas | Separating, Filtering, Clarifying, Precipitating, and Still Machine Setters, Operators, and Tenders | Service Unit Operators, Oil and Gas | Stationary Engineers and Boiler Operators | Water and Wastewater Treatment Plant and System Operators</t>
+  </si>
+  <si>
+    <t>Operate power pumps and auxiliary equipment to produce flow of oil or gas from wells in oil field.</t>
+  </si>
+  <si>
+    <t>Attach pumps and hoses to wellheads. | Change water filters. | Gauge oil and gas production. | Mix acids, chemicals, or dry cement as required for a specific job. | Monitor control panels during pumping operations to ensure that materials are being pumped at the correct pressure, density, rate, and concentration. | Monitor pumps and flow lines for gas and fluid leaks. | Open valves to return compressed gas to bottoms of specified wells to repressurize them and force oil to surface. | Operate engines and pumps to shut off wells according to production schedules, and to switch flow of oil into storage tanks. | Perform routine maintenance on vehicles and equipment. | Prepare trucks and equipment necessary for the type of pumping service required. | Repair gas and oil meters and gauges. | Start compressor engines and divert oil from storage tanks into compressor units and auxiliary equipment to recover natural gas from oil. | Supervise oil pumpers and other workers engaged in producing oil from wells. | Unload and assemble pipes and pumping equipment, using hand tools.</t>
+  </si>
+  <si>
+    <t>53-7081.00</t>
+  </si>
+  <si>
+    <t>Refuse and Recyclable Material Collectors</t>
+  </si>
+  <si>
+    <t>Front Load Trash Truck Driver | Garbage Man | Recycle Driver | Refuse Collector | Roll Off Container Truck Driver | Roll Off Truck Driver | Sanitation Laborer | Swamper | Trash Collector | Truck Driver</t>
+  </si>
+  <si>
+    <t>AMCS Platform | Computerized maintenance management system CMMS | Dossier software | Fleet management software | Global positioning system GPS software | Mileage logging software | Payroll software | Routeware software | Squeegee | WAM software</t>
+  </si>
+  <si>
+    <t>Multilimb Coordination | Arm-Hand Steadiness | Static Strength | Manual Dexterity | Reaction Time | Trunk Strength | Near Vision | Far Vision | Oral Comprehension | Extent Flexibility</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Outdoors, Exposed to All Weather Conditions | In an Enclosed Vehicle or Operate Enclosed Equipment | Spend Time Making Repetitive Motions | Exposed to Contaminants | Exposed to Very Hot or Cold Temperatures | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Freedom to Make Decisions | Time Pressure | Exposed to Hazardous Equipment | Face-to-Face Discussions with Individuals and Within Teams | Determine Tasks, Priorities and Goals | Contact With Others | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable</t>
+  </si>
+  <si>
+    <t>Cleaners of Vehicles and Equipment | Conveyor Operators and Tenders | Crane and Tower Operators | Excavating and Loading Machine and Dragline Operators, Surface Mining | Hazardous Materials Removal Workers | Heavy and Tractor-Trailer Truck Drivers | Helpers--Extraction Workers | Highway Maintenance Workers | Hoist and Winch Operators | Industrial Truck and Tractor Operators | Laborers and Freight, Stock, and Material Movers, Hand | Light Truck Drivers | Loading and Moving Machine Operators, Underground Mining | Operating Engineers and Other Construction Equipment Operators | Pile Driver Operators | Recycling Coordinators | Recycling and Reclamation Workers | Septic Tank Servicers and Sewer Pipe Cleaners | Tank Car, Truck, and Ship Loaders | Transportation Vehicle, Equipment and Systems Inspectors, Except Aviation</t>
+  </si>
+  <si>
+    <t>Collect and dump refuse or recyclable materials from containers into truck. May drive truck.</t>
+  </si>
+  <si>
+    <t>Check road or weather conditions to determine how routes will be affected. | Clean trucks or compactor bodies after routes have been completed. | Communicate with dispatchers concerning delays, unsafe sites, accidents, equipment breakdowns, or other maintenance problems. | Dismount garbage trucks to collect garbage and remount trucks to ride to the next collection point. | Drive trucks, following established routes, through residential streets or alleys or through business or industrial areas. | Dump refuse or recyclable materials at disposal sites. | Fill out defective equipment reports. | Inspect trucks prior to beginning routes to ensure safe operating condition. | Make special pickups of recyclable materials, such as food scraps, used oil, discarded computers, or other electronic items. | Operate automated or semi-automated hoisting devices that raise refuse bins and dump contents into openings in truck bodies. | Operate equipment that compresses collected refuse. | Organize schedules for refuse collection. | Refuel trucks or add other fluids, such as oil or brake fluid. | Tag garbage or recycling containers to inform customers of problems, such as excess garbage or inclusion of items that are not permitted.</t>
+  </si>
+  <si>
+    <t>53-7121.00</t>
+  </si>
+  <si>
+    <t>Tank Car, Truck, and Ship Loaders</t>
+  </si>
+  <si>
+    <t>Load Out Person | Loader | Loader Operator | Loading Operator | Oil Movements Operator | PVC Loader (Polyvinyl Chloride Loader) | Rail Car Loader | Tank Car Loader | Tankerman | Truck Loader</t>
+  </si>
+  <si>
+    <t>CompuWeigh GMS | Distributed control system DCS | Linux | Microsoft Excel | Microsoft Office software | SAP software | Warehouse management system WMS</t>
+  </si>
+  <si>
+    <t>Reading Comprehension | Monitoring | Critical Thinking | Speaking | Writing | Active Listening</t>
+  </si>
+  <si>
+    <t>Transportation | Production and Processing | English Language | Public Safety and Security</t>
+  </si>
+  <si>
+    <t>Control Precision | Multilimb Coordination | Far Vision | Rate Control | Manual Dexterity | Problem Sensitivity | Depth Perception | Reaction Time | Perceptual Speed | Static Strength | Near Vision | Arm-Hand Steadiness | Oral Comprehension | Speech Clarity | Speech Recognition | Selective Attention | Finger Dexterity | Oral Expression | Extent Flexibility | Stamina | Trunk Strength | Visualization | Time Sharing | Auditory Attention | Hearing Sensitivity | Flexibility of Closure | Information Ordering | Written Expression | Written Comprehension | Gross Body Equilibrium</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Face-to-Face Discussions with Individuals and Within Teams | Outdoors, Exposed to All Weather Conditions | Consequence of Error | Exposed to Contaminants | Exposed to Hazardous Conditions | Work With or Contribute to a Work Group or Team | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Health and Safety of Other Workers | Contact With Others | Time Pressure | Importance of Being Exact or Accurate | Importance of Repeating Same Tasks | Frequency of Decision Making | Telephone Conversations | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Exposed to Very Hot or Cold Temperatures | In an Enclosed Vehicle or Operate Enclosed Equipment | Exposed to Hazardous Equipment | Exposed to High Places | Wear Specialized Protective or Safety Equipment such as Breathing Apparatus, Safety Harness, Full Protection Suits, or Radiation Protection | Impact of Decisions on Co-workers or Company Results | Coordinate or Lead Others in Accomplishing Work Activities | E-Mail | Freedom to Make Decisions | Indoors, Not Environmentally Controlled | Determine Tasks, Priorities and Goals | Spend Time Making Repetitive Motions | Conflict Situations | Work Outcomes and Results of Other Workers | Exposed to Extremely Bright or Inadequate Lighting Conditions | Spend Time Standing | Exposed to Cramped Work Space, Awkward Positions | Pace Determined by Speed of Equipment</t>
+  </si>
+  <si>
+    <t>Bus and Truck Mechanics and Diesel Engine Specialists | Chemical Plant and System Operators | Continuous Mining Machine Operators | Conveyor Operators and Tenders | Crane and Tower Operators | Excavating and Loading Machine and Dragline Operators, Surface Mining | Gas Compressor and Gas Pumping Station Operators | Heavy and Tractor-Trailer Truck Drivers | Hoist and Winch Operators | Industrial Machinery Mechanics | Industrial Truck and Tractor Operators | Laborers and Freight, Stock, and Material Movers, Hand | Loading and Moving Machine Operators, Underground Mining | Machine Feeders and Offbearers | Maintenance Workers, Machinery | Mobile Heavy Equipment Mechanics, Except Engines | Petroleum Pump System Operators, Refinery Operators, and Gaugers | Pump Operators, Except Wellhead Pumpers | Recycling and Reclamation Workers | Separating, Filtering, Clarifying, Precipitating, and Still Machine Setters, Operators, and Tenders</t>
+  </si>
+  <si>
+    <t>Load and unload chemicals and bulk solids, such as coal, sand, and grain, into or from tank cars, trucks, or ships, using material moving equipment. May perform a variety of other tasks relating to shipment of products. May gauge or sample shipping tanks and test them for leaks.</t>
+  </si>
+  <si>
+    <t>Check conditions and weights of vessels to ensure cleanliness and compliance with loading procedures. | Clean interiors of tank cars or tank trucks, using mechanical spray nozzles. | Connect ground cables to carry off static electricity when unloading tanker cars. | Copy and attach load specifications to loaded tanks. | Lower gauge rods into tanks or read meters to verify contents, temperatures, and volumes of liquid loads. | Monitor product movement to and from storage tanks, coordinating activities with other workers to ensure constant product flow. | Observe positions of cars passing loading spouts, and swing spouts into the correct positions at the appropriate times. | Operate conveyors and equipment to transfer grain or other materials from transportation vehicles. | Operate industrial trucks, tractors, loaders, and other equipment to transport materials to and from transportation vehicles and loading docks, and to store and retrieve materials in warehouses. | Operate ship loading and unloading equipment, conveyors, hoists, and other specialized material handling equipment such as railroad tank car unloading equipment. | Perform general warehouse activities, such as opening containers and crates, filling warehouse orders, assisting in taking inventory, and weighing and checking materials. | Record operating data such as products and quantities pumped, gauge readings, and operating times, manually or using computers. | Remove and replace tank car dome caps, or direct other workers in their removal and replacement. | Seal outlet valves on tank cars, barges, and trucks. | Start pumps and adjust valves or cables to regulate the flow of products to vessels, using knowledge of loading procedures. | Test samples for specific gravity, using hydrometers, or send samples to laboratories for testing. | Test vessels for leaks, damage, and defects, and repair or replace defective parts as necessary. | Unload cars containing liquids by connecting hoses to outlet plugs and pumping compressed air into cars to force liquids into storage tanks. | Verify tank car, barge, or truck load numbers to ensure car placement accuracy based on written or verbal instructions.</t>
+  </si>
+  <si>
+    <t>53-7199.00</t>
+  </si>
+  <si>
+    <t>Material Moving Workers, All Other</t>
+  </si>
+  <si>
+    <t>Bulk Material Handler | Load Handler | Material Handler | Material Moving Worker | Materials Mover | Equipment Operator | Loader Operator | Transfer Worker | Yard Material Handler | Bulk Loader</t>
+  </si>
+  <si>
+    <t>Fleet management software | Transportation management software | Warehouse management system WMS | Microsoft Excel | Microsoft Word | Email software | Inventory management systems | Database software | Scheduling software | Web browser software | Microsoft Outlook | Enterprise resource planning ERP system | Supervisory control and data acquisition SCADA software</t>
+  </si>
+  <si>
+    <t>Transportation | Mechanical | Public Safety and Security | English Language | Production and Processing | Mathematics</t>
+  </si>
+  <si>
+    <t>Indoors, Not Environmentally Controlled | Spend Time Standing | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Spend Time Making Repetitive Motions | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Exposed to Contaminants | Exposed to Hazardous Equipment | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Spend Time Bending or Twisting Your Body | Physical Proximity | Pace Determined by Speed of Equipment | Health and Safety of Other Workers | Consequence of Error | Degree of Automation | Importance of Repeating Same Tasks | Face-to-Face Discussions with Individuals and Within Teams | Work With or Contribute to a Work Group or Team | Importance of Being Exact or Accurate | Outdoors, Exposed to All Weather Conditions | In an Enclosed Vehicle or Operate Enclosed Equipment | Exposed to Whole Body Vibration</t>
+  </si>
+  <si>
+    <t>Laborers and Freight, Stock, and Material Movers, Hand | Industrial Truck and Tractor Operators | Machine Feeders and Offbearers | Conveyor Operators and Tenders | Crane and Tower Operators | Hoist and Winch Operators | Dredge Operators | Tank Car, Truck, and Ship Loaders | Packers and Packagers, Hand | Stockers and Order Fillers | Refuse and Recyclable Material Collectors | Recycling and Reclamation Workers | Cleaners of Vehicles and Equipment | Gas Compressor and Gas Pumping Station Operators | Pump Operators, Except Wellhead Pumpers | Shipping, Receiving, and Inventory Clerks | First-Line Supervisors of Material-Moving Machine and Vehicle Operators | First-Line Supervisors of Helpers, Laborers, and Material Movers, Hand | Transportation, Storage, and Distribution Managers | Heavy and Tractor-Trailer Truck Drivers</t>
+  </si>
+  <si>
+    <t>All material moving workers not listed separately.</t>
+  </si>
+  <si>
+    <t>Move materials in roles not classified separately. | Operate equipment that loads, unloads, transfers, and stacks materials. | Attach and detach slings, hoses, chutes, and loading attachments. | Position containers, hoppers, and vehicles for loading and unloading. | Monitor material flow and adjust equipment to prevent spills and jams. | Weigh, measure, and record quantities of materials moved. | Inspect equipment and report mechanical problems and safety hazards. | Perform routine cleaning, lubrication, and minor equipment maintenance. | Follow procedures for handling hazardous and bulk materials. | Verify shipping documents, tags, and material identification. | Secure loads and apply blocking, bracing, and covers. | Communicate with operators, drivers, and supervisors using radios and signals. | Keep work areas, chutes, and conveyors clear of debris. | Assist with inventory counts and material staging.</t>
+  </si>
+  <si>
+    <t>55-1011.00</t>
+  </si>
+  <si>
+    <t>Air Crew Officers</t>
+  </si>
+  <si>
+    <t>Air Battle Manager | Airborne Mission Systems Officer | Combat Systems Officer | Electronic Warfare Officer | Flight Officer | Naval Flight Officer | Tactical Coordinator | Weapon Systems Officer | Airborne Mission Commander | Aircrew Officer</t>
+  </si>
+  <si>
+    <t>Radar software | Flight simulation software | Navigation software | Geographic information system GIS software | Digital mapping software | Satellite database software | Simulation and modeling software | Electronic aircraft information databases | Microsoft Excel | Microsoft Word | Microsoft PowerPoint | Email software | Terrain surface mapping software | Satellite image databases</t>
+  </si>
+  <si>
+    <t>Critical Thinking | Speaking | Active Listening | Monitoring | Reading Comprehension | Active Learning | Writing | Learning Strategies</t>
+  </si>
+  <si>
+    <t>Public Safety and Security | Transportation | Telecommunications | Computers and Electronics | Geography | English Language | Administration and Management | Engineering and Technology | Education and Training | Personnel and Human Resources</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Oral Expression | Written Comprehension | Written Expression | Deductive Reasoning | Inductive Reasoning | Problem Sensitivity | Information Ordering | Speech Clarity | Speech Recognition | Near Vision | Far Vision | Selective Attention | Category Flexibility | Fluency of Ideas | Originality | Time Sharing | Visualization | Auditory Attention | Reaction Time | Spatial Orientation</t>
+  </si>
+  <si>
+    <t>Face-to-Face Discussions with Individuals and Within Teams | Work With or Contribute to a Work Group or Team | Contact With Others | Consequence of Error | Importance of Being Exact or Accurate | Health and Safety of Other Workers | Frequency of Decision Making | Time Pressure | Physical Proximity | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Coordinate or Lead Others in Accomplishing Work Activities | Impact of Decisions on Co-workers or Company Results | Work Outcomes and Results of Other Workers | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | E-Mail | Telephone Conversations | In an Enclosed Vehicle or Operate Enclosed Equipment | Exposed to Hazardous Conditions | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Spend Time Sitting</t>
+  </si>
+  <si>
+    <t>Airline Pilots, Copilots, and Flight Engineers | Commercial Pilots | Air Traffic Controllers | Airfield Operations Specialists | Aircraft Mechanics and Service Technicians | Avionics Technicians | Aerospace Engineers | Aerospace Engineering and Operations Technologists and Technicians | Emergency Management Directors | Transportation, Storage, and Distribution Managers | Logisticians | General and Operations Managers | Chief Executives | First-Line Supervisors of Police and Detectives | Detectives and Criminal Investigators | Police and Sheriff's Patrol Officers | Security Guards | Transportation Security Screeners | Training and Development Specialists | Occupational Health and Safety Specialists</t>
+  </si>
+  <si>
+    <t>Perform and direct in-flight duties to ensure the successful completion of combat, reconnaissance, transport, and search and rescue missions. Duties include operating aircraft communications and radar equipment, such as establishing satellite linkages and jamming enemy communications capabilities; operating aircraft weapons and defensive systems; conducting preflight, in-flight, and postflight inspections of onboard equipment; and directing cargo and personnel drops.</t>
+  </si>
+  <si>
+    <t>Direct in-flight duties of air crew members to ensure successful completion of combat, reconnaissance, transport, and search and rescue missions. | Operate aircraft communications and radar equipment, including establishing satellite linkages and jamming enemy communications capabilities. | Conduct preflight briefings covering mission objectives, threat assessments, weather conditions, and emergency procedures. | Monitor and interpret radar, sonar, and electronic warfare displays to detect, identify, and track airborne and surface contacts. | Coordinate tactical air operations with ground, naval, and allied command elements. | Direct the operation of airborne weapons and defensive countermeasure systems. | Evaluate mission data and prepare post-flight reports documenting results, malfunctions, and threat activity. | Supervise the loading and securing of cargo, equipment, and personnel aboard aircraft. | Direct search and rescue operations, including the deployment of recovery equipment and personnel. | Ensure compliance with flight safety regulations, operating procedures, and rules of engagement. | Train and evaluate air crew members on mission systems, emergency procedures, and survival techniques. | Perform preflight and postflight inspections of aircraft mission equipment. | Maintain flight logs, mission records, and equipment status reports. | Calculate fuel requirements, payload limits, and weight and balance data for assigned missions. | Recommend improvements to tactics, techniques, and procedures based on mission experience. | Coordinate aircraft maintenance requirements with ground support personnel.</t>
+  </si>
+  <si>
+    <t>55-1012.00</t>
+  </si>
+  <si>
+    <t>Aircraft Launch and Recovery Officers</t>
+  </si>
+  <si>
+    <t>Aircraft Handling Officer | Air Officer | Catapult and Arresting Gear Officer | Flight Deck Officer | Launch and Recovery Officer | Aviation Boatswain Officer | Carrier Air Traffic Control Officer | Aircraft Launch Officer | Flight Deck Operations Officer | Arresting Gear Officer</t>
+  </si>
+  <si>
+    <t>Computerized maintenance management system CMMS | Radar software | Maintenance management software | Microsoft Excel | Microsoft Word | Email software | Simulation and modeling software | Navigation software | Digital mapping software | Logistics management information LMI database software | Microsoft PowerPoint | Satellite database software</t>
+  </si>
+  <si>
+    <t>Mechanical | Public Safety and Security | Engineering and Technology | Transportation | Administration and Management | Physics | English Language | Personnel and Human Resources | Education and Training</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Oral Expression | Written Comprehension | Written Expression | Deductive Reasoning | Inductive Reasoning | Problem Sensitivity | Information Ordering | Speech Clarity | Speech Recognition | Near Vision | Far Vision | Selective Attention | Category Flexibility | Fluency of Ideas | Originality | Time Sharing | Visualization | Auditory Attention | Reaction Time | Depth Perception | Control Precision</t>
+  </si>
+  <si>
+    <t>Face-to-Face Discussions with Individuals and Within Teams | Work With or Contribute to a Work Group or Team | Contact With Others | Consequence of Error | Importance of Being Exact or Accurate | Health and Safety of Other Workers | Frequency of Decision Making | Time Pressure | Physical Proximity | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Coordinate or Lead Others in Accomplishing Work Activities | Impact of Decisions on Co-workers or Company Results | Work Outcomes and Results of Other Workers | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | E-Mail | Telephone Conversations | Exposed to Hazardous Equipment | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Outdoors, Exposed to All Weather Conditions | Exposed to Contaminants | Spend Time Standing</t>
+  </si>
+  <si>
+    <t>Aircraft Mechanics and Service Technicians | Avionics Technicians | Industrial Machinery Mechanics | Mobile Heavy Equipment Mechanics, Except Engines | Electrical and Electronics Repairers, Commercial and Industrial Equipment | Telecommunications Equipment Installers and Repairers, Except Line Installers | Radio, Cellular, and Tower Equipment Installers and Repairers | Riggers | Crane and Tower Operators | Operating Engineers and Other Construction Equipment Operators | Ship Engineers | Sailors and Marine Oilers | Captains, Mates, and Pilots of Water Vessels | Airfield Operations Specialists | Logisticians | Transportation, Storage, and Distribution Managers | General and Operations Managers | Occupational Health and Safety Specialists | Training and Development Specialists | Explosives Workers, Ordnance Handling Experts, and Blasters</t>
+  </si>
+  <si>
+    <t>Plan and direct the operation and maintenance of catapults, arresting gear, and associated mechanical, hydraulic, and control systems involved primarily in aircraft carrier takeoff and landing operations. Duties include supervision of readiness and safety of arresting gear, launching equipment, barricades, and visual landing aid systems; planning and coordinating the design, development, and testing of launch and recovery systems; preparing specifications for catapult and arresting gear installations; evaluating design proposals; determining handling equipment needed for new aircraft; preparing technical data and instructions for operation of landing aids; and training personnel in carrier takeoff and landing procedures.</t>
+  </si>
+  <si>
+    <t>Plan and direct the operation and maintenance of catapults, arresting gear, and associated mechanical, hydraulic, and control systems. | Supervise the readiness and safety of arresting gear, launching equipment, barricades, and visual landing aids. | Direct flight deck crews during aircraft launch and recovery cycles. | Establish and enforce flight deck safety procedures and foreign object damage prevention programs. | Coordinate launch and recovery sequences with air traffic control and ship navigation personnel. | Inspect launch and recovery equipment to verify compliance with operating standards. | Direct emergency procedures for aircraft crashes, fires, and equipment failures on the flight deck. | Calculate catapult settings and arresting gear configurations based on aircraft type, weight, and wind conditions. | Supervise the maintenance, testing, and certification of launch and recovery systems. | Train and qualify personnel in flight deck operations and equipment handling. | Maintain records of equipment operation, maintenance actions, and launch and recovery cycles. | Coordinate aircraft movement, spotting, and tie-down operations on the flight deck and hangar bay. | Evaluate crew performance and recommend corrective training or procedural changes. | Direct the handling and servicing of aircraft fuel, ordnance, and support equipment. | Investigate equipment malfunctions and mishaps and prepare formal reports.</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -330,10 +1940,1761 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:K50"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I3" t="s">
+        <v>30</v>
+      </c>
+      <c r="J3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G4" t="s">
+        <v>39</v>
+      </c>
+      <c r="H4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I4" t="s">
+        <v>41</v>
+      </c>
+      <c r="J4" t="s">
+        <v>42</v>
+      </c>
+      <c r="K4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F5" t="s">
+        <v>49</v>
+      </c>
+      <c r="G5" t="s">
+        <v>50</v>
+      </c>
+      <c r="H5" t="s">
+        <v>51</v>
+      </c>
+      <c r="I5" t="s">
+        <v>52</v>
+      </c>
+      <c r="J5" t="s">
+        <v>53</v>
+      </c>
+      <c r="K5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C6" t="s">
+        <v>57</v>
+      </c>
+      <c r="D6" t="s">
+        <v>58</v>
+      </c>
+      <c r="E6" t="s">
+        <v>59</v>
+      </c>
+      <c r="F6" t="s">
+        <v>60</v>
+      </c>
+      <c r="G6" t="s">
+        <v>61</v>
+      </c>
+      <c r="H6" t="s">
+        <v>62</v>
+      </c>
+      <c r="I6" t="s">
+        <v>63</v>
+      </c>
+      <c r="J6" t="s">
+        <v>64</v>
+      </c>
+      <c r="K6" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>66</v>
+      </c>
+      <c r="B7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D7" t="s">
+        <v>69</v>
+      </c>
+      <c r="E7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F7" t="s">
+        <v>71</v>
+      </c>
+      <c r="G7" t="s">
+        <v>72</v>
+      </c>
+      <c r="H7" t="s">
+        <v>73</v>
+      </c>
+      <c r="I7" t="s">
+        <v>74</v>
+      </c>
+      <c r="J7" t="s">
+        <v>75</v>
+      </c>
+      <c r="K7" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>77</v>
+      </c>
+      <c r="B8" t="s">
+        <v>78</v>
+      </c>
+      <c r="C8" t="s">
+        <v>79</v>
+      </c>
+      <c r="D8" t="s">
+        <v>80</v>
+      </c>
+      <c r="E8" t="s">
+        <v>81</v>
+      </c>
+      <c r="F8" t="s">
+        <v>82</v>
+      </c>
+      <c r="G8" t="s">
+        <v>83</v>
+      </c>
+      <c r="H8" t="s">
+        <v>84</v>
+      </c>
+      <c r="I8" t="s">
+        <v>85</v>
+      </c>
+      <c r="J8" t="s">
+        <v>86</v>
+      </c>
+      <c r="K8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>88</v>
+      </c>
+      <c r="B9" t="s">
+        <v>89</v>
+      </c>
+      <c r="C9" t="s">
+        <v>90</v>
+      </c>
+      <c r="D9" t="s">
+        <v>91</v>
+      </c>
+      <c r="E9" t="s">
+        <v>92</v>
+      </c>
+      <c r="F9" t="s">
+        <v>93</v>
+      </c>
+      <c r="G9" t="s">
+        <v>94</v>
+      </c>
+      <c r="H9" t="s">
+        <v>95</v>
+      </c>
+      <c r="I9" t="s">
+        <v>96</v>
+      </c>
+      <c r="J9" t="s">
+        <v>97</v>
+      </c>
+      <c r="K9" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>99</v>
+      </c>
+      <c r="B10" t="s">
+        <v>100</v>
+      </c>
+      <c r="C10" t="s">
+        <v>101</v>
+      </c>
+      <c r="D10" t="s">
+        <v>102</v>
+      </c>
+      <c r="E10" t="s">
+        <v>103</v>
+      </c>
+      <c r="F10" t="s">
+        <v>104</v>
+      </c>
+      <c r="G10" t="s">
+        <v>105</v>
+      </c>
+      <c r="H10" t="s">
+        <v>106</v>
+      </c>
+      <c r="I10" t="s">
+        <v>107</v>
+      </c>
+      <c r="J10" t="s">
+        <v>108</v>
+      </c>
+      <c r="K10" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>110</v>
+      </c>
+      <c r="B11" t="s">
+        <v>111</v>
+      </c>
+      <c r="C11" t="s">
+        <v>112</v>
+      </c>
+      <c r="D11" t="s">
+        <v>113</v>
+      </c>
+      <c r="E11" t="s">
+        <v>103</v>
+      </c>
+      <c r="F11" t="s">
+        <v>114</v>
+      </c>
+      <c r="G11" t="s">
+        <v>115</v>
+      </c>
+      <c r="H11" t="s">
+        <v>116</v>
+      </c>
+      <c r="I11" t="s">
+        <v>117</v>
+      </c>
+      <c r="J11" t="s">
+        <v>118</v>
+      </c>
+      <c r="K11" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>120</v>
+      </c>
+      <c r="B12" t="s">
+        <v>121</v>
+      </c>
+      <c r="C12" t="s">
+        <v>122</v>
+      </c>
+      <c r="D12" t="s">
+        <v>123</v>
+      </c>
+      <c r="E12" t="s">
+        <v>124</v>
+      </c>
+      <c r="F12" t="s">
+        <v>125</v>
+      </c>
+      <c r="G12" t="s">
+        <v>126</v>
+      </c>
+      <c r="H12" t="s">
+        <v>127</v>
+      </c>
+      <c r="I12" t="s">
+        <v>128</v>
+      </c>
+      <c r="J12" t="s">
+        <v>129</v>
+      </c>
+      <c r="K12" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>131</v>
+      </c>
+      <c r="B13" t="s">
+        <v>132</v>
+      </c>
+      <c r="C13" t="s">
+        <v>133</v>
+      </c>
+      <c r="D13" t="s">
+        <v>134</v>
+      </c>
+      <c r="E13" t="s">
+        <v>135</v>
+      </c>
+      <c r="F13" t="s">
+        <v>136</v>
+      </c>
+      <c r="G13" t="s">
+        <v>137</v>
+      </c>
+      <c r="H13" t="s">
+        <v>138</v>
+      </c>
+      <c r="I13" t="s">
+        <v>139</v>
+      </c>
+      <c r="J13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>142</v>
+      </c>
+      <c r="B14" t="s">
+        <v>143</v>
+      </c>
+      <c r="C14" t="s">
+        <v>144</v>
+      </c>
+      <c r="D14" t="s">
+        <v>145</v>
+      </c>
+      <c r="E14" t="s">
+        <v>146</v>
+      </c>
+      <c r="F14" t="s">
+        <v>147</v>
+      </c>
+      <c r="G14" t="s">
+        <v>148</v>
+      </c>
+      <c r="H14" t="s">
+        <v>149</v>
+      </c>
+      <c r="I14" t="s">
+        <v>150</v>
+      </c>
+      <c r="J14" t="s">
+        <v>151</v>
+      </c>
+      <c r="K14" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>153</v>
+      </c>
+      <c r="B15" t="s">
+        <v>154</v>
+      </c>
+      <c r="C15" t="s">
+        <v>155</v>
+      </c>
+      <c r="D15" t="s">
+        <v>156</v>
+      </c>
+      <c r="E15" t="s">
+        <v>157</v>
+      </c>
+      <c r="F15" t="s">
+        <v>158</v>
+      </c>
+      <c r="G15" t="s">
+        <v>159</v>
+      </c>
+      <c r="H15" t="s">
+        <v>160</v>
+      </c>
+      <c r="I15" t="s">
+        <v>161</v>
+      </c>
+      <c r="J15" t="s">
+        <v>162</v>
+      </c>
+      <c r="K15" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>164</v>
+      </c>
+      <c r="B16" t="s">
+        <v>165</v>
+      </c>
+      <c r="C16" t="s">
+        <v>166</v>
+      </c>
+      <c r="D16" t="s">
+        <v>167</v>
+      </c>
+      <c r="E16" t="s">
+        <v>168</v>
+      </c>
+      <c r="F16" t="s">
+        <v>169</v>
+      </c>
+      <c r="G16" t="s">
+        <v>170</v>
+      </c>
+      <c r="H16" t="s">
+        <v>171</v>
+      </c>
+      <c r="I16" t="s">
+        <v>172</v>
+      </c>
+      <c r="J16" t="s">
+        <v>173</v>
+      </c>
+      <c r="K16" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>175</v>
+      </c>
+      <c r="B17" t="s">
+        <v>176</v>
+      </c>
+      <c r="C17" t="s">
+        <v>177</v>
+      </c>
+      <c r="D17" t="s">
+        <v>178</v>
+      </c>
+      <c r="E17" t="s">
+        <v>103</v>
+      </c>
+      <c r="F17" t="s">
+        <v>179</v>
+      </c>
+      <c r="G17" t="s">
+        <v>115</v>
+      </c>
+      <c r="H17" t="s">
+        <v>180</v>
+      </c>
+      <c r="I17" t="s">
+        <v>181</v>
+      </c>
+      <c r="J17" t="s">
+        <v>182</v>
+      </c>
+      <c r="K17" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>184</v>
+      </c>
+      <c r="B18" t="s">
+        <v>185</v>
+      </c>
+      <c r="C18" t="s">
+        <v>186</v>
+      </c>
+      <c r="D18" t="s">
+        <v>187</v>
+      </c>
+      <c r="E18" t="s">
+        <v>188</v>
+      </c>
+      <c r="F18" t="s">
+        <v>189</v>
+      </c>
+      <c r="G18" t="s">
+        <v>190</v>
+      </c>
+      <c r="H18" t="s">
+        <v>191</v>
+      </c>
+      <c r="I18" t="s">
+        <v>192</v>
+      </c>
+      <c r="J18" t="s">
+        <v>193</v>
+      </c>
+      <c r="K18" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>195</v>
+      </c>
+      <c r="B19" t="s">
+        <v>196</v>
+      </c>
+      <c r="C19" t="s">
+        <v>197</v>
+      </c>
+      <c r="D19" t="s">
+        <v>198</v>
+      </c>
+      <c r="E19" t="s">
+        <v>199</v>
+      </c>
+      <c r="F19" t="s">
+        <v>200</v>
+      </c>
+      <c r="G19" t="s">
+        <v>201</v>
+      </c>
+      <c r="H19" t="s">
+        <v>202</v>
+      </c>
+      <c r="I19" t="s">
+        <v>203</v>
+      </c>
+      <c r="J19" t="s">
+        <v>204</v>
+      </c>
+      <c r="K19" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>206</v>
+      </c>
+      <c r="B20" t="s">
+        <v>207</v>
+      </c>
+      <c r="C20" t="s">
+        <v>208</v>
+      </c>
+      <c r="D20" t="s">
+        <v>209</v>
+      </c>
+      <c r="E20" t="s">
+        <v>210</v>
+      </c>
+      <c r="F20" t="s">
+        <v>211</v>
+      </c>
+      <c r="G20" t="s">
+        <v>212</v>
+      </c>
+      <c r="H20" t="s">
+        <v>213</v>
+      </c>
+      <c r="I20" t="s">
+        <v>214</v>
+      </c>
+      <c r="J20" t="s">
+        <v>215</v>
+      </c>
+      <c r="K20" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>217</v>
+      </c>
+      <c r="B21" t="s">
+        <v>218</v>
+      </c>
+      <c r="C21" t="s">
+        <v>219</v>
+      </c>
+      <c r="D21" t="s">
+        <v>220</v>
+      </c>
+      <c r="E21" t="s">
+        <v>221</v>
+      </c>
+      <c r="F21" t="s">
+        <v>222</v>
+      </c>
+      <c r="G21" t="s">
+        <v>223</v>
+      </c>
+      <c r="H21" t="s">
+        <v>224</v>
+      </c>
+      <c r="I21" t="s">
+        <v>225</v>
+      </c>
+      <c r="J21" t="s">
+        <v>226</v>
+      </c>
+      <c r="K21" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>228</v>
+      </c>
+      <c r="B22" t="s">
+        <v>229</v>
+      </c>
+      <c r="C22" t="s">
+        <v>230</v>
+      </c>
+      <c r="D22" t="s">
+        <v>231</v>
+      </c>
+      <c r="E22" t="s">
+        <v>232</v>
+      </c>
+      <c r="F22" t="s">
+        <v>233</v>
+      </c>
+      <c r="G22" t="s">
+        <v>234</v>
+      </c>
+      <c r="H22" t="s">
+        <v>235</v>
+      </c>
+      <c r="I22" t="s">
+        <v>236</v>
+      </c>
+      <c r="J22" t="s">
+        <v>237</v>
+      </c>
+      <c r="K22" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>239</v>
+      </c>
+      <c r="B23" t="s">
+        <v>240</v>
+      </c>
+      <c r="C23" t="s">
+        <v>241</v>
+      </c>
+      <c r="D23" t="s">
+        <v>242</v>
+      </c>
+      <c r="E23" t="s">
+        <v>243</v>
+      </c>
+      <c r="F23" t="s">
+        <v>244</v>
+      </c>
+      <c r="G23" t="s">
+        <v>245</v>
+      </c>
+      <c r="H23" t="s">
+        <v>246</v>
+      </c>
+      <c r="I23" t="s">
+        <v>247</v>
+      </c>
+      <c r="J23" t="s">
+        <v>248</v>
+      </c>
+      <c r="K23" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>250</v>
+      </c>
+      <c r="B24" t="s">
+        <v>251</v>
+      </c>
+      <c r="C24" t="s">
+        <v>252</v>
+      </c>
+      <c r="D24" t="s">
+        <v>253</v>
+      </c>
+      <c r="E24" t="s">
+        <v>254</v>
+      </c>
+      <c r="F24" t="s">
+        <v>255</v>
+      </c>
+      <c r="G24" t="s">
+        <v>256</v>
+      </c>
+      <c r="H24" t="s">
+        <v>257</v>
+      </c>
+      <c r="I24" t="s">
+        <v>258</v>
+      </c>
+      <c r="J24" t="s">
+        <v>259</v>
+      </c>
+      <c r="K24" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>261</v>
+      </c>
+      <c r="B25" t="s">
+        <v>262</v>
+      </c>
+      <c r="C25" t="s">
+        <v>263</v>
+      </c>
+      <c r="D25" t="s">
+        <v>264</v>
+      </c>
+      <c r="E25" t="s">
+        <v>103</v>
+      </c>
+      <c r="F25" t="s">
+        <v>265</v>
+      </c>
+      <c r="G25" t="s">
+        <v>266</v>
+      </c>
+      <c r="H25" t="s">
+        <v>267</v>
+      </c>
+      <c r="I25" t="s">
+        <v>268</v>
+      </c>
+      <c r="J25" t="s">
+        <v>269</v>
+      </c>
+      <c r="K25" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>271</v>
+      </c>
+      <c r="B26" t="s">
+        <v>272</v>
+      </c>
+      <c r="C26" t="s">
+        <v>273</v>
+      </c>
+      <c r="D26" t="s">
+        <v>274</v>
+      </c>
+      <c r="E26" t="s">
+        <v>275</v>
+      </c>
+      <c r="F26" t="s">
+        <v>276</v>
+      </c>
+      <c r="G26" t="s">
+        <v>277</v>
+      </c>
+      <c r="H26" t="s">
+        <v>278</v>
+      </c>
+      <c r="I26" t="s">
+        <v>279</v>
+      </c>
+      <c r="J26" t="s">
+        <v>280</v>
+      </c>
+      <c r="K26" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>282</v>
+      </c>
+      <c r="B27" t="s">
+        <v>283</v>
+      </c>
+      <c r="C27" t="s">
+        <v>284</v>
+      </c>
+      <c r="D27" t="s">
+        <v>285</v>
+      </c>
+      <c r="E27" t="s">
+        <v>286</v>
+      </c>
+      <c r="F27" t="s">
+        <v>287</v>
+      </c>
+      <c r="G27" t="s">
+        <v>288</v>
+      </c>
+      <c r="H27" t="s">
+        <v>289</v>
+      </c>
+      <c r="I27" t="s">
+        <v>290</v>
+      </c>
+      <c r="J27" t="s">
+        <v>291</v>
+      </c>
+      <c r="K27" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>293</v>
+      </c>
+      <c r="B28" t="s">
+        <v>294</v>
+      </c>
+      <c r="C28" t="s">
+        <v>295</v>
+      </c>
+      <c r="D28" t="s">
+        <v>296</v>
+      </c>
+      <c r="E28" t="s">
+        <v>297</v>
+      </c>
+      <c r="F28" t="s">
+        <v>298</v>
+      </c>
+      <c r="G28" t="s">
+        <v>299</v>
+      </c>
+      <c r="H28" t="s">
+        <v>300</v>
+      </c>
+      <c r="I28" t="s">
+        <v>301</v>
+      </c>
+      <c r="J28" t="s">
+        <v>302</v>
+      </c>
+      <c r="K28" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>304</v>
+      </c>
+      <c r="B29" t="s">
+        <v>305</v>
+      </c>
+      <c r="C29" t="s">
+        <v>306</v>
+      </c>
+      <c r="D29" t="s">
+        <v>307</v>
+      </c>
+      <c r="E29" t="s">
+        <v>308</v>
+      </c>
+      <c r="F29" t="s">
+        <v>309</v>
+      </c>
+      <c r="G29" t="s">
+        <v>310</v>
+      </c>
+      <c r="H29" t="s">
+        <v>311</v>
+      </c>
+      <c r="I29" t="s">
+        <v>312</v>
+      </c>
+      <c r="J29" t="s">
+        <v>313</v>
+      </c>
+      <c r="K29" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>315</v>
+      </c>
+      <c r="B30" t="s">
+        <v>316</v>
+      </c>
+      <c r="C30" t="s">
+        <v>317</v>
+      </c>
+      <c r="D30" t="s">
+        <v>318</v>
+      </c>
+      <c r="E30" t="s">
+        <v>319</v>
+      </c>
+      <c r="F30" t="s">
+        <v>320</v>
+      </c>
+      <c r="G30" t="s">
+        <v>321</v>
+      </c>
+      <c r="H30" t="s">
+        <v>322</v>
+      </c>
+      <c r="I30" t="s">
+        <v>323</v>
+      </c>
+      <c r="J30" t="s">
+        <v>324</v>
+      </c>
+      <c r="K30" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>326</v>
+      </c>
+      <c r="B31" t="s">
+        <v>327</v>
+      </c>
+      <c r="C31" t="s">
+        <v>328</v>
+      </c>
+      <c r="D31" t="s">
+        <v>113</v>
+      </c>
+      <c r="E31" t="s">
+        <v>103</v>
+      </c>
+      <c r="F31" t="s">
+        <v>329</v>
+      </c>
+      <c r="G31" t="s">
+        <v>115</v>
+      </c>
+      <c r="H31" t="s">
+        <v>330</v>
+      </c>
+      <c r="I31" t="s">
+        <v>331</v>
+      </c>
+      <c r="J31" t="s">
+        <v>332</v>
+      </c>
+      <c r="K31" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>334</v>
+      </c>
+      <c r="B32" t="s">
+        <v>335</v>
+      </c>
+      <c r="C32" t="s">
+        <v>336</v>
+      </c>
+      <c r="D32" t="s">
+        <v>337</v>
+      </c>
+      <c r="E32" t="s">
+        <v>188</v>
+      </c>
+      <c r="F32" t="s">
+        <v>338</v>
+      </c>
+      <c r="G32" t="s">
+        <v>339</v>
+      </c>
+      <c r="H32" t="s">
+        <v>340</v>
+      </c>
+      <c r="I32" t="s">
+        <v>341</v>
+      </c>
+      <c r="J32" t="s">
+        <v>342</v>
+      </c>
+      <c r="K32" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>344</v>
+      </c>
+      <c r="B33" t="s">
+        <v>345</v>
+      </c>
+      <c r="C33" t="s">
+        <v>346</v>
+      </c>
+      <c r="D33" t="s">
+        <v>347</v>
+      </c>
+      <c r="E33" t="s">
+        <v>348</v>
+      </c>
+      <c r="F33" t="s">
+        <v>349</v>
+      </c>
+      <c r="G33" t="s">
+        <v>350</v>
+      </c>
+      <c r="H33" t="s">
+        <v>351</v>
+      </c>
+      <c r="I33" t="s">
+        <v>352</v>
+      </c>
+      <c r="J33" t="s">
+        <v>353</v>
+      </c>
+      <c r="K33" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>355</v>
+      </c>
+      <c r="B34" t="s">
+        <v>356</v>
+      </c>
+      <c r="C34" t="s">
+        <v>357</v>
+      </c>
+      <c r="D34" t="s">
+        <v>358</v>
+      </c>
+      <c r="E34" t="s">
+        <v>359</v>
+      </c>
+      <c r="F34" t="s">
+        <v>360</v>
+      </c>
+      <c r="G34" t="s">
+        <v>361</v>
+      </c>
+      <c r="H34" t="s">
+        <v>362</v>
+      </c>
+      <c r="I34" t="s">
+        <v>363</v>
+      </c>
+      <c r="J34" t="s">
+        <v>364</v>
+      </c>
+      <c r="K34" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>366</v>
+      </c>
+      <c r="B35" t="s">
+        <v>367</v>
+      </c>
+      <c r="C35" t="s">
+        <v>368</v>
+      </c>
+      <c r="D35" t="s">
+        <v>369</v>
+      </c>
+      <c r="E35" t="s">
+        <v>370</v>
+      </c>
+      <c r="F35" t="s">
+        <v>371</v>
+      </c>
+      <c r="G35" t="s">
+        <v>372</v>
+      </c>
+      <c r="H35" t="s">
+        <v>373</v>
+      </c>
+      <c r="I35" t="s">
+        <v>374</v>
+      </c>
+      <c r="J35" t="s">
+        <v>375</v>
+      </c>
+      <c r="K35" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>377</v>
+      </c>
+      <c r="B36" t="s">
+        <v>378</v>
+      </c>
+      <c r="C36" t="s">
+        <v>379</v>
+      </c>
+      <c r="D36" t="s">
+        <v>380</v>
+      </c>
+      <c r="E36" t="s">
+        <v>103</v>
+      </c>
+      <c r="F36" t="s">
+        <v>381</v>
+      </c>
+      <c r="G36" t="s">
+        <v>382</v>
+      </c>
+      <c r="H36" t="s">
+        <v>383</v>
+      </c>
+      <c r="I36" t="s">
+        <v>384</v>
+      </c>
+      <c r="J36" t="s">
+        <v>385</v>
+      </c>
+      <c r="K36" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>387</v>
+      </c>
+      <c r="B37" t="s">
+        <v>388</v>
+      </c>
+      <c r="C37" t="s">
+        <v>389</v>
+      </c>
+      <c r="D37" t="s">
+        <v>390</v>
+      </c>
+      <c r="E37" t="s">
+        <v>391</v>
+      </c>
+      <c r="F37" t="s">
+        <v>244</v>
+      </c>
+      <c r="G37" t="s">
+        <v>392</v>
+      </c>
+      <c r="H37" t="s">
+        <v>393</v>
+      </c>
+      <c r="I37" t="s">
+        <v>394</v>
+      </c>
+      <c r="J37" t="s">
+        <v>395</v>
+      </c>
+      <c r="K37" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>397</v>
+      </c>
+      <c r="B38" t="s">
+        <v>398</v>
+      </c>
+      <c r="C38" t="s">
+        <v>399</v>
+      </c>
+      <c r="D38" t="s">
+        <v>400</v>
+      </c>
+      <c r="E38" t="s">
+        <v>401</v>
+      </c>
+      <c r="F38" t="s">
+        <v>402</v>
+      </c>
+      <c r="G38" t="s">
+        <v>403</v>
+      </c>
+      <c r="H38" t="s">
+        <v>404</v>
+      </c>
+      <c r="I38" t="s">
+        <v>405</v>
+      </c>
+      <c r="J38" t="s">
+        <v>406</v>
+      </c>
+      <c r="K38" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>408</v>
+      </c>
+      <c r="B39" t="s">
+        <v>409</v>
+      </c>
+      <c r="C39" t="s">
+        <v>410</v>
+      </c>
+      <c r="D39" t="s">
+        <v>411</v>
+      </c>
+      <c r="E39" t="s">
+        <v>412</v>
+      </c>
+      <c r="F39" t="s">
+        <v>413</v>
+      </c>
+      <c r="G39" t="s">
+        <v>414</v>
+      </c>
+      <c r="H39" t="s">
+        <v>415</v>
+      </c>
+      <c r="I39" t="s">
+        <v>416</v>
+      </c>
+      <c r="J39" t="s">
+        <v>417</v>
+      </c>
+      <c r="K39" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>419</v>
+      </c>
+      <c r="B40" t="s">
+        <v>420</v>
+      </c>
+      <c r="C40" t="s">
+        <v>421</v>
+      </c>
+      <c r="D40" t="s">
+        <v>422</v>
+      </c>
+      <c r="E40" t="s">
+        <v>423</v>
+      </c>
+      <c r="F40" t="s">
+        <v>424</v>
+      </c>
+      <c r="G40" t="s">
+        <v>425</v>
+      </c>
+      <c r="H40" t="s">
+        <v>426</v>
+      </c>
+      <c r="I40" t="s">
+        <v>427</v>
+      </c>
+      <c r="J40" t="s">
+        <v>428</v>
+      </c>
+      <c r="K40" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>430</v>
+      </c>
+      <c r="B41" t="s">
+        <v>431</v>
+      </c>
+      <c r="C41" t="s">
+        <v>432</v>
+      </c>
+      <c r="D41" t="s">
+        <v>433</v>
+      </c>
+      <c r="E41" t="s">
+        <v>423</v>
+      </c>
+      <c r="F41" t="s">
+        <v>434</v>
+      </c>
+      <c r="G41" t="s">
+        <v>435</v>
+      </c>
+      <c r="H41" t="s">
+        <v>436</v>
+      </c>
+      <c r="I41" t="s">
+        <v>437</v>
+      </c>
+      <c r="J41" t="s">
+        <v>438</v>
+      </c>
+      <c r="K41" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>440</v>
+      </c>
+      <c r="B42" t="s">
+        <v>441</v>
+      </c>
+      <c r="C42" t="s">
+        <v>442</v>
+      </c>
+      <c r="D42" t="s">
+        <v>443</v>
+      </c>
+      <c r="E42" t="s">
+        <v>444</v>
+      </c>
+      <c r="F42" t="s">
+        <v>445</v>
+      </c>
+      <c r="G42" t="s">
+        <v>446</v>
+      </c>
+      <c r="H42" t="s">
+        <v>447</v>
+      </c>
+      <c r="I42" t="s">
+        <v>448</v>
+      </c>
+      <c r="J42" t="s">
+        <v>449</v>
+      </c>
+      <c r="K42" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>451</v>
+      </c>
+      <c r="B43" t="s">
+        <v>452</v>
+      </c>
+      <c r="C43" t="s">
+        <v>453</v>
+      </c>
+      <c r="D43" t="s">
+        <v>454</v>
+      </c>
+      <c r="E43" t="s">
+        <v>455</v>
+      </c>
+      <c r="F43" t="s">
+        <v>456</v>
+      </c>
+      <c r="G43" t="s">
+        <v>457</v>
+      </c>
+      <c r="H43" t="s">
+        <v>458</v>
+      </c>
+      <c r="I43" t="s">
+        <v>459</v>
+      </c>
+      <c r="J43" t="s">
+        <v>460</v>
+      </c>
+      <c r="K43" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>462</v>
+      </c>
+      <c r="B44" t="s">
+        <v>463</v>
+      </c>
+      <c r="C44" t="s">
+        <v>464</v>
+      </c>
+      <c r="D44" t="s">
+        <v>465</v>
+      </c>
+      <c r="E44" t="s">
+        <v>466</v>
+      </c>
+      <c r="F44" t="s">
+        <v>467</v>
+      </c>
+      <c r="G44" t="s">
+        <v>468</v>
+      </c>
+      <c r="H44" t="s">
+        <v>469</v>
+      </c>
+      <c r="I44" t="s">
+        <v>470</v>
+      </c>
+      <c r="J44" t="s">
+        <v>471</v>
+      </c>
+      <c r="K44" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>473</v>
+      </c>
+      <c r="B45" t="s">
+        <v>474</v>
+      </c>
+      <c r="C45" t="s">
+        <v>475</v>
+      </c>
+      <c r="D45" t="s">
+        <v>476</v>
+      </c>
+      <c r="E45" t="s">
+        <v>477</v>
+      </c>
+      <c r="F45" t="s">
+        <v>349</v>
+      </c>
+      <c r="G45" t="s">
+        <v>478</v>
+      </c>
+      <c r="H45" t="s">
+        <v>479</v>
+      </c>
+      <c r="I45" t="s">
+        <v>480</v>
+      </c>
+      <c r="J45" t="s">
+        <v>481</v>
+      </c>
+      <c r="K45" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>483</v>
+      </c>
+      <c r="B46" t="s">
+        <v>484</v>
+      </c>
+      <c r="C46" t="s">
+        <v>485</v>
+      </c>
+      <c r="D46" t="s">
+        <v>486</v>
+      </c>
+      <c r="E46" t="s">
+        <v>103</v>
+      </c>
+      <c r="F46" t="s">
+        <v>371</v>
+      </c>
+      <c r="G46" t="s">
+        <v>487</v>
+      </c>
+      <c r="H46" t="s">
+        <v>488</v>
+      </c>
+      <c r="I46" t="s">
+        <v>489</v>
+      </c>
+      <c r="J46" t="s">
+        <v>490</v>
+      </c>
+      <c r="K46" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>492</v>
+      </c>
+      <c r="B47" t="s">
+        <v>493</v>
+      </c>
+      <c r="C47" t="s">
+        <v>494</v>
+      </c>
+      <c r="D47" t="s">
+        <v>495</v>
+      </c>
+      <c r="E47" t="s">
+        <v>496</v>
+      </c>
+      <c r="F47" t="s">
+        <v>497</v>
+      </c>
+      <c r="G47" t="s">
+        <v>498</v>
+      </c>
+      <c r="H47" t="s">
+        <v>499</v>
+      </c>
+      <c r="I47" t="s">
+        <v>500</v>
+      </c>
+      <c r="J47" t="s">
+        <v>501</v>
+      </c>
+      <c r="K47" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>503</v>
+      </c>
+      <c r="B48" t="s">
+        <v>504</v>
+      </c>
+      <c r="C48" t="s">
+        <v>505</v>
+      </c>
+      <c r="D48" t="s">
+        <v>506</v>
+      </c>
+      <c r="E48" t="s">
+        <v>103</v>
+      </c>
+      <c r="F48" t="s">
+        <v>507</v>
+      </c>
+      <c r="G48" t="s">
+        <v>115</v>
+      </c>
+      <c r="H48" t="s">
+        <v>508</v>
+      </c>
+      <c r="I48" t="s">
+        <v>509</v>
+      </c>
+      <c r="J48" t="s">
+        <v>510</v>
+      </c>
+      <c r="K48" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>512</v>
+      </c>
+      <c r="B49" t="s">
+        <v>513</v>
+      </c>
+      <c r="C49" t="s">
+        <v>514</v>
+      </c>
+      <c r="D49" t="s">
+        <v>515</v>
+      </c>
+      <c r="E49" t="s">
+        <v>516</v>
+      </c>
+      <c r="F49" t="s">
+        <v>517</v>
+      </c>
+      <c r="G49" t="s">
+        <v>518</v>
+      </c>
+      <c r="H49" t="s">
+        <v>519</v>
+      </c>
+      <c r="I49" t="s">
+        <v>520</v>
+      </c>
+      <c r="J49" t="s">
+        <v>521</v>
+      </c>
+      <c r="K49" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>523</v>
+      </c>
+      <c r="B50" t="s">
+        <v>524</v>
+      </c>
+      <c r="C50" t="s">
+        <v>525</v>
+      </c>
+      <c r="D50" t="s">
+        <v>526</v>
+      </c>
+      <c r="E50" t="s">
+        <v>516</v>
+      </c>
+      <c r="F50" t="s">
+        <v>527</v>
+      </c>
+      <c r="G50" t="s">
+        <v>528</v>
+      </c>
+      <c r="H50" t="s">
+        <v>529</v>
+      </c>
+      <c r="I50" t="s">
+        <v>530</v>
+      </c>
+      <c r="J50" t="s">
+        <v>531</v>
+      </c>
+      <c r="K50" t="s">
+        <v>532</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>